--- a/AAII_Financials/Quarterly/TSN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TSN_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -656,409 +656,421 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45290</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45108</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45017</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44835</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44744</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44653</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44562</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44471</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44380</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44289</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44198</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44107</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44009</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43918</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43827</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43736</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43645</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43554</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43463</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43372</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43099</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42917</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42826</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>13319000</v>
+      </c>
+      <c r="E8" s="3">
         <v>13348000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>13140000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>13133000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>13260000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>13737000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>13495000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>13117000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>12933000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>12811000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>12478000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>11300000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>10460000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>11460000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>10022000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>10888000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>10815000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>10884000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>10885000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>10443000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>10193000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>9999000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>10051000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>9773000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>10229000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>10145000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>9850000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>9083000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>9182000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>9156000</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>12418000</v>
+      </c>
+      <c r="E9" s="3">
         <v>12666000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>12451000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>12518000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>12319000</v>
       </c>
-      <c r="H9" s="3">
-        <v>12430000</v>
-      </c>
       <c r="I9" s="3">
+        <v>12412000</v>
+      </c>
+      <c r="J9" s="3">
         <v>11884000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>11382000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>10918000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>10270000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>10803000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>9952000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>9163000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>9653000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>8394000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>9966000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>9337000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>19490000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>9549000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>9251000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>8838000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>8660000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>8752000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>8753000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>8786000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>8794000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>8648000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>8036000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>7699000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>8067000</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>901000</v>
+      </c>
+      <c r="E10" s="3">
         <v>682000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>689000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>615000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>941000</v>
       </c>
-      <c r="H10" s="3">
-        <v>1307000</v>
-      </c>
       <c r="I10" s="3">
+        <v>1325000</v>
+      </c>
+      <c r="J10" s="3">
         <v>1611000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1735000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2015000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2541000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1675000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1348000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1297000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1807000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1628000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>922000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1478000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>-8606000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1336000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1192000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1355000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1339000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1299000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1020000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1443000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1351000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1202000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1047000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1483000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1089000</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1091,8 +1103,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1183,8 +1196,11 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1275,28 +1291,31 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>105000</v>
+      </c>
+      <c r="E14" s="3">
         <v>581000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>491000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>114000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-14000</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>8</v>
+      <c r="I14" s="3">
+        <v>66000</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>8</v>
@@ -1304,50 +1323,50 @@
       <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="3">
         <v>65000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>55000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>95000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>120000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>223000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>342000</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>52000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>10000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-40000</v>
-      </c>
-      <c r="V14" s="3">
-        <v>8000</v>
       </c>
       <c r="W14" s="3">
         <v>8000</v>
       </c>
       <c r="X14" s="3">
-        <v>14000</v>
+        <v>8000</v>
       </c>
       <c r="Y14" s="3">
         <v>14000</v>
       </c>
       <c r="Z14" s="3">
-        <v>0</v>
+        <v>14000</v>
       </c>
       <c r="AA14" s="3">
         <v>0</v>
@@ -1367,8 +1386,11 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1459,8 +1481,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1490,192 +1515,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>13088000</v>
+      </c>
+      <c r="E17" s="3">
         <v>13811000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>13468000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>13182000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>12793000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>12971000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>12462000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>11961000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>11478000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>10902000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>11416000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>10580000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>9755000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>10554000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>9247000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>10373000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>10057000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>10337000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>10049000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>9808000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>9386000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>9180000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>9254000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>9275000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>9307000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>9464000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>9153000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>8512000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>8200000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>8570000</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>231000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-463000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-328000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-49000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>467000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>766000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1033000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1156000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1455000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1909000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1062000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>720000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>705000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>906000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>775000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>515000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>758000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>547000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>836000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>635000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>807000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>819000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>797000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>498000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>922000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>681000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>697000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>571000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>982000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>586000</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1708,468 +1740,484 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>35000</v>
       </c>
       <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>-9000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>8000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>51000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-17000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>38000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>28000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>55000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>29000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>9000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>14000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>21000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>14000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>109000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>19000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-15000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>9000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>12000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>5000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>25000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>13000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>9000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>6000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-7000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-9000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>4000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-12000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>639000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-67000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-14000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>276000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>821000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1059000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1368000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1479000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1810000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2246000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1373000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1040000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1024000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1221000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1084000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>917000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1065000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>821000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1131000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>920000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1062000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1090000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1048000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>737000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1157000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>892000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>875000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>754000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1147000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>768000</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>105000</v>
+      </c>
+      <c r="E22" s="3">
         <v>93000</v>
-      </c>
-      <c r="E22" s="3">
-        <v>89000</v>
       </c>
       <c r="F22" s="3">
         <v>89000</v>
       </c>
       <c r="G22" s="3">
+        <v>89000</v>
+      </c>
+      <c r="H22" s="3">
         <v>84000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>83000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>85000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>97000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>100000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>103000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>105000</v>
-      </c>
-      <c r="N22" s="3">
-        <v>110000</v>
       </c>
       <c r="O22" s="3">
         <v>110000</v>
       </c>
       <c r="P22" s="3">
+        <v>110000</v>
+      </c>
+      <c r="Q22" s="3">
         <v>124000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>122000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>119000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>120000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>123000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>121000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>119000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>99000</v>
-      </c>
-      <c r="X22" s="3">
-        <v>87000</v>
       </c>
       <c r="Y22" s="3">
         <v>87000</v>
       </c>
       <c r="Z22" s="3">
+        <v>87000</v>
+      </c>
+      <c r="AA22" s="3">
         <v>84000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>86000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>94000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>71000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>56000</v>
-      </c>
-      <c r="AE22" s="3">
-        <v>58000</v>
       </c>
       <c r="AF22" s="3">
         <v>58000</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>58000</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>161000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-556000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-426000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-130000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>434000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>666000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>986000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1087000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1410000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1835000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>966000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>624000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>616000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>781000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>667000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>505000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>657000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>409000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>724000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>528000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>713000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>757000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>723000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>423000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>842000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>580000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>617000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>519000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>912000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>531000</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>47000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-113000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>9000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-39000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>114000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>129000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>233000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>254000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>284000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>477000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>213000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>147000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>144000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>165000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>140000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>126000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>148000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>79000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>43000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>98000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>161000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>220000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>182000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>116000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>204000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>185000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>169000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>178000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>318000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>139000</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2260,192 +2308,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>114000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-443000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-435000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-91000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>320000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>537000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>753000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>833000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1126000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1358000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>753000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>477000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>472000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>616000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>527000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>379000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>509000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>330000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>681000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>430000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>552000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>537000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>541000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>307000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>638000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>395000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>448000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>341000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>594000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>392000</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>107000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-450000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-417000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-97000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>316000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>538000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>750000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>829000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1121000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1355000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>749000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>476000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>467000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>613000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>527000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>376000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>505000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>327000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>676000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>426000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>551000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>537000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>540000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>306000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>637000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>394000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>447000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>340000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>593000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>391000</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2536,8 +2593,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2586,8 +2646,8 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>8</v>
+      <c r="S29" s="3">
+        <v>0</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>8</v>
@@ -2601,20 +2661,20 @@
       <c r="W29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X29" s="3">
-        <v>0</v>
+      <c r="X29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3">
         <v>1000</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>9000</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>994000</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
@@ -2628,8 +2688,11 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2720,8 +2783,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2812,192 +2878,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>-35000</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>9000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-8000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-51000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>17000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-38000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-28000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-55000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-29000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-9000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-14000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-21000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-14000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-109000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-19000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>15000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-9000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-12000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-5000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-25000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-13000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-9000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-6000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>7000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>9000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-4000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>12000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-3000</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>107000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-450000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-417000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-97000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>316000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>538000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>750000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>829000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1121000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1355000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>749000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>476000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>467000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>613000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>527000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>376000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>505000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>327000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>676000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>426000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>551000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>537000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>541000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>315000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1631000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>394000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>447000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>340000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>593000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>391000</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3088,197 +3163,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>107000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-450000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-417000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-97000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>316000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>538000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>750000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>829000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1121000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1355000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>749000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>476000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>467000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>613000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>527000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>376000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>505000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>327000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>676000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>426000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>551000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>537000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>541000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>315000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1631000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>394000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>447000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>340000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>593000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>391000</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45290</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45108</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45017</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44835</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44744</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44653</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44562</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44471</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44380</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44289</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44198</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44107</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44009</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43918</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43827</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43736</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43645</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43554</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43463</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43372</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43099</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42917</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42826</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3311,8 +3395,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3345,100 +3430,104 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1484000</v>
+      </c>
+      <c r="E41" s="3">
         <v>573000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>699000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>543000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>654000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1031000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1056000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1151000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2956000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2507000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1613000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>877000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2406000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1420000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1365000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>437000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>497000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>484000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>406000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>360000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>400000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>270000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>170000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>198000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>293000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>318000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>231000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>243000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>307000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>349000</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3529,376 +3618,391 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2263000</v>
+      </c>
+      <c r="E43" s="3">
         <v>2476000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2451000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2433000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2295000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2577000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2518000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2408000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2091000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2400000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2324000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2113000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1900000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1952000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2064000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2248000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2063000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>4346000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2452000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1837000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1892000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1723000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1684000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1594000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1600000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1675000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1710000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1589000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1512000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1542000</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>5087000</v>
+      </c>
+      <c r="E44" s="3">
         <v>5328000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>5391000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>5504000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>5596000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>5514000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>5332000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>4990000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>4454000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>4382000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>4262000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>4128000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>3915000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>3859000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>3915000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>4025000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>4304000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>3929000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>4149000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>3899000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>3777000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>3513000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>3378000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>3328000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>3213000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>3239000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>3248000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>2970000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>2767000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>2732000</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>382000</v>
+      </c>
+      <c r="E45" s="3">
         <v>345000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>342000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>412000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>408000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>508000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>397000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>448000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>635000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>533000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1009000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>896000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>323000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>367000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>355000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>389000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>329000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>404000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>426000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>280000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>232000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>182000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>845000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>870000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>887000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1026000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1099000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>215000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>156000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>265000</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>9216000</v>
+      </c>
+      <c r="E46" s="3">
         <v>8722000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>8883000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>8892000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>8953000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>9630000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>9303000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>8997000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>10136000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>9822000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>9208000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>8014000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>8544000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>7598000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>7699000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>7099000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>7193000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>6990000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>7433000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>6376000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>6301000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>5688000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>6077000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>5990000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>5993000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>6258000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>6288000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>5017000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>4742000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>4888000</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3989,192 +4093,201 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>9672000</v>
+      </c>
+      <c r="E48" s="3">
         <v>9634000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>9612000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>9351000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>9120000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>9192000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>8393000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>8193000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>8012000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>7837000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>7725000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>7661000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>7664000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>8128000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>8055000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>8005000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>7911000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>7282000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>7271000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>7085000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>7018000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>6169000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>5925000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>5755000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>5673000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>5568000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>5545000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>5283000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>5206000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>5170000</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>15931000</v>
+      </c>
+      <c r="E49" s="3">
         <v>15976000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>16366000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>16707000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>16763000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>16765000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>16856000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>16945000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>17009000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>17068000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>17141000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>17204000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>17632000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>17673000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>17732000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>17745000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>17837000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>17881000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>18150000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>18241000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>18255000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>16498000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>15903000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>15635000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>15686000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>15567000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>15636000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>11705000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>11733000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>11753000</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4265,8 +4378,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4357,100 +4473,106 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1927000</v>
+      </c>
+      <c r="E52" s="3">
         <v>1919000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1900000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1846000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1842000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1234000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1693000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1763000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1667000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1582000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1589000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1595000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1618000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1057000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1072000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1041000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>870000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>765000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>811000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>796000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>761000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>754000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>733000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>711000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>694000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>673000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>594000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>591000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>576000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>562000</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4541,100 +4663,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>36746000</v>
+      </c>
+      <c r="E54" s="3">
         <v>36251000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>36761000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>36796000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>36678000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>36821000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>36245000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>35898000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>36824000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>36309000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>35663000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>34474000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>35458000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>34456000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>34558000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>33890000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>33811000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>32918000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>33665000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>32498000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>32335000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>29109000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>28638000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>28091000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>28046000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>28066000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>28063000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>22596000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>22257000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>22373000</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4667,8 +4795,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4701,560 +4830,579 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2623000</v>
+      </c>
+      <c r="E57" s="3">
         <v>2594000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2421000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2387000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2530000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2483000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2306000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2269000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2115000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2225000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1950000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1900000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1997000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1876000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1743000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1742000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1916000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1926000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1958000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1710000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1962000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1694000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1546000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1485000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1748000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1698000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1608000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1466000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1591000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1511000</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1308000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1895000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>457000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1065000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>490000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>459000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>67000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>79000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1090000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1067000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1566000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>580000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>566000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>548000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>750000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1142000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1947000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>2102000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>2125000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1564000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>3917000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1911000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1308000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1128000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>811000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>906000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1017000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>543000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>66000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>79000</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2241000</v>
+      </c>
+      <c r="E59" s="3">
         <v>2010000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2070000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1894000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2094000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2371000</v>
-      </c>
-      <c r="I59" s="3">
-        <v>2309000</v>
       </c>
       <c r="J59" s="3">
         <v>2309000</v>
       </c>
       <c r="K59" s="3">
+        <v>2309000</v>
+      </c>
+      <c r="L59" s="3">
         <v>2829000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3033000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2668000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2132000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2286000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1810000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1780000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1522000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1673000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1485000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1514000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1340000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1551000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1426000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1258000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1225000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1419000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1428000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1240000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1097000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1315000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1172000</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6172000</v>
+      </c>
+      <c r="E60" s="3">
         <v>6499000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>4948000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>5346000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>5114000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>5313000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>4682000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>4657000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>6034000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>6325000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>6184000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>4612000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>4849000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>4234000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>4273000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>4406000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>5536000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>5513000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>5597000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>4614000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>7430000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>5031000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>4112000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>3838000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>3978000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>4032000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>3865000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>3106000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>2972000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>2762000</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>8370000</v>
+      </c>
+      <c r="E61" s="3">
         <v>7611000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>8863000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>7865000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>7859000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>7862000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>8261000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>8270000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>8274000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>8281000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>8786000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>9784000</v>
-      </c>
-      <c r="O61" s="3">
-        <v>10791000</v>
       </c>
       <c r="P61" s="3">
         <v>10791000</v>
       </c>
       <c r="Q61" s="3">
+        <v>10791000</v>
+      </c>
+      <c r="R61" s="3">
         <v>11279000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>10978000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>9772000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>9830000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>10461000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>10810000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>8075000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>7962000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>8852000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>8872000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>8875000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>9297000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>9807000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>5905000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>5901000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>6200000</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3916000</v>
+      </c>
+      <c r="E62" s="3">
         <v>3886000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>4040000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>4027000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>3918000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3835000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3813000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3815000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3974000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3849000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>4000000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>4008000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>4037000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>4045000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>4002000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3912000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3937000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3481000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3466000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3516000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>3571000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>3305000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>3237000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>3225000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>3219000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>4178000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>4254000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>3796000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>3817000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>3787000</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5345,8 +5493,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5437,8 +5588,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5529,100 +5683,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>18596000</v>
+      </c>
+      <c r="E66" s="3">
         <v>18118000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>17982000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>17397000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>17043000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>17119000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>16890000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>16884000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>18421000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>18586000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>19102000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>18543000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>19820000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>19202000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>19700000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>19441000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>19392000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>18968000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>19737000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>19075000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>19208000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>16306000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>16212000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>15955000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>16091000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>17525000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>17946000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>12825000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>12707000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>12765000</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5655,8 +5815,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5747,8 +5908,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5839,8 +6003,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5931,8 +6098,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6023,100 +6193,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>18693000</v>
+      </c>
+      <c r="E72" s="3">
         <v>18760000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>19378000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>19962000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>20225000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>20084000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>19708000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>19119000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>18453000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>17502000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>16305000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>15716000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>15399000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>15100000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>14769000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>14392000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>14178000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>13655000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>13553000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>13012000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>12719000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>12329000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>11913000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>11479000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>11272000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>9776000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>9464000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>9098000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>8837000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>8348000</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6207,8 +6383,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6299,8 +6478,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6391,100 +6573,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>18150000</v>
+      </c>
+      <c r="E76" s="3">
         <v>18133000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>18779000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>19399000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>19635000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>19702000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>19355000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>19014000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>18403000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>17723000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>16561000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>15931000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>15638000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>15254000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>14858000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>14449000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>14419000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>13950000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>13928000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>13423000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>13127000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>12803000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>12426000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>12136000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>11955000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>10541000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>10117000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>9771000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>9550000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>9608000</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6575,197 +6763,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45290</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45108</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45017</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44835</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44744</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44653</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44562</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44471</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44380</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44289</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44198</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44107</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44009</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43918</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43827</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43736</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43645</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43554</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43463</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43372</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43099</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42917</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42826</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>107000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-450000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-417000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-97000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>316000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>538000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>750000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>829000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1121000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1355000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>749000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>476000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>467000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>613000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>527000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>376000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>505000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>327000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>676000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>426000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>551000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>537000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>541000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>315000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1631000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>394000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>447000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>340000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>593000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>391000</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6798,100 +6995,104 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>373000</v>
+      </c>
+      <c r="E83" s="3">
         <v>396000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>323000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>317000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>303000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>310000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>297000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>295000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>300000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>308000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>302000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>306000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>298000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>316000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>295000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>293000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>288000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>289000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>286000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>273000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>250000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>246000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>238000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>230000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>229000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>218000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>187000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>179000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>177000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>179000</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6982,8 +7183,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7074,8 +7278,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7166,8 +7373,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7258,8 +7468,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7350,100 +7563,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1300000</v>
+      </c>
+      <c r="E89" s="3">
         <v>323000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>660000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>7000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>762000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>797000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>666000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-208000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1432000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1184000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1307000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-36000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1385000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1166000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1448000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>366000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>894000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>978000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>596000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>71000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>868000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1039000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>785000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>13000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1126000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1150000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>467000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-152000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1134000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>843000</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7476,100 +7695,104 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-354000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-375000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-467000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-508000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-589000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-564000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-476000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-439000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-408000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-350000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-302000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-268000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-289000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-292000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-283000</v>
-      </c>
-      <c r="R91" s="3">
-        <v>-312000</v>
       </c>
       <c r="S91" s="3">
         <v>-312000</v>
       </c>
       <c r="T91" s="3">
+        <v>-312000</v>
+      </c>
+      <c r="U91" s="3">
         <v>-288000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-315000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-338000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-318000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-313000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-328000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-263000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-296000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-287000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-315000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-267000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-200000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-180000</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7660,8 +7883,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7752,100 +7978,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-378000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-427000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-696000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-507000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-669000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-610000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-440000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-426000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-459000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>841000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-275000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-249000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-259000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-280000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-266000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-496000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-381000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-129000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-569000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-317000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-2449000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-483000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-737000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-264000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-422000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-297000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-3389000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-264000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-214000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-182000</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7878,13 +8110,14 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-167000</v>
+        <v>-171000</v>
       </c>
       <c r="E96" s="3">
         <v>-167000</v>
@@ -7893,22 +8126,22 @@
         <v>-167000</v>
       </c>
       <c r="G96" s="3">
+        <v>-167000</v>
+      </c>
+      <c r="H96" s="3">
         <v>-169000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-162000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-163000</v>
-      </c>
-      <c r="J96" s="3">
-        <v>-164000</v>
       </c>
       <c r="K96" s="3">
         <v>-164000</v>
       </c>
       <c r="L96" s="3">
-        <v>-159000</v>
+        <v>-164000</v>
       </c>
       <c r="M96" s="3">
         <v>-159000</v>
@@ -7920,34 +8153,34 @@
         <v>-159000</v>
       </c>
       <c r="P96" s="3">
-        <v>-150000</v>
+        <v>-159000</v>
       </c>
       <c r="Q96" s="3">
         <v>-150000</v>
       </c>
       <c r="R96" s="3">
+        <v>-150000</v>
+      </c>
+      <c r="S96" s="3">
         <v>-151000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-150000</v>
-      </c>
-      <c r="T96" s="3">
-        <v>-134000</v>
       </c>
       <c r="U96" s="3">
         <v>-134000</v>
       </c>
       <c r="V96" s="3">
+        <v>-134000</v>
+      </c>
+      <c r="W96" s="3">
         <v>-135000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-134000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-107000</v>
-      </c>
-      <c r="Y96" s="3">
-        <v>-108000</v>
       </c>
       <c r="Z96" s="3">
         <v>-108000</v>
@@ -7956,22 +8189,25 @@
         <v>-108000</v>
       </c>
       <c r="AB96" s="3">
+        <v>-108000</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-81000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-80000</v>
-      </c>
-      <c r="AD96" s="3">
-        <v>-79000</v>
       </c>
       <c r="AE96" s="3">
         <v>-79000</v>
       </c>
       <c r="AF96" s="3">
+        <v>-79000</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-54000</v>
       </c>
     </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8062,8 +8298,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8154,8 +8393,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8246,280 +8488,292 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-26000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-13000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>202000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>381000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-482000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-195000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-361000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1283000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-484000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1189000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-197000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1172000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-173000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-874000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-255000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>168000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-507000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-761000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>20000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>201000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>1711000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-455000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-71000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>153000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-729000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-769000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>2908000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>348000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-957000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-510000</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-9000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-10000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>8000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>12000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-17000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-24000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>4000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>2000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-7000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>1000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-6000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>16000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>7000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>1000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-16000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>7000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-10000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-1000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>5000</v>
       </c>
-      <c r="W101" s="3">
-        <v>0</v>
-      </c>
       <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-5000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>3000</v>
       </c>
-      <c r="AA101" s="3">
-        <v>0</v>
-      </c>
       <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="3">
         <v>3000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>2000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>4000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-5000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>911000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-126000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>156000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-111000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-377000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-25000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-159000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1913000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>491000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>829000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>836000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1463000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>969000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>19000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>928000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>22000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>13000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>78000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>46000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-40000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>130000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>100000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-28000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-95000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-25000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>87000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-12000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-64000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-42000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>152000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TSN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TSN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="92">
   <si>
     <t>TSN</t>
   </si>
@@ -656,421 +656,434 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45381</v>
+      </c>
+      <c r="E7" s="2">
         <v>45290</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45108</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45017</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44835</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44744</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44653</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44562</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44471</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44380</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44289</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44198</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44107</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44009</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43918</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43827</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43736</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43645</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43554</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43463</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43372</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43099</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42917</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42826</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>13072000</v>
+      </c>
+      <c r="E8" s="3">
         <v>13319000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>13348000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>13140000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>13133000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>13260000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>13737000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>13495000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>13117000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>12933000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>12811000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>12478000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>11300000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>10460000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>11460000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>10022000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>10888000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>10815000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>10884000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>10885000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>10443000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>10193000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>9999000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>10051000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>9773000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>10229000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>10145000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>9850000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>9083000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>9182000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>9156000</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>12170000</v>
+      </c>
+      <c r="E9" s="3">
         <v>12418000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>12666000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>12451000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>12518000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>12319000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>12412000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>11884000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>11382000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>10918000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>10270000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>10803000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>9952000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>9163000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>9653000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>8394000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>9966000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>9337000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>19490000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>9549000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>9251000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>8838000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>8660000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>8752000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>8753000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>8786000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>8794000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>8648000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>8036000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>7699000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>8067000</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>902000</v>
+      </c>
+      <c r="E10" s="3">
         <v>901000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>682000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>689000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>615000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>941000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1325000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1611000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1735000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2015000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2541000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1675000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1348000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1297000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1807000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1628000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>922000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1478000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>-8606000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1336000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1192000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1355000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1339000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1299000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1020000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1443000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1351000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1202000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1047000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1483000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1089000</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1104,8 +1117,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1199,8 +1213,11 @@
       <c r="AG12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1294,31 +1311,34 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>40000</v>
+      </c>
+      <c r="E14" s="3">
         <v>105000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>581000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>491000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>114000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-14000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>66000</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>8</v>
@@ -1326,50 +1346,50 @@
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="3">
         <v>65000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>55000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>95000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>120000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>223000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>342000</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>52000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>10000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-40000</v>
-      </c>
-      <c r="W14" s="3">
-        <v>8000</v>
       </c>
       <c r="X14" s="3">
         <v>8000</v>
       </c>
       <c r="Y14" s="3">
-        <v>14000</v>
+        <v>8000</v>
       </c>
       <c r="Z14" s="3">
         <v>14000</v>
       </c>
       <c r="AA14" s="3">
-        <v>0</v>
+        <v>14000</v>
       </c>
       <c r="AB14" s="3">
         <v>0</v>
@@ -1389,8 +1409,11 @@
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1484,8 +1507,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1516,198 +1542,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>12760000</v>
+      </c>
+      <c r="E17" s="3">
         <v>13088000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>13811000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>13468000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>13182000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>12793000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>12971000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>12462000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>11961000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>11478000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>10902000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>11416000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>10580000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>9755000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>10554000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>9247000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>10373000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>10057000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>10337000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>10049000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>9808000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>9386000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>9180000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>9254000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>9275000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>9307000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>9464000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>9153000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>8512000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>8200000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>8570000</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>312000</v>
+      </c>
+      <c r="E18" s="3">
         <v>231000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-463000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-328000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-49000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>467000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>766000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1033000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1156000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1455000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1909000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1062000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>720000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>705000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>906000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>775000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>515000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>758000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>547000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>836000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>635000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>807000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>819000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>797000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>498000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>922000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>681000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>697000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>571000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>982000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>586000</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1741,483 +1774,499 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E20" s="3">
         <v>35000</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>-9000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>8000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>51000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-17000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>38000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>28000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>55000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>29000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>9000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>14000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>21000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>14000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>109000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>19000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-15000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>9000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>12000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>5000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>25000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>13000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>9000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>6000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-7000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-9000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>4000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-12000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>663000</v>
+      </c>
+      <c r="E21" s="3">
         <v>639000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-67000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-14000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>276000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>821000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1059000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1368000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1479000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1810000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2246000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1373000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1040000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1024000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1221000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1084000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>917000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1065000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>821000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1131000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>920000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1062000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1090000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1048000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>737000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1157000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>892000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>875000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>754000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1147000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>768000</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>111000</v>
+      </c>
+      <c r="E22" s="3">
         <v>105000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>93000</v>
-      </c>
-      <c r="F22" s="3">
-        <v>89000</v>
       </c>
       <c r="G22" s="3">
         <v>89000</v>
       </c>
       <c r="H22" s="3">
+        <v>89000</v>
+      </c>
+      <c r="I22" s="3">
         <v>84000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>83000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>85000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>97000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>100000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>103000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>105000</v>
-      </c>
-      <c r="O22" s="3">
-        <v>110000</v>
       </c>
       <c r="P22" s="3">
         <v>110000</v>
       </c>
       <c r="Q22" s="3">
+        <v>110000</v>
+      </c>
+      <c r="R22" s="3">
         <v>124000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>122000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>119000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>120000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>123000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>121000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>119000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>99000</v>
-      </c>
-      <c r="Y22" s="3">
-        <v>87000</v>
       </c>
       <c r="Z22" s="3">
         <v>87000</v>
       </c>
       <c r="AA22" s="3">
+        <v>87000</v>
+      </c>
+      <c r="AB22" s="3">
         <v>84000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>86000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>94000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>71000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>56000</v>
-      </c>
-      <c r="AF22" s="3">
-        <v>58000</v>
       </c>
       <c r="AG22" s="3">
         <v>58000</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>58000</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>203000</v>
+      </c>
+      <c r="E23" s="3">
         <v>161000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-556000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-426000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-130000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>434000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>666000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>986000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1087000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1410000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1835000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>966000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>624000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>616000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>781000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>667000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>505000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>657000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>409000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>724000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>528000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>713000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>757000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>723000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>423000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>842000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>580000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>617000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>519000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>912000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>531000</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>55000</v>
+      </c>
+      <c r="E24" s="3">
         <v>47000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-113000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>9000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-39000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>114000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>129000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>233000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>254000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>284000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>477000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>213000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>147000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>144000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>165000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>140000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>126000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>148000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>79000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>43000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>98000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>161000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>220000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>182000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>116000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>204000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>185000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>169000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>178000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>318000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>139000</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2311,198 +2360,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>148000</v>
+      </c>
+      <c r="E26" s="3">
         <v>114000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-443000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-435000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-91000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>320000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>537000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>753000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>833000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1126000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1358000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>753000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>477000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>472000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>616000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>527000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>379000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>509000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>330000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>681000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>430000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>552000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>537000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>541000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>307000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>638000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>395000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>448000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>341000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>594000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>392000</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>145000</v>
+      </c>
+      <c r="E27" s="3">
         <v>107000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-450000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-417000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-97000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>316000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>538000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>750000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>829000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1121000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1355000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>749000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>476000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>467000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>613000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>527000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>376000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>505000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>327000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>676000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>426000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>551000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>537000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>540000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>306000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>637000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>394000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>447000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>340000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>593000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>391000</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2596,8 +2654,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2649,8 +2710,8 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>8</v>
+      <c r="T29" s="3">
+        <v>0</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>8</v>
@@ -2664,20 +2725,20 @@
       <c r="X29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y29" s="3">
-        <v>0</v>
+      <c r="Y29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3">
         <v>1000</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>9000</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>994000</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
@@ -2691,8 +2752,11 @@
       <c r="AG29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2786,8 +2850,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2881,198 +2948,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-35000</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <v>9000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-8000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-51000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>17000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-38000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-28000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-55000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-29000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-9000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-14000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-21000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-14000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-109000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-19000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>15000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-9000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-12000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-5000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-25000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-13000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-9000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-6000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>7000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>9000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-4000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>12000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-3000</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>145000</v>
+      </c>
+      <c r="E33" s="3">
         <v>107000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-450000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-417000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-97000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>316000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>538000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>750000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>829000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1121000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1355000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>749000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>476000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>467000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>613000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>527000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>376000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>505000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>327000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>676000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>426000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>551000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>537000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>541000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>315000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1631000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>394000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>447000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>340000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>593000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>391000</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3166,203 +3242,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>145000</v>
+      </c>
+      <c r="E35" s="3">
         <v>107000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-450000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-417000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-97000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>316000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>538000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>750000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>829000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1121000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1355000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>749000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>476000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>467000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>613000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>527000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>376000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>505000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>327000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>676000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>426000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>551000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>537000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>541000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>315000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1631000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>394000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>447000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>340000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>593000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>391000</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45381</v>
+      </c>
+      <c r="E38" s="2">
         <v>45290</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45108</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45017</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44835</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44744</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44653</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44562</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44471</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44380</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44289</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44198</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44107</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44009</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43918</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43827</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43736</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43645</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43554</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43463</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43372</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43099</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42917</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42826</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3396,8 +3481,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3431,103 +3517,107 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2182000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1484000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>573000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>699000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>543000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>654000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1031000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1056000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1151000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2956000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2507000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1613000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>877000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2406000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1420000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1365000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>437000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>497000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>484000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>406000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>360000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>400000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>270000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>170000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>198000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>293000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>318000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>231000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>243000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>307000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>349000</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3621,388 +3711,403 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2358000</v>
+      </c>
+      <c r="E43" s="3">
         <v>2263000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2476000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2451000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2433000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2295000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2577000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2518000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2408000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2091000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2400000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2324000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2113000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1900000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1952000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2064000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2248000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2063000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>4346000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2452000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1837000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1892000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1723000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1684000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1594000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1600000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1675000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1710000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1589000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1512000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1542000</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>5056000</v>
+      </c>
+      <c r="E44" s="3">
         <v>5087000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>5328000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>5391000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>5504000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>5596000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>5514000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>5332000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>4990000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>4454000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>4382000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>4262000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>4128000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>3915000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>3859000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>3915000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>4025000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>4304000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>3929000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>4149000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>3899000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>3777000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>3513000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>3378000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>3328000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>3213000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>3239000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>3248000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>2970000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>2767000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>2732000</v>
       </c>
     </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>370000</v>
+      </c>
+      <c r="E45" s="3">
         <v>382000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>345000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>342000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>412000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>408000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>508000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>397000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>448000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>635000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>533000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1009000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>896000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>323000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>367000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>355000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>389000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>329000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>404000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>426000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>280000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>232000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>182000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>845000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>870000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>887000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1026000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1099000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>215000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>156000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>265000</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>9966000</v>
+      </c>
+      <c r="E46" s="3">
         <v>9216000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>8722000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>8883000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>8892000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>8953000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>9630000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>9303000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>8997000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>10136000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>9822000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>9208000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>8014000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>8544000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>7598000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>7699000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>7099000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>7193000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>6990000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>7433000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>6376000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>6301000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>5688000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>6077000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>5990000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>5993000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>6258000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>6288000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>5017000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>4742000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>4888000</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4096,198 +4201,207 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>9593000</v>
+      </c>
+      <c r="E48" s="3">
         <v>9672000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>9634000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>9612000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>9351000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>9120000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>9192000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>8393000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>8193000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>8012000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>7837000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>7725000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>7661000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>7664000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>8128000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>8055000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>8005000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>7911000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>7282000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>7271000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>7085000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>7018000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>6169000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>5925000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>5755000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>5673000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>5568000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>5545000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>5283000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>5206000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>5170000</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>15863000</v>
+      </c>
+      <c r="E49" s="3">
         <v>15931000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>15976000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>16366000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>16707000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>16763000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>16765000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>16856000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>16945000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>17009000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>17068000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>17141000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>17204000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>17632000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>17673000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>17732000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>17745000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>17837000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>17881000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>18150000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>18241000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>18255000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>16498000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>15903000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>15635000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>15686000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>15567000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>15636000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>11705000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>11733000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>11753000</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4381,8 +4495,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4476,103 +4593,109 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2043000</v>
+      </c>
+      <c r="E52" s="3">
         <v>1927000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1919000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1900000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1846000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1842000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1234000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1693000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1763000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1667000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1582000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1589000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1595000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1618000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1057000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1072000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1041000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>870000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>765000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>811000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>796000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>761000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>754000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>733000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>711000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>694000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>673000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>594000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>591000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>576000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>562000</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4666,103 +4789,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>37465000</v>
+      </c>
+      <c r="E54" s="3">
         <v>36746000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>36251000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>36761000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>36796000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>36678000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>36821000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>36245000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>35898000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>36824000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>36309000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>35663000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>34474000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>35458000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>34456000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>34558000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>33890000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>33811000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>32918000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>33665000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>32498000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>32335000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>29109000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>28638000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>28091000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>28046000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>28066000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>28063000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>22596000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>22257000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>22373000</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4796,8 +4925,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4831,578 +4961,597 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2244000</v>
+      </c>
+      <c r="E57" s="3">
         <v>2623000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2594000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2421000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2387000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2530000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2483000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2306000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2269000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2115000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2225000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1950000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1900000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1997000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1876000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1743000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1742000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1916000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1926000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1958000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1710000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1962000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1694000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1546000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1485000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1748000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1698000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1608000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1466000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1591000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1511000</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1315000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1308000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1895000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>457000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1065000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>490000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>459000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>67000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>79000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1090000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1067000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1566000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>580000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>566000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>548000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>750000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1142000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1947000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>2102000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>2125000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1564000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>3917000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1911000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1308000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1128000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>811000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>906000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1017000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>543000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>66000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>79000</v>
       </c>
     </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2074000</v>
+      </c>
+      <c r="E59" s="3">
         <v>2241000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2010000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2070000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1894000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2094000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2371000</v>
-      </c>
-      <c r="J59" s="3">
-        <v>2309000</v>
       </c>
       <c r="K59" s="3">
         <v>2309000</v>
       </c>
       <c r="L59" s="3">
+        <v>2309000</v>
+      </c>
+      <c r="M59" s="3">
         <v>2829000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3033000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2668000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2132000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2286000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1810000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1780000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1522000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1673000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1485000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1514000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1340000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1551000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1426000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1258000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1225000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1419000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1428000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1240000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1097000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1315000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1172000</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>5633000</v>
+      </c>
+      <c r="E60" s="3">
         <v>6172000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>6499000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>4948000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>5346000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>5114000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>5313000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>4682000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4657000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>6034000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>6325000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>6184000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>4612000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>4849000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>4234000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>4273000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>4406000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>5536000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>5513000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>5597000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>4614000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>7430000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>5031000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>4112000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>3838000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>3978000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>4032000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>3865000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>3106000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>2972000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>2762000</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>9645000</v>
+      </c>
+      <c r="E61" s="3">
         <v>8370000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>7611000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>8863000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>7865000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>7859000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>7862000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>8261000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>8270000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>8274000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>8281000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>8786000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>9784000</v>
-      </c>
-      <c r="P61" s="3">
-        <v>10791000</v>
       </c>
       <c r="Q61" s="3">
         <v>10791000</v>
       </c>
       <c r="R61" s="3">
+        <v>10791000</v>
+      </c>
+      <c r="S61" s="3">
         <v>11279000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>10978000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>9772000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>9830000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>10461000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>10810000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>8075000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>7962000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>8852000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>8872000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>8875000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>9297000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>9807000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>5905000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>5901000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>6200000</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3964000</v>
+      </c>
+      <c r="E62" s="3">
         <v>3916000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>3886000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>4040000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>4027000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3918000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3835000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3813000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3815000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3974000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3849000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>4000000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>4008000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>4037000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>4045000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>4002000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3912000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3937000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3481000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3466000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>3516000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>3571000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>3305000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>3237000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>3225000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>3219000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>4178000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>4254000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>3796000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>3817000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>3787000</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5496,8 +5645,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5591,8 +5743,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5686,103 +5841,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>19376000</v>
+      </c>
+      <c r="E66" s="3">
         <v>18596000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>18118000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>17982000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>17397000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>17043000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>17119000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>16890000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>16884000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>18421000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>18586000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>19102000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>18543000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>19820000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>19202000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>19700000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>19441000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>19392000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>18968000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>19737000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>19075000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>19208000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>16306000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>16212000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>15955000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>16091000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>17525000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>17946000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>12825000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>12707000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>12765000</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5816,8 +5977,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5911,8 +6073,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6006,8 +6171,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6101,8 +6269,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6196,103 +6367,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>18667000</v>
+      </c>
+      <c r="E72" s="3">
         <v>18693000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>18760000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>19378000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>19962000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>20225000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>20084000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>19708000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>19119000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>18453000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>17502000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>16305000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>15716000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>15399000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>15100000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>14769000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>14392000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>14178000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>13655000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>13553000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>13012000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>12719000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>12329000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>11913000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>11479000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>11272000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>9776000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>9464000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>9098000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>8837000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>8348000</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6386,8 +6563,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6481,8 +6661,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6576,103 +6759,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>18089000</v>
+      </c>
+      <c r="E76" s="3">
         <v>18150000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>18133000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>18779000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>19399000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>19635000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>19702000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>19355000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>19014000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>18403000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>17723000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>16561000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>15931000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>15638000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>15254000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>14858000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>14449000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>14419000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>13950000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>13928000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>13423000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>13127000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>12803000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>12426000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>12136000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>11955000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>10541000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>10117000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>9771000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>9550000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>9608000</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6766,203 +6955,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45381</v>
+      </c>
+      <c r="E80" s="2">
         <v>45290</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45108</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45017</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44835</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44744</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44653</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44562</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44471</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44380</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44289</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44198</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44107</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44009</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43918</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43827</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43736</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43645</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43554</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43463</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43372</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43099</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42917</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42826</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>145000</v>
+      </c>
+      <c r="E81" s="3">
         <v>107000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-450000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-417000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-97000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>316000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>538000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>750000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>829000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1121000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1355000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>749000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>476000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>467000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>613000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>527000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>376000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>505000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>327000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>676000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>426000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>551000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>537000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>541000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>315000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1631000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>394000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>447000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>340000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>593000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>391000</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6996,103 +7194,107 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>349000</v>
+      </c>
+      <c r="E83" s="3">
         <v>373000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>396000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>323000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>317000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>303000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>310000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>297000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>295000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>300000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>308000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>302000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>306000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>298000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>316000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>295000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>293000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>288000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>289000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>286000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>273000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>250000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>246000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>238000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>230000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>229000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>218000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>187000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>179000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>177000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>179000</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7186,8 +7388,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7281,8 +7486,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7376,8 +7584,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7471,8 +7682,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7566,103 +7780,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-123000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1300000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>323000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>660000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>7000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>762000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>797000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>666000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-208000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1432000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1184000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1307000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-36000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1385000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1166000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1448000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>366000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>894000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>978000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>596000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>71000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>868000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1039000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>785000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>13000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1126000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1150000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>467000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-152000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1134000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>843000</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7696,103 +7916,107 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-267000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-354000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-375000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-467000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-508000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-589000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-564000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-476000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-439000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-408000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-350000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-302000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-268000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-289000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-292000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-283000</v>
-      </c>
-      <c r="S91" s="3">
-        <v>-312000</v>
       </c>
       <c r="T91" s="3">
         <v>-312000</v>
       </c>
       <c r="U91" s="3">
+        <v>-312000</v>
+      </c>
+      <c r="V91" s="3">
         <v>-288000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-315000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-338000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-318000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-313000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-328000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-263000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-296000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-287000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-315000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-267000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-200000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-180000</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7886,8 +8110,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7981,103 +8208,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-243000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-378000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-427000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-696000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-507000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-669000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-610000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-440000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-426000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-459000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>841000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-275000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-249000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-259000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-280000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-266000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-496000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-381000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-129000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-569000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-317000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-2449000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-483000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-737000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-264000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-422000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-297000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-3389000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-264000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-214000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-182000</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8111,8 +8344,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8120,7 +8354,7 @@
         <v>-171000</v>
       </c>
       <c r="E96" s="3">
-        <v>-167000</v>
+        <v>-171000</v>
       </c>
       <c r="F96" s="3">
         <v>-167000</v>
@@ -8129,22 +8363,22 @@
         <v>-167000</v>
       </c>
       <c r="H96" s="3">
+        <v>-167000</v>
+      </c>
+      <c r="I96" s="3">
         <v>-169000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-162000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-163000</v>
-      </c>
-      <c r="K96" s="3">
-        <v>-164000</v>
       </c>
       <c r="L96" s="3">
         <v>-164000</v>
       </c>
       <c r="M96" s="3">
-        <v>-159000</v>
+        <v>-164000</v>
       </c>
       <c r="N96" s="3">
         <v>-159000</v>
@@ -8156,34 +8390,34 @@
         <v>-159000</v>
       </c>
       <c r="Q96" s="3">
-        <v>-150000</v>
+        <v>-159000</v>
       </c>
       <c r="R96" s="3">
         <v>-150000</v>
       </c>
       <c r="S96" s="3">
+        <v>-150000</v>
+      </c>
+      <c r="T96" s="3">
         <v>-151000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-150000</v>
-      </c>
-      <c r="U96" s="3">
-        <v>-134000</v>
       </c>
       <c r="V96" s="3">
         <v>-134000</v>
       </c>
       <c r="W96" s="3">
+        <v>-134000</v>
+      </c>
+      <c r="X96" s="3">
         <v>-135000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-134000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-107000</v>
-      </c>
-      <c r="Z96" s="3">
-        <v>-108000</v>
       </c>
       <c r="AA96" s="3">
         <v>-108000</v>
@@ -8192,22 +8426,25 @@
         <v>-108000</v>
       </c>
       <c r="AC96" s="3">
+        <v>-108000</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-81000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-80000</v>
-      </c>
-      <c r="AE96" s="3">
-        <v>-79000</v>
       </c>
       <c r="AF96" s="3">
         <v>-79000</v>
       </c>
       <c r="AG96" s="3">
+        <v>-79000</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-54000</v>
       </c>
     </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8301,8 +8538,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8396,8 +8636,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8491,289 +8734,301 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1077000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-26000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-13000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>202000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>381000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-482000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-195000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-361000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1283000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-484000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1189000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-197000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1172000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-173000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-874000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-255000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>168000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-507000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-761000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>20000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>201000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>1711000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-455000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-71000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>153000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-729000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-769000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>2908000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>348000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-957000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-510000</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="E101" s="3">
         <v>15000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-9000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-10000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>8000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>12000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-17000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-24000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>4000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>2000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-7000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>1000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-6000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>16000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>7000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>1000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-16000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>7000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-10000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-1000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>5000</v>
       </c>
-      <c r="X101" s="3">
-        <v>0</v>
-      </c>
       <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z101" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-5000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>3000</v>
       </c>
-      <c r="AB101" s="3">
-        <v>0</v>
-      </c>
       <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD101" s="3">
         <v>3000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>2000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>4000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-5000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>698000</v>
+      </c>
+      <c r="E102" s="3">
         <v>911000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-126000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>156000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-111000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-377000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-25000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-159000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1913000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>491000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>829000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>836000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1463000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>969000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>19000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>928000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>22000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>13000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>78000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>46000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-40000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>130000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>100000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-28000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-95000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-25000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>87000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-12000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-64000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-42000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>152000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TSN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TSN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="92">
   <si>
     <t>TSN</t>
   </si>
@@ -656,434 +656,447 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45472</v>
+      </c>
+      <c r="E7" s="2">
         <v>45381</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45290</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45108</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45017</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44835</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44744</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44653</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44562</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44471</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44380</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44289</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44198</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44107</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44009</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43918</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43827</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43736</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43645</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43554</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43463</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43372</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43099</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42917</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42826</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>13353000</v>
+      </c>
+      <c r="E8" s="3">
         <v>13072000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>13319000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>13348000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>13140000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>13133000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>13260000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>13737000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>13495000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>13117000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>12933000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>12811000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>12478000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>11300000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>10460000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>11460000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>10022000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>10888000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>10815000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>10884000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>10885000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>10443000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>10193000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>9999000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>10051000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>9773000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>10229000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>10145000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>9850000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>9083000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>9182000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>9156000</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>12170000</v>
+        <v>12436000</v>
       </c>
       <c r="E9" s="3">
-        <v>12418000</v>
+        <v>12116000</v>
       </c>
       <c r="F9" s="3">
+        <v>12368000</v>
+      </c>
+      <c r="G9" s="3">
         <v>12666000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>12451000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>12518000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>12319000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>12412000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>11884000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>11382000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>10918000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>10270000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>10803000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>9952000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>9163000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>9653000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>8394000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>9966000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>9337000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>19490000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>9549000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>9251000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>8838000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>8660000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>8752000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>8753000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>8786000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>8794000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>8648000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>8036000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>7699000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>8067000</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>902000</v>
+        <v>917000</v>
       </c>
       <c r="E10" s="3">
-        <v>901000</v>
+        <v>956000</v>
       </c>
       <c r="F10" s="3">
+        <v>951000</v>
+      </c>
+      <c r="G10" s="3">
         <v>682000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>689000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>615000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>941000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1325000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1611000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1735000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2015000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2541000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1675000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1348000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1297000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1807000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1628000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>922000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1478000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>-8606000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1336000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1192000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1355000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1339000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1299000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1020000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1443000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1351000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1202000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1047000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1483000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1089000</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1118,8 +1131,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1216,8 +1230,11 @@
       <c r="AH12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1314,34 +1331,37 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>40000</v>
+        <v>39000</v>
       </c>
       <c r="E14" s="3">
-        <v>105000</v>
+        <v>94000</v>
       </c>
       <c r="F14" s="3">
+        <v>155000</v>
+      </c>
+      <c r="G14" s="3">
         <v>581000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>491000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>114000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-14000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>66000</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>8</v>
@@ -1349,50 +1369,50 @@
       <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O14" s="3">
         <v>65000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>55000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>95000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>120000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>223000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>342000</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>52000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>10000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>-40000</v>
-      </c>
-      <c r="X14" s="3">
-        <v>8000</v>
       </c>
       <c r="Y14" s="3">
         <v>8000</v>
       </c>
       <c r="Z14" s="3">
-        <v>14000</v>
+        <v>8000</v>
       </c>
       <c r="AA14" s="3">
         <v>14000</v>
       </c>
       <c r="AB14" s="3">
-        <v>0</v>
+        <v>14000</v>
       </c>
       <c r="AC14" s="3">
         <v>0</v>
@@ -1412,8 +1432,11 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1510,8 +1533,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1543,204 +1569,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>13012000</v>
+      </c>
+      <c r="E17" s="3">
         <v>12760000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>13088000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>13811000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>13468000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>13182000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>12793000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>12971000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>12462000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>11961000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>11478000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>10902000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>11416000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>10580000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>9755000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>10554000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>9247000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>10373000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>10057000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>10337000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>10049000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>9808000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>9386000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>9180000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>9254000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>9275000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>9307000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>9464000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>9153000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>8512000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>8200000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>8570000</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>341000</v>
+      </c>
+      <c r="E18" s="3">
         <v>312000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>231000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-463000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-328000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-49000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>467000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>766000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1033000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1156000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1455000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1909000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1062000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>720000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>705000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>906000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>775000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>515000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>758000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>547000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>836000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>635000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>807000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>819000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>797000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>498000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>922000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>681000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>697000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>571000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>982000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>586000</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1775,498 +1808,514 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>47000</v>
+      </c>
+      <c r="E20" s="3">
         <v>2000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>35000</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>-9000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>8000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>51000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-17000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>38000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>28000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>55000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>29000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>9000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>14000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>21000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>14000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>109000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>19000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-15000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>9000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>12000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>5000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>25000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>13000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>9000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>6000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-7000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-9000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>4000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-12000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>748000</v>
+      </c>
+      <c r="E21" s="3">
         <v>663000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>639000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-67000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-14000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>276000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>821000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1059000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1368000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1479000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1810000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2246000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1373000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1040000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1024000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1221000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1084000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>917000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1065000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>821000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1131000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>920000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1062000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1090000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1048000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>737000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1157000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>892000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>875000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>754000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1147000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>768000</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>135000</v>
+      </c>
+      <c r="E22" s="3">
         <v>111000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>105000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>93000</v>
-      </c>
-      <c r="G22" s="3">
-        <v>89000</v>
       </c>
       <c r="H22" s="3">
         <v>89000</v>
       </c>
       <c r="I22" s="3">
+        <v>89000</v>
+      </c>
+      <c r="J22" s="3">
         <v>84000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>83000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>85000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>97000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>100000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>103000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>105000</v>
-      </c>
-      <c r="P22" s="3">
-        <v>110000</v>
       </c>
       <c r="Q22" s="3">
         <v>110000</v>
       </c>
       <c r="R22" s="3">
+        <v>110000</v>
+      </c>
+      <c r="S22" s="3">
         <v>124000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>122000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>119000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>120000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>123000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>121000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>119000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>99000</v>
-      </c>
-      <c r="Z22" s="3">
-        <v>87000</v>
       </c>
       <c r="AA22" s="3">
         <v>87000</v>
       </c>
       <c r="AB22" s="3">
+        <v>87000</v>
+      </c>
+      <c r="AC22" s="3">
         <v>84000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>86000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>94000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>71000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>56000</v>
-      </c>
-      <c r="AG22" s="3">
-        <v>58000</v>
       </c>
       <c r="AH22" s="3">
         <v>58000</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>58000</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>253000</v>
+      </c>
+      <c r="E23" s="3">
         <v>203000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>161000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-556000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-426000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-130000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>434000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>666000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>986000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1087000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1410000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1835000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>966000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>624000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>616000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>781000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>667000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>505000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>657000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>409000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>724000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>528000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>713000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>757000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>723000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>423000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>842000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>580000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>617000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>519000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>912000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>531000</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>57000</v>
+      </c>
+      <c r="E24" s="3">
         <v>55000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>47000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-113000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>9000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-39000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>114000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>129000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>233000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>254000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>284000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>477000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>213000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>147000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>144000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>165000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>140000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>126000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>148000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>79000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>43000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>98000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>161000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>220000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>182000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>116000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>204000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>185000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>169000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>178000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>318000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>139000</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2363,204 +2412,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>196000</v>
+      </c>
+      <c r="E26" s="3">
         <v>148000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>114000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-443000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-435000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-91000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>320000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>537000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>753000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>833000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1126000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1358000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>753000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>477000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>472000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>616000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>527000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>379000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>509000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>330000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>681000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>430000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>552000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>537000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>541000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>307000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>638000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>395000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>448000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>341000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>594000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>392000</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>191000</v>
+      </c>
+      <c r="E27" s="3">
         <v>145000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>107000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-450000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-417000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-97000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>316000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>538000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>750000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>829000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1121000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1355000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>749000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>476000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>467000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>613000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>527000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>376000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>505000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>327000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>676000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>426000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>551000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>537000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>540000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>306000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>637000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>394000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>447000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>340000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>593000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>391000</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2657,8 +2715,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2713,8 +2774,8 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>8</v>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>8</v>
@@ -2728,20 +2789,20 @@
       <c r="Y29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z29" s="3">
-        <v>0</v>
+      <c r="Z29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="3">
         <v>1000</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>9000</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>994000</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>8</v>
@@ -2755,8 +2816,11 @@
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2853,8 +2917,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2951,204 +3018,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-47000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-2000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-35000</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>9000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-8000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-51000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>17000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-38000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-28000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-55000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-29000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-9000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-14000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-21000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-14000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-109000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-19000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>15000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-9000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-12000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-5000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-25000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-13000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-9000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-6000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>7000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>9000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-4000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>12000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-3000</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>191000</v>
+      </c>
+      <c r="E33" s="3">
         <v>145000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>107000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-450000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-417000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-97000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>316000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>538000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>750000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>829000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1121000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1355000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>749000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>476000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>467000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>613000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>527000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>376000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>505000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>327000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>676000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>426000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>551000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>537000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>541000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>315000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1631000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>394000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>447000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>340000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>593000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>391000</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3245,209 +3321,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>191000</v>
+      </c>
+      <c r="E35" s="3">
         <v>145000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>107000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-450000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-417000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-97000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>316000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>538000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>750000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>829000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1121000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1355000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>749000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>476000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>467000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>613000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>527000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>376000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>505000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>327000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>676000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>426000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>551000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>537000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>541000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>315000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1631000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>394000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>447000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>340000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>593000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>391000</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45472</v>
+      </c>
+      <c r="E38" s="2">
         <v>45381</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45290</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45108</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45017</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44835</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44744</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44653</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44562</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44471</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44380</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44289</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44198</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44107</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44009</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43918</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43827</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43736</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43645</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43554</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43463</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43372</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43099</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42917</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42826</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3482,8 +3567,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3518,106 +3604,110 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2569000</v>
+      </c>
+      <c r="E41" s="3">
         <v>2182000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1484000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>573000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>699000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>543000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>654000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1031000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1056000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1151000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2956000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2507000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1613000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>877000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2406000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1420000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1365000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>437000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>497000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>484000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>406000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>360000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>400000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>270000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>170000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>198000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>293000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>318000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>231000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>243000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>307000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>349000</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3714,400 +3804,415 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2389000</v>
+      </c>
+      <c r="E43" s="3">
         <v>2358000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2263000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2476000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2451000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2433000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2295000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2577000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2518000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2408000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2091000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2400000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2324000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2113000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1900000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1952000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2064000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2248000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2063000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>4346000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2452000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1837000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1892000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1723000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1684000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1594000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1600000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1675000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1710000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1589000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1512000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>1542000</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>5033000</v>
+      </c>
+      <c r="E44" s="3">
         <v>5056000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>5087000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>5328000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>5391000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>5504000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>5596000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>5514000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>5332000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>4990000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>4454000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>4382000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>4262000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>4128000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>3915000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>3859000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>3915000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>4025000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>4304000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>3929000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>4149000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>3899000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>3777000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>3513000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>3378000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>3328000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>3213000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>3239000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>3248000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>2970000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>2767000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>2732000</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>581000</v>
+      </c>
+      <c r="E45" s="3">
         <v>370000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>382000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>345000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>342000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>412000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>408000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>508000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>397000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>448000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>635000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>533000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1009000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>896000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>323000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>367000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>355000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>389000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>329000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>404000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>426000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>280000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>232000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>182000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>845000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>870000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>887000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1026000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1099000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>215000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>156000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>265000</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>10572000</v>
+      </c>
+      <c r="E46" s="3">
         <v>9966000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>9216000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>8722000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>8883000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>8892000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>8953000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>9630000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>9303000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>8997000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>10136000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>9822000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>9208000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>8014000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>8544000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>7598000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>7699000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>7099000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>7193000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>6990000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>7433000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>6376000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>6301000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>5688000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>6077000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>5990000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>5993000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>6258000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>6288000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>5017000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>4742000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>4888000</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4204,204 +4309,213 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>9368000</v>
+      </c>
+      <c r="E48" s="3">
         <v>9593000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>9672000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>9634000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>9612000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>9351000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>9120000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>9192000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>8393000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>8193000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>8012000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>7837000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>7725000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>7661000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>7664000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>8128000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>8055000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>8005000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>7911000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>7282000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>7271000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>7085000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>7018000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>6169000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>5925000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>5755000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>5673000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>5568000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>5545000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>5283000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>5206000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>5170000</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>15729000</v>
+      </c>
+      <c r="E49" s="3">
         <v>15863000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>15931000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>15976000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>16366000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>16707000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>16763000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>16765000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>16856000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>16945000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>17009000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>17068000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>17141000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>17204000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>17632000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>17673000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>17732000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>17745000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>17837000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>17881000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>18150000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>18241000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>18255000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>16498000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>15903000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>15635000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>15686000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>15567000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>15636000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>11705000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>11733000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>11753000</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4498,8 +4612,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4596,106 +4713,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2063000</v>
+      </c>
+      <c r="E52" s="3">
         <v>2043000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1927000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1919000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1900000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1846000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1842000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1234000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1693000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1763000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1667000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1582000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1589000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1595000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1618000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1057000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1072000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1041000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>870000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>765000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>811000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>796000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>761000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>754000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>733000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>711000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>694000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>673000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>594000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>591000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>576000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>562000</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4792,106 +4915,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>37732000</v>
+      </c>
+      <c r="E54" s="3">
         <v>37465000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>36746000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>36251000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>36761000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>36796000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>36678000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>36821000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>36245000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>35898000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>36824000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>36309000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>35663000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>34474000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>35458000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>34456000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>34558000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>33890000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>33811000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>32918000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>33665000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>32498000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>32335000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>29109000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>28638000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>28091000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>28046000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>28066000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>28063000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>22596000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>22257000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>22373000</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4926,8 +5055,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4962,596 +5092,615 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2291000</v>
+      </c>
+      <c r="E57" s="3">
         <v>2244000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2623000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2594000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2421000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2387000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2530000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2483000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2306000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2269000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2115000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2225000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1950000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1900000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1997000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1876000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1743000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1742000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1916000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1926000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1958000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1710000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1962000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1694000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1546000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1485000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1748000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1698000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1608000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1466000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1591000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1511000</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1320000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1315000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1308000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1895000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>457000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1065000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>490000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>459000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>67000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>79000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1090000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1067000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1566000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>580000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>566000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>548000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>750000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1142000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1947000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>2102000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>2125000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1564000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>3917000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1911000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1308000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1128000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>811000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>906000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1017000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>543000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>66000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>79000</v>
       </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2199000</v>
+      </c>
+      <c r="E59" s="3">
         <v>2074000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2241000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2010000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2070000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1894000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2094000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2371000</v>
-      </c>
-      <c r="K59" s="3">
-        <v>2309000</v>
       </c>
       <c r="L59" s="3">
         <v>2309000</v>
       </c>
       <c r="M59" s="3">
+        <v>2309000</v>
+      </c>
+      <c r="N59" s="3">
         <v>2829000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3033000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2668000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2132000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2286000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1810000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1780000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1522000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1673000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1485000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1514000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1340000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1551000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1426000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1258000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1225000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1419000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1428000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1240000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1097000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1315000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1172000</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>5810000</v>
+      </c>
+      <c r="E60" s="3">
         <v>5633000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>6172000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>6499000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>4948000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>5346000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>5114000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>5313000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4682000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4657000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>6034000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>6325000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>6184000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>4612000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>4849000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>4234000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>4273000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>4406000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>5536000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>5513000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>5597000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>4614000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>7430000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>5031000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>4112000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>3838000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>3978000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>4032000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>3865000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>3106000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>2972000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>2762000</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>9701000</v>
+      </c>
+      <c r="E61" s="3">
         <v>9645000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>8370000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>7611000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>8863000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>7865000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>7859000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>7862000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>8261000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>8270000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>8274000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>8281000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>8786000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>9784000</v>
-      </c>
-      <c r="Q61" s="3">
-        <v>10791000</v>
       </c>
       <c r="R61" s="3">
         <v>10791000</v>
       </c>
       <c r="S61" s="3">
+        <v>10791000</v>
+      </c>
+      <c r="T61" s="3">
         <v>11279000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>10978000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>9772000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>9830000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>10461000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>10810000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>8075000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>7962000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>8852000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>8872000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>8875000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>9297000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>9807000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>5905000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>5901000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>6200000</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>4019000</v>
+      </c>
+      <c r="E62" s="3">
         <v>3964000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>3916000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>3886000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>4040000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>4027000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3918000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3835000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3813000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3815000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3974000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3849000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>4000000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>4008000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>4037000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>4045000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>4002000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3912000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3937000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3481000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>3466000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>3516000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>3571000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>3305000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>3237000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>3225000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>3219000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>4178000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>4254000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>3796000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>3817000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>3787000</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5648,8 +5797,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5746,8 +5898,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5844,106 +5999,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>19656000</v>
+      </c>
+      <c r="E66" s="3">
         <v>19376000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>18596000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>18118000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>17982000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>17397000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>17043000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>17119000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>16890000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>16884000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>18421000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>18586000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>19102000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>18543000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>19820000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>19202000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>19700000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>19441000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>19392000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>18968000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>19737000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>19075000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>19208000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>16306000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>16212000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>15955000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>16091000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>17525000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>17946000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>12825000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>12707000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>12765000</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5978,8 +6139,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6076,8 +6238,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6174,8 +6339,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6272,8 +6440,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6370,106 +6541,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>18687000</v>
+      </c>
+      <c r="E72" s="3">
         <v>18667000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>18693000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>18760000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>19378000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>19962000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>20225000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>20084000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>19708000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>19119000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>18453000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>17502000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>16305000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>15716000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>15399000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>15100000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>14769000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>14392000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>14178000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>13655000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>13553000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>13012000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>12719000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>12329000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>11913000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>11479000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>11272000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>9776000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>9464000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>9098000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>8837000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>8348000</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6566,8 +6743,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6664,8 +6844,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6762,106 +6945,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>18076000</v>
+      </c>
+      <c r="E76" s="3">
         <v>18089000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>18150000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>18133000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>18779000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>19399000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>19635000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>19702000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>19355000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>19014000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>18403000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>17723000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>16561000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>15931000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>15638000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>15254000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>14858000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>14449000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>14419000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>13950000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>13928000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>13423000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>13127000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>12803000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>12426000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>12136000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>11955000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>10541000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>10117000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>9771000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>9550000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>9608000</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6958,209 +7147,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45472</v>
+      </c>
+      <c r="E80" s="2">
         <v>45381</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45290</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45108</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45017</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44835</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44744</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44653</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44562</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44471</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44380</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44289</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44198</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44107</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44009</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43918</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43827</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43736</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43645</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43554</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43463</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43372</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43099</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42917</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42826</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>191000</v>
+      </c>
+      <c r="E81" s="3">
         <v>145000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>107000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-450000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-417000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-97000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>316000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>538000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>750000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>829000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1121000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1355000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>749000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>476000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>467000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>613000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>527000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>376000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>505000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>327000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>676000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>426000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>551000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>537000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>541000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>315000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1631000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>394000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>447000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>340000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>593000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>391000</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7195,106 +7393,110 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>360000</v>
+      </c>
+      <c r="E83" s="3">
         <v>349000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>373000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>396000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>323000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>317000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>303000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>310000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>297000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>295000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>300000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>308000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>302000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>306000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>298000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>316000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>295000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>293000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>288000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>289000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>286000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>273000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>250000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>246000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>238000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>230000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>229000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>218000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>187000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>179000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>177000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>179000</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7391,8 +7593,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7489,8 +7694,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7587,8 +7795,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7685,8 +7896,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7783,106 +7997,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>796000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-123000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1300000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>323000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>660000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>7000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>762000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>797000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>666000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-208000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1432000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1184000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1307000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-36000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1385000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1166000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1448000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>366000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>894000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>978000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>596000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>71000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>868000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1039000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>785000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>13000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1126000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1150000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>467000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-152000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1134000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>843000</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7917,106 +8137,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-263000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-267000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-354000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-375000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-467000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-508000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-589000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-564000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-476000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-439000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-408000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-350000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-302000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-268000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-289000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-292000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-283000</v>
-      </c>
-      <c r="T91" s="3">
-        <v>-312000</v>
       </c>
       <c r="U91" s="3">
         <v>-312000</v>
       </c>
       <c r="V91" s="3">
+        <v>-312000</v>
+      </c>
+      <c r="W91" s="3">
         <v>-288000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-315000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-338000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-318000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-313000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-328000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-263000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-296000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-287000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-315000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-267000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-200000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-180000</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8113,8 +8337,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8211,106 +8438,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-233000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-243000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-378000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-427000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-696000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-507000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-669000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-610000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-440000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-426000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-459000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>841000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-275000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-249000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-259000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-280000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-266000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-496000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-381000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-129000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-569000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-317000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-2449000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-483000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-737000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-264000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-422000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-297000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-3389000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-264000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-214000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-182000</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8345,8 +8578,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8357,7 +8591,7 @@
         <v>-171000</v>
       </c>
       <c r="F96" s="3">
-        <v>-167000</v>
+        <v>-171000</v>
       </c>
       <c r="G96" s="3">
         <v>-167000</v>
@@ -8366,22 +8600,22 @@
         <v>-167000</v>
       </c>
       <c r="I96" s="3">
+        <v>-167000</v>
+      </c>
+      <c r="J96" s="3">
         <v>-169000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-162000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-163000</v>
-      </c>
-      <c r="L96" s="3">
-        <v>-164000</v>
       </c>
       <c r="M96" s="3">
         <v>-164000</v>
       </c>
       <c r="N96" s="3">
-        <v>-159000</v>
+        <v>-164000</v>
       </c>
       <c r="O96" s="3">
         <v>-159000</v>
@@ -8393,34 +8627,34 @@
         <v>-159000</v>
       </c>
       <c r="R96" s="3">
-        <v>-150000</v>
+        <v>-159000</v>
       </c>
       <c r="S96" s="3">
         <v>-150000</v>
       </c>
       <c r="T96" s="3">
+        <v>-150000</v>
+      </c>
+      <c r="U96" s="3">
         <v>-151000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-150000</v>
-      </c>
-      <c r="V96" s="3">
-        <v>-134000</v>
       </c>
       <c r="W96" s="3">
         <v>-134000</v>
       </c>
       <c r="X96" s="3">
+        <v>-134000</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-135000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-134000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-107000</v>
-      </c>
-      <c r="AA96" s="3">
-        <v>-108000</v>
       </c>
       <c r="AB96" s="3">
         <v>-108000</v>
@@ -8429,22 +8663,25 @@
         <v>-108000</v>
       </c>
       <c r="AD96" s="3">
+        <v>-108000</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-81000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-80000</v>
-      </c>
-      <c r="AF96" s="3">
-        <v>-79000</v>
       </c>
       <c r="AG96" s="3">
         <v>-79000</v>
       </c>
       <c r="AH96" s="3">
+        <v>-79000</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-54000</v>
       </c>
     </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8541,8 +8778,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8639,8 +8879,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8737,298 +8980,310 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-168000</v>
+      </c>
+      <c r="E100" s="3">
         <v>1077000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-26000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-13000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>202000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>381000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-482000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-195000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-361000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1283000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-484000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1189000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-197000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1172000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-173000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-874000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-255000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>168000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-507000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-761000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>20000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>201000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>1711000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-455000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-71000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>153000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-729000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-769000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>2908000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>348000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-957000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-510000</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-13000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>15000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-9000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-10000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>8000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>12000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-17000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-24000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>4000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>2000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-7000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>1000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-6000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>16000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>7000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>1000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-16000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>7000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-10000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-1000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>5000</v>
       </c>
-      <c r="Y101" s="3">
-        <v>0</v>
-      </c>
       <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-5000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>3000</v>
       </c>
-      <c r="AC101" s="3">
-        <v>0</v>
-      </c>
       <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE101" s="3">
         <v>3000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>2000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>4000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-5000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>387000</v>
+      </c>
+      <c r="E102" s="3">
         <v>698000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>911000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-126000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>156000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-111000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-377000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-25000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-159000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1913000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>491000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>829000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>836000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1463000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>969000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>19000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>928000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>22000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>13000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>78000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>46000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-40000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>130000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>100000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-28000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-95000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-25000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>87000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-12000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-64000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-42000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>152000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TSN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TSN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="92">
   <si>
     <t>TSN</t>
   </si>
@@ -656,447 +656,460 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45563</v>
+      </c>
+      <c r="E7" s="2">
         <v>45472</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45381</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45290</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45108</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45017</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44835</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44744</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44653</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44562</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44471</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44380</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44289</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44198</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44107</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44009</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43918</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43827</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43736</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43645</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43554</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43463</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43372</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43099</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42917</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42826</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>13565000</v>
+      </c>
+      <c r="E8" s="3">
         <v>13353000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>13072000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>13319000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>13348000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>13140000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>13133000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>13260000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>13737000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>13495000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>13117000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>12933000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>12811000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>12478000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>11300000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>10460000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>11460000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>10022000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>10888000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>10815000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>10884000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>10885000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>10443000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>10193000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>9999000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>10051000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>9773000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>10229000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>10145000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>9850000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>9083000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>9182000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>9156000</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>12436000</v>
+        <v>12526000</v>
       </c>
       <c r="E9" s="3">
+        <v>12370000</v>
+      </c>
+      <c r="F9" s="3">
         <v>12116000</v>
       </c>
-      <c r="F9" s="3">
-        <v>12368000</v>
-      </c>
       <c r="G9" s="3">
-        <v>12666000</v>
+        <v>12293000</v>
       </c>
       <c r="H9" s="3">
+        <v>12664000</v>
+      </c>
+      <c r="I9" s="3">
         <v>12451000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>12518000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>12319000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>12412000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>11884000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>11382000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>10918000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>10270000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>10803000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>9952000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>9163000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>9653000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>8394000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>9966000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>9337000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>19490000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>9549000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>9251000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>8838000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>8660000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>8752000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>8753000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>8786000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>8794000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>8648000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>8036000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>7699000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>8067000</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>917000</v>
+        <v>1039000</v>
       </c>
       <c r="E10" s="3">
+        <v>983000</v>
+      </c>
+      <c r="F10" s="3">
         <v>956000</v>
       </c>
-      <c r="F10" s="3">
-        <v>951000</v>
-      </c>
       <c r="G10" s="3">
-        <v>682000</v>
+        <v>1026000</v>
       </c>
       <c r="H10" s="3">
+        <v>684000</v>
+      </c>
+      <c r="I10" s="3">
         <v>689000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>615000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>941000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1325000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1611000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1735000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2015000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2541000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1675000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1348000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1297000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1807000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1628000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>922000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1478000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>-8606000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1336000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1192000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1355000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1339000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1299000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1020000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1443000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1351000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1202000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1047000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1483000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1089000</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1132,13 +1145,14 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>8</v>
+      <c r="D12" s="3">
+        <v>106000</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>8</v>
@@ -1149,8 +1163,8 @@
       <c r="G12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H12" s="3" t="s">
-        <v>8</v>
+      <c r="H12" s="3">
+        <v>114000</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>8</v>
@@ -1233,8 +1247,11 @@
       <c r="AI12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1334,37 +1351,40 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>39000</v>
+        <v>-62000</v>
       </c>
       <c r="E14" s="3">
+        <v>105000</v>
+      </c>
+      <c r="F14" s="3">
         <v>94000</v>
       </c>
-      <c r="F14" s="3">
-        <v>155000</v>
-      </c>
       <c r="G14" s="3">
-        <v>581000</v>
+        <v>400000</v>
       </c>
       <c r="H14" s="3">
-        <v>491000</v>
+        <v>583000</v>
       </c>
       <c r="I14" s="3">
+        <v>469000</v>
+      </c>
+      <c r="J14" s="3">
         <v>114000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-14000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>66000</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>8</v>
@@ -1372,50 +1392,50 @@
       <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P14" s="3">
         <v>65000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>55000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>95000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>120000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>223000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>342000</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>52000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>10000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>-40000</v>
-      </c>
-      <c r="Y14" s="3">
-        <v>8000</v>
       </c>
       <c r="Z14" s="3">
         <v>8000</v>
       </c>
       <c r="AA14" s="3">
-        <v>14000</v>
+        <v>8000</v>
       </c>
       <c r="AB14" s="3">
         <v>14000</v>
       </c>
       <c r="AC14" s="3">
-        <v>0</v>
+        <v>14000</v>
       </c>
       <c r="AD14" s="3">
         <v>0</v>
@@ -1435,31 +1455,34 @@
       <c r="AI14" s="3">
         <v>0</v>
       </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>325000</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>341000</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>349000</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>373000</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>381000</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>309000</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>317000</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1536,8 +1559,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1570,210 +1596,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>13012000</v>
+        <v>13052000</v>
       </c>
       <c r="E17" s="3">
-        <v>12760000</v>
+        <v>12907000</v>
       </c>
       <c r="F17" s="3">
-        <v>13088000</v>
+        <v>12666000</v>
       </c>
       <c r="G17" s="3">
-        <v>13811000</v>
+        <v>12688000</v>
       </c>
       <c r="H17" s="3">
-        <v>13468000</v>
+        <v>13235000</v>
       </c>
       <c r="I17" s="3">
-        <v>13182000</v>
+        <v>12999000</v>
       </c>
       <c r="J17" s="3">
+        <v>13068000</v>
+      </c>
+      <c r="K17" s="3">
         <v>12793000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>12971000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>12462000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>11961000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>11478000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>10902000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>11416000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>10580000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>9755000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>10554000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>9247000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>10373000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>10057000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>10337000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>10049000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>9808000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>9386000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>9180000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>9254000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>9275000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>9307000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>9464000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>9153000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>8512000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>8200000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>8570000</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>341000</v>
+        <v>513000</v>
       </c>
       <c r="E18" s="3">
-        <v>312000</v>
+        <v>446000</v>
       </c>
       <c r="F18" s="3">
-        <v>231000</v>
+        <v>406000</v>
       </c>
       <c r="G18" s="3">
-        <v>-463000</v>
+        <v>631000</v>
       </c>
       <c r="H18" s="3">
-        <v>-328000</v>
+        <v>113000</v>
       </c>
       <c r="I18" s="3">
-        <v>-49000</v>
+        <v>141000</v>
       </c>
       <c r="J18" s="3">
+        <v>65000</v>
+      </c>
+      <c r="K18" s="3">
         <v>467000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>766000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1033000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1156000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1455000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1909000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1062000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>720000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>705000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>906000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>775000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>515000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>758000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>547000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>836000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>635000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>807000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>819000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>797000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>498000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>922000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>681000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>697000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>571000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>982000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>586000</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1809,513 +1842,529 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>47000</v>
+        <v>-1000</v>
       </c>
       <c r="E20" s="3">
-        <v>2000</v>
+        <v>-11000</v>
       </c>
       <c r="F20" s="3">
-        <v>35000</v>
+        <v>12000</v>
       </c>
       <c r="G20" s="3">
-        <v>0</v>
+        <v>-25000</v>
       </c>
       <c r="H20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I20" s="3">
+        <v>15000</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="K20" s="3">
+        <v>51000</v>
+      </c>
+      <c r="L20" s="3">
+        <v>-17000</v>
+      </c>
+      <c r="M20" s="3">
+        <v>38000</v>
+      </c>
+      <c r="N20" s="3">
+        <v>28000</v>
+      </c>
+      <c r="O20" s="3">
+        <v>55000</v>
+      </c>
+      <c r="P20" s="3">
+        <v>29000</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>9000</v>
+      </c>
+      <c r="R20" s="3">
+        <v>14000</v>
+      </c>
+      <c r="S20" s="3">
+        <v>21000</v>
+      </c>
+      <c r="T20" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="U20" s="3">
+        <v>14000</v>
+      </c>
+      <c r="V20" s="3">
+        <v>109000</v>
+      </c>
+      <c r="W20" s="3">
+        <v>19000</v>
+      </c>
+      <c r="X20" s="3">
+        <v>-15000</v>
+      </c>
+      <c r="Y20" s="3">
+        <v>9000</v>
+      </c>
+      <c r="Z20" s="3">
+        <v>12000</v>
+      </c>
+      <c r="AA20" s="3">
+        <v>5000</v>
+      </c>
+      <c r="AB20" s="3">
+        <v>25000</v>
+      </c>
+      <c r="AC20" s="3">
+        <v>13000</v>
+      </c>
+      <c r="AD20" s="3">
+        <v>9000</v>
+      </c>
+      <c r="AE20" s="3">
+        <v>6000</v>
+      </c>
+      <c r="AF20" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="AG20" s="3">
         <v>-9000</v>
       </c>
-      <c r="I20" s="3">
-        <v>8000</v>
-      </c>
-      <c r="J20" s="3">
-        <v>51000</v>
-      </c>
-      <c r="K20" s="3">
-        <v>-17000</v>
-      </c>
-      <c r="L20" s="3">
-        <v>38000</v>
-      </c>
-      <c r="M20" s="3">
-        <v>28000</v>
-      </c>
-      <c r="N20" s="3">
-        <v>55000</v>
-      </c>
-      <c r="O20" s="3">
-        <v>29000</v>
-      </c>
-      <c r="P20" s="3">
-        <v>9000</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>14000</v>
-      </c>
-      <c r="R20" s="3">
-        <v>21000</v>
-      </c>
-      <c r="S20" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="T20" s="3">
-        <v>14000</v>
-      </c>
-      <c r="U20" s="3">
-        <v>109000</v>
-      </c>
-      <c r="V20" s="3">
-        <v>19000</v>
-      </c>
-      <c r="W20" s="3">
-        <v>-15000</v>
-      </c>
-      <c r="X20" s="3">
-        <v>9000</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>12000</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>5000</v>
-      </c>
-      <c r="AA20" s="3">
-        <v>25000</v>
-      </c>
-      <c r="AB20" s="3">
-        <v>13000</v>
-      </c>
-      <c r="AC20" s="3">
-        <v>9000</v>
-      </c>
-      <c r="AD20" s="3">
-        <v>6000</v>
-      </c>
-      <c r="AE20" s="3">
-        <v>-7000</v>
-      </c>
-      <c r="AF20" s="3">
-        <v>-9000</v>
-      </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>4000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-12000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>748000</v>
+        <v>839000</v>
       </c>
       <c r="E21" s="3">
-        <v>663000</v>
+        <v>798000</v>
       </c>
       <c r="F21" s="3">
-        <v>639000</v>
+        <v>743000</v>
       </c>
       <c r="G21" s="3">
-        <v>-67000</v>
+        <v>1029000</v>
       </c>
       <c r="H21" s="3">
-        <v>-14000</v>
+        <v>493000</v>
       </c>
       <c r="I21" s="3">
-        <v>276000</v>
+        <v>435000</v>
       </c>
       <c r="J21" s="3">
+        <v>383000</v>
+      </c>
+      <c r="K21" s="3">
         <v>821000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1059000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1368000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1479000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1810000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2246000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1373000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1040000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1024000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1221000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1084000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>917000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1065000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>821000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1131000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>920000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1062000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1090000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1048000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>737000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1157000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>892000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>875000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>754000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1147000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>768000</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>130000</v>
+      </c>
+      <c r="E22" s="3">
         <v>135000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>111000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>105000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>93000</v>
-      </c>
-      <c r="H22" s="3">
-        <v>89000</v>
       </c>
       <c r="I22" s="3">
         <v>89000</v>
       </c>
       <c r="J22" s="3">
+        <v>89000</v>
+      </c>
+      <c r="K22" s="3">
         <v>84000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>83000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>85000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>97000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>100000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>103000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>105000</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>110000</v>
       </c>
       <c r="R22" s="3">
         <v>110000</v>
       </c>
       <c r="S22" s="3">
+        <v>110000</v>
+      </c>
+      <c r="T22" s="3">
         <v>124000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>122000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>119000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>120000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>123000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>121000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>119000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>99000</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>87000</v>
       </c>
       <c r="AB22" s="3">
         <v>87000</v>
       </c>
       <c r="AC22" s="3">
+        <v>87000</v>
+      </c>
+      <c r="AD22" s="3">
         <v>84000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>86000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>94000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>71000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>56000</v>
-      </c>
-      <c r="AH22" s="3">
-        <v>58000</v>
       </c>
       <c r="AI22" s="3">
         <v>58000</v>
       </c>
+      <c r="AJ22" s="3">
+        <v>58000</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>475000</v>
+      </c>
+      <c r="E23" s="3">
         <v>253000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>203000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>161000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-556000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-426000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-130000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>434000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>666000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>986000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1087000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1410000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1835000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>966000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>624000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>616000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>781000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>667000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>505000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>657000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>409000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>724000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>528000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>713000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>757000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>723000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>423000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>842000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>580000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>617000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>519000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>912000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>531000</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>111000</v>
+      </c>
+      <c r="E24" s="3">
         <v>57000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>55000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>47000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-113000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>9000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-39000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>114000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>129000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>233000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>254000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>284000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>477000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>213000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>147000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>144000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>165000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>140000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>126000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>148000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>79000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>43000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>98000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>161000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>220000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>182000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>116000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>204000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>185000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>169000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>178000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>318000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>139000</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2415,210 +2464,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>364000</v>
+      </c>
+      <c r="E26" s="3">
         <v>196000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>148000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>114000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-443000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-435000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-91000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>320000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>537000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>753000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>833000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1126000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1358000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>753000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>477000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>472000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>616000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>527000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>379000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>509000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>330000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>681000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>430000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>552000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>537000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>541000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>307000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>638000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>395000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>448000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>341000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>594000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>392000</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>357000</v>
+      </c>
+      <c r="E27" s="3">
         <v>191000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>145000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>107000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-450000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-417000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-97000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>316000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>538000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>750000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>829000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1121000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1355000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>749000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>476000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>467000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>613000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>527000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>376000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>505000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>327000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>676000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>426000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>551000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>537000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>540000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>306000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>637000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>394000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>447000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>340000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>593000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>391000</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2718,8 +2776,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2777,8 +2838,8 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>8</v>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>8</v>
@@ -2792,20 +2853,20 @@
       <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA29" s="3">
-        <v>0</v>
+      <c r="AA29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="3">
         <v>1000</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>9000</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>994000</v>
-      </c>
-      <c r="AE29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>8</v>
@@ -2819,8 +2880,11 @@
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2920,8 +2984,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3021,210 +3088,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-47000</v>
+        <v>1000</v>
       </c>
       <c r="E32" s="3">
-        <v>-2000</v>
+        <v>11000</v>
       </c>
       <c r="F32" s="3">
-        <v>-35000</v>
+        <v>-12000</v>
       </c>
       <c r="G32" s="3">
-        <v>0</v>
+        <v>25000</v>
       </c>
       <c r="H32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="I32" s="3">
+        <v>-15000</v>
+      </c>
+      <c r="J32" s="3">
+        <v>1000</v>
+      </c>
+      <c r="K32" s="3">
+        <v>-51000</v>
+      </c>
+      <c r="L32" s="3">
+        <v>17000</v>
+      </c>
+      <c r="M32" s="3">
+        <v>-38000</v>
+      </c>
+      <c r="N32" s="3">
+        <v>-28000</v>
+      </c>
+      <c r="O32" s="3">
+        <v>-55000</v>
+      </c>
+      <c r="P32" s="3">
+        <v>-29000</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="R32" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="S32" s="3">
+        <v>-21000</v>
+      </c>
+      <c r="T32" s="3">
+        <v>1000</v>
+      </c>
+      <c r="U32" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="V32" s="3">
+        <v>-109000</v>
+      </c>
+      <c r="W32" s="3">
+        <v>-19000</v>
+      </c>
+      <c r="X32" s="3">
+        <v>15000</v>
+      </c>
+      <c r="Y32" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="Z32" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="AA32" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="AB32" s="3">
+        <v>-25000</v>
+      </c>
+      <c r="AC32" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="AD32" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="AE32" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="AF32" s="3">
+        <v>7000</v>
+      </c>
+      <c r="AG32" s="3">
         <v>9000</v>
       </c>
-      <c r="I32" s="3">
-        <v>-8000</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-51000</v>
-      </c>
-      <c r="K32" s="3">
-        <v>17000</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-38000</v>
-      </c>
-      <c r="M32" s="3">
-        <v>-28000</v>
-      </c>
-      <c r="N32" s="3">
-        <v>-55000</v>
-      </c>
-      <c r="O32" s="3">
-        <v>-29000</v>
-      </c>
-      <c r="P32" s="3">
-        <v>-9000</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>-14000</v>
-      </c>
-      <c r="R32" s="3">
-        <v>-21000</v>
-      </c>
-      <c r="S32" s="3">
-        <v>1000</v>
-      </c>
-      <c r="T32" s="3">
-        <v>-14000</v>
-      </c>
-      <c r="U32" s="3">
-        <v>-109000</v>
-      </c>
-      <c r="V32" s="3">
-        <v>-19000</v>
-      </c>
-      <c r="W32" s="3">
-        <v>15000</v>
-      </c>
-      <c r="X32" s="3">
-        <v>-9000</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>-12000</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>-5000</v>
-      </c>
-      <c r="AA32" s="3">
-        <v>-25000</v>
-      </c>
-      <c r="AB32" s="3">
-        <v>-13000</v>
-      </c>
-      <c r="AC32" s="3">
-        <v>-9000</v>
-      </c>
-      <c r="AD32" s="3">
-        <v>-6000</v>
-      </c>
-      <c r="AE32" s="3">
-        <v>7000</v>
-      </c>
-      <c r="AF32" s="3">
-        <v>9000</v>
-      </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-4000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>12000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-3000</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>357000</v>
+      </c>
+      <c r="E33" s="3">
         <v>191000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>145000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>107000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-450000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-417000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-97000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>316000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>538000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>750000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>829000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1121000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1355000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>749000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>476000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>467000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>613000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>527000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>376000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>505000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>327000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>676000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>426000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>551000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>537000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>541000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>315000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1631000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>394000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>447000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>340000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>593000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>391000</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3324,215 +3400,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>357000</v>
+      </c>
+      <c r="E35" s="3">
         <v>191000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>145000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>107000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-450000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-417000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-97000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>316000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>538000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>750000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>829000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1121000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1355000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>749000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>476000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>467000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>613000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>527000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>376000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>505000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>327000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>676000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>426000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>551000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>537000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>541000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>315000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1631000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>394000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>447000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>340000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>593000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>391000</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45563</v>
+      </c>
+      <c r="E38" s="2">
         <v>45472</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45381</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45290</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45108</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45017</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44835</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44744</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44653</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44562</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44471</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44380</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44289</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44198</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44107</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44009</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43918</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43827</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43736</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43645</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43554</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43463</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43372</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43099</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42917</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42826</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3568,8 +3653,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3605,132 +3691,136 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1717000</v>
+      </c>
+      <c r="E41" s="3">
         <v>2569000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2182000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1484000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>573000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>699000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>543000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>654000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1031000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1056000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1151000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2956000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2507000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1613000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>877000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2406000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1420000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1365000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>437000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>497000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>484000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>406000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>360000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>400000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>270000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>170000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>198000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>293000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>318000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>231000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>243000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>307000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>349000</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>13000</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>16000</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I42" s="3">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -3807,435 +3897,450 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2406000</v>
+      </c>
+      <c r="E43" s="3">
         <v>2389000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2358000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2263000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2476000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2451000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2433000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2295000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2577000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2518000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2408000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2091000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2400000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2324000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2113000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1900000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1952000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2064000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2248000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2063000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>4346000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2452000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1837000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1892000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1723000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1684000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1594000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1600000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1675000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1710000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1589000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>1512000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>1542000</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>5195000</v>
+      </c>
+      <c r="E44" s="3">
         <v>5033000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>5056000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>5087000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>5328000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>5391000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>5504000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>5596000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>5514000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>5332000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>4990000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>4454000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>4382000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>4262000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>4128000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>3915000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>3859000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>3915000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>4025000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>4304000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>3929000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>4149000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>3899000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>3777000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>3513000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>3378000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>3328000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>3213000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>3239000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>3248000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>2970000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>2767000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>2732000</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>581000</v>
+        <v>423000</v>
       </c>
       <c r="E45" s="3">
-        <v>370000</v>
+        <v>568000</v>
       </c>
       <c r="F45" s="3">
-        <v>382000</v>
+        <v>354000</v>
       </c>
       <c r="G45" s="3">
-        <v>345000</v>
+        <v>367000</v>
       </c>
       <c r="H45" s="3">
-        <v>342000</v>
+        <v>330000</v>
       </c>
       <c r="I45" s="3">
-        <v>412000</v>
+        <v>335000</v>
       </c>
       <c r="J45" s="3">
+        <v>405000</v>
+      </c>
+      <c r="K45" s="3">
         <v>408000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>508000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>397000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>448000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>635000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>533000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1009000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>896000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>323000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>367000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>355000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>389000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>329000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>404000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>426000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>280000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>232000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>182000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>845000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>870000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>887000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1026000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1099000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>215000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>156000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>265000</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>9751000</v>
+      </c>
+      <c r="E46" s="3">
         <v>10572000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>9966000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>9216000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>8722000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>8883000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>8892000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>8953000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>9630000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>9303000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>8997000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>10136000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>9822000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>9208000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>8014000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>8544000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>7598000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>7699000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>7099000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>7193000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>6990000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>7433000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>6376000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>6301000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>5688000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>6077000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>5990000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>5993000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>6258000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>6288000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>5017000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>4742000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>4888000</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>0</v>
+        <v>103000</v>
       </c>
       <c r="E47" s="3">
-        <v>0</v>
+        <v>96000</v>
       </c>
       <c r="F47" s="3">
-        <v>0</v>
+        <v>92000</v>
       </c>
       <c r="G47" s="3">
-        <v>0</v>
+        <v>93000</v>
       </c>
       <c r="H47" s="3">
-        <v>0</v>
+        <v>89000</v>
       </c>
       <c r="I47" s="3">
-        <v>0</v>
+        <v>97000</v>
       </c>
       <c r="J47" s="3">
-        <v>0</v>
+        <v>97000</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -4312,210 +4417,219 @@
       <c r="AI47" s="3">
         <v>0</v>
       </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>10152000</v>
+      </c>
+      <c r="E48" s="3">
         <v>9368000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>9593000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>9672000</v>
       </c>
-      <c r="G48" s="3">
-        <v>9634000</v>
-      </c>
       <c r="H48" s="3">
+        <v>10178000</v>
+      </c>
+      <c r="I48" s="3">
         <v>9612000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>9351000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>9120000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>9192000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>8393000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>8193000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>8012000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>7837000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>7725000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>7661000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>7664000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>8128000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>8055000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>8005000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>7911000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>7282000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>7271000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>7085000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>7018000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>6169000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>5925000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>5755000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>5673000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>5568000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>5545000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>5283000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>5206000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>5170000</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>15694000</v>
+      </c>
+      <c r="E49" s="3">
         <v>15729000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>15863000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>15931000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>15976000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>16366000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>16707000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>16763000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>16765000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>16856000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>16945000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>17009000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>17068000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>17141000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>17204000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>17632000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>17673000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>17732000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>17745000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>17837000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>17881000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>18150000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>18241000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>18255000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>16498000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>15903000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>15635000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>15686000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>15567000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>15636000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>11705000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>11733000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>11753000</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4615,8 +4729,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4716,109 +4833,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>2063000</v>
+        <v>1400000</v>
       </c>
       <c r="E52" s="3">
-        <v>2043000</v>
+        <v>1967000</v>
       </c>
       <c r="F52" s="3">
-        <v>1927000</v>
+        <v>1951000</v>
       </c>
       <c r="G52" s="3">
-        <v>1919000</v>
+        <v>1834000</v>
       </c>
       <c r="H52" s="3">
-        <v>1900000</v>
+        <v>1286000</v>
       </c>
       <c r="I52" s="3">
-        <v>1846000</v>
+        <v>1803000</v>
       </c>
       <c r="J52" s="3">
+        <v>1749000</v>
+      </c>
+      <c r="K52" s="3">
         <v>1842000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1234000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1693000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1763000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1667000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1582000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1589000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1595000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1618000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1057000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1072000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1041000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>870000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>765000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>811000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>796000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>761000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>754000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>733000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>711000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>694000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>673000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>594000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>591000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>576000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>562000</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4918,109 +5041,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>37100000</v>
+      </c>
+      <c r="E54" s="3">
         <v>37732000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>37465000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>36746000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>36251000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>36761000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>36796000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>36678000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>36821000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>36245000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>35898000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>36824000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>36309000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>35663000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>34474000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>35458000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>34456000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>34558000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>33890000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>33811000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>32918000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>33665000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>32498000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>32335000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>29109000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>28638000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>28091000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>28046000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>28066000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>28063000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>22596000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>22257000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>22373000</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5056,8 +5185,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5093,614 +5223,633 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2402000</v>
+      </c>
+      <c r="E57" s="3">
         <v>2291000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2244000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2623000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2594000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2421000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2387000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2530000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2483000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2306000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2269000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2115000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2225000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1950000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1900000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1997000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1876000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1743000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1742000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1916000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1926000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1958000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1710000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1962000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1694000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1546000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1485000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1748000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1698000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1608000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1466000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1591000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1511000</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>247000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1320000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1315000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1308000</v>
       </c>
-      <c r="G58" s="3">
-        <v>1895000</v>
-      </c>
       <c r="H58" s="3">
+        <v>2048000</v>
+      </c>
+      <c r="I58" s="3">
         <v>457000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1065000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>490000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>459000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>67000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>79000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1090000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1067000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1566000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>580000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>566000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>548000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>750000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1142000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1947000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>2102000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>2125000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1564000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>3917000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1911000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1308000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1128000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>811000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>906000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1017000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>543000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>66000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>79000</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>2199000</v>
+        <v>1226000</v>
       </c>
       <c r="E59" s="3">
-        <v>2074000</v>
+        <v>1373000</v>
       </c>
       <c r="F59" s="3">
-        <v>2241000</v>
+        <v>1321000</v>
       </c>
       <c r="G59" s="3">
-        <v>2010000</v>
+        <v>1500000</v>
       </c>
       <c r="H59" s="3">
-        <v>2070000</v>
+        <v>1185000</v>
       </c>
       <c r="I59" s="3">
-        <v>1894000</v>
+        <v>1368000</v>
       </c>
       <c r="J59" s="3">
+        <v>1214000</v>
+      </c>
+      <c r="K59" s="3">
         <v>2094000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2371000</v>
-      </c>
-      <c r="L59" s="3">
-        <v>2309000</v>
       </c>
       <c r="M59" s="3">
         <v>2309000</v>
       </c>
       <c r="N59" s="3">
+        <v>2309000</v>
+      </c>
+      <c r="O59" s="3">
         <v>2829000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3033000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2668000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2132000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2286000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1810000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1780000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1522000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1673000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1485000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1514000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1340000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1551000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1426000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1258000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1225000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1419000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1428000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1240000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1097000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1315000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1172000</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4787000</v>
+      </c>
+      <c r="E60" s="3">
         <v>5810000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>5633000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>6172000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>6499000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>4948000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>5346000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>5114000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>5313000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4682000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>4657000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>6034000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>6325000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>6184000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>4612000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>4849000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>4234000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>4273000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>4406000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>5536000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>5513000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>5597000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>4614000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>7430000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>5031000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>4112000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>3838000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>3978000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>4032000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>3865000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>3106000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>2972000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>2762000</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>10234000</v>
+      </c>
+      <c r="E61" s="3">
         <v>9701000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>9645000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>8370000</v>
       </c>
-      <c r="G61" s="3">
-        <v>7611000</v>
-      </c>
       <c r="H61" s="3">
+        <v>7987000</v>
+      </c>
+      <c r="I61" s="3">
         <v>8863000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>7865000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>7859000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>7862000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>8261000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>8270000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>8274000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>8281000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>8786000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>9784000</v>
-      </c>
-      <c r="R61" s="3">
-        <v>10791000</v>
       </c>
       <c r="S61" s="3">
         <v>10791000</v>
       </c>
       <c r="T61" s="3">
+        <v>10791000</v>
+      </c>
+      <c r="U61" s="3">
         <v>11279000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>10978000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>9772000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>9830000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>10461000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>10810000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>8075000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>7962000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>8852000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>8872000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>8875000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>9297000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>9807000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>5905000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>5901000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>6200000</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>4019000</v>
+        <v>1100000</v>
       </c>
       <c r="E62" s="3">
-        <v>3964000</v>
+        <v>1701000</v>
       </c>
       <c r="F62" s="3">
-        <v>3916000</v>
+        <v>1672000</v>
       </c>
       <c r="G62" s="3">
-        <v>3886000</v>
+        <v>1614000</v>
       </c>
       <c r="H62" s="3">
-        <v>4040000</v>
+        <v>1009000</v>
       </c>
       <c r="I62" s="3">
-        <v>4027000</v>
+        <v>1599000</v>
       </c>
       <c r="J62" s="3">
+        <v>1589000</v>
+      </c>
+      <c r="K62" s="3">
         <v>3918000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3835000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3813000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3815000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3974000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3849000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>4000000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>4008000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>4037000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>4045000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>4002000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3912000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3937000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>3481000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>3466000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>3516000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>3571000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>3305000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>3237000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>3225000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>3219000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>4178000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>4254000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>3796000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>3817000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>3787000</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5800,8 +5949,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5901,8 +6053,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6002,109 +6157,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>19656000</v>
+        <v>18586000</v>
       </c>
       <c r="E66" s="3">
-        <v>19376000</v>
+        <v>19530000</v>
       </c>
       <c r="F66" s="3">
-        <v>18596000</v>
+        <v>19242000</v>
       </c>
       <c r="G66" s="3">
-        <v>18118000</v>
+        <v>18458000</v>
       </c>
       <c r="H66" s="3">
-        <v>17982000</v>
+        <v>17996000</v>
       </c>
       <c r="I66" s="3">
-        <v>17397000</v>
+        <v>17851000</v>
       </c>
       <c r="J66" s="3">
+        <v>17238000</v>
+      </c>
+      <c r="K66" s="3">
         <v>17043000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>17119000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>16890000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>16884000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>18421000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>18586000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>19102000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>18543000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>19820000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>19202000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>19700000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>19441000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>19392000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>18968000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>19737000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>19075000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>19208000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>16306000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>16212000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>15955000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>16091000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>17525000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>17946000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>12825000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>12707000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>12765000</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6140,8 +6301,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6241,8 +6403,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6342,8 +6507,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6443,8 +6611,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6544,109 +6715,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>18873000</v>
+      </c>
+      <c r="E72" s="3">
         <v>18687000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>18667000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>18693000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>18760000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>19378000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>19962000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>20225000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>20084000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>19708000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>19119000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>18453000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>17502000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>16305000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>15716000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>15399000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>15100000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>14769000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>14392000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>14178000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>13655000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>13553000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>13012000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>12719000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>12329000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>11913000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>11479000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>11272000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>9776000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>9464000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>9098000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>8837000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>8348000</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6746,8 +6923,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6847,8 +7027,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6948,109 +7131,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>18390000</v>
+      </c>
+      <c r="E76" s="3">
         <v>18076000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>18089000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>18150000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>18133000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>18779000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>19399000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>19635000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>19702000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>19355000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>19014000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>18403000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>17723000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>16561000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>15931000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>15638000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>15254000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>14858000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>14449000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>14419000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>13950000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>13928000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>13423000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>13127000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>12803000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>12426000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>12136000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>11955000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>10541000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>10117000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>9771000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>9550000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>9608000</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7150,215 +7339,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45563</v>
+      </c>
+      <c r="E80" s="2">
         <v>45472</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45381</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45290</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45108</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45017</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44835</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44744</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44653</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44562</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44471</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44380</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44289</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44198</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44107</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44009</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43918</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43827</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43736</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43645</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43554</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43463</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43372</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43099</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42917</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42826</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>357000</v>
+      </c>
+      <c r="E81" s="3">
         <v>191000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>145000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>107000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-450000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-417000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-97000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>316000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>538000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>750000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>829000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1121000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1355000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>749000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>476000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>467000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>613000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>527000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>376000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>505000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>327000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>676000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>426000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>551000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>537000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>541000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>315000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1631000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>394000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>447000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>340000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>593000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>391000</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7394,109 +7592,113 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>360000</v>
+        <v>152000</v>
       </c>
       <c r="E83" s="3">
-        <v>349000</v>
+        <v>309000</v>
       </c>
       <c r="F83" s="3">
-        <v>373000</v>
+        <v>317000</v>
       </c>
       <c r="G83" s="3">
-        <v>396000</v>
+        <v>303000</v>
       </c>
       <c r="H83" s="3">
-        <v>323000</v>
+        <v>246000</v>
       </c>
       <c r="I83" s="3">
-        <v>317000</v>
+        <v>233000</v>
       </c>
       <c r="J83" s="3">
+        <v>230000</v>
+      </c>
+      <c r="K83" s="3">
         <v>303000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>310000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>297000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>295000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>300000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>308000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>302000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>306000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>298000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>316000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>295000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>293000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>288000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>289000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>286000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>273000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>250000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>246000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>238000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>230000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>229000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>218000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>187000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>179000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>177000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>179000</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7596,8 +7798,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7697,8 +7902,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7798,8 +8006,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7899,8 +8110,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8000,109 +8214,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>617000</v>
+      </c>
+      <c r="E89" s="3">
         <v>796000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-123000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1300000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>323000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>660000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>7000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>762000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>797000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>666000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-208000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1432000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1184000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1307000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-36000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1385000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1166000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1448000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>366000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>894000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>978000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>596000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>71000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>868000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1039000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>785000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>13000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1126000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1150000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>467000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-152000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1134000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>843000</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8138,109 +8358,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-248000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-263000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-267000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-354000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-375000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-467000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-508000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-589000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-564000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-476000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-439000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-408000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-350000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-302000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-268000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-289000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-292000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-283000</v>
-      </c>
-      <c r="U91" s="3">
-        <v>-312000</v>
       </c>
       <c r="V91" s="3">
         <v>-312000</v>
       </c>
       <c r="W91" s="3">
+        <v>-312000</v>
+      </c>
+      <c r="X91" s="3">
         <v>-288000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-315000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-338000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-318000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-313000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-328000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-263000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-296000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-287000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-315000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-267000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-200000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-180000</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8340,8 +8564,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8441,109 +8668,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-34000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-233000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-243000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-378000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-427000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-696000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-507000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-669000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-610000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-440000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-426000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-459000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>841000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-275000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-249000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-259000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-280000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-266000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-496000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-381000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-129000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-569000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-317000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-2449000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-483000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-737000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-264000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-422000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-297000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-3389000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-264000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-214000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-182000</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8579,46 +8812,47 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-171000</v>
+        <v>171000</v>
       </c>
       <c r="E96" s="3">
-        <v>-171000</v>
+        <v>171000</v>
       </c>
       <c r="F96" s="3">
-        <v>-171000</v>
+        <v>171000</v>
       </c>
       <c r="G96" s="3">
-        <v>-167000</v>
+        <v>171000</v>
       </c>
       <c r="H96" s="3">
-        <v>-167000</v>
+        <v>167000</v>
       </c>
       <c r="I96" s="3">
-        <v>-167000</v>
+        <v>167000</v>
       </c>
       <c r="J96" s="3">
+        <v>167000</v>
+      </c>
+      <c r="K96" s="3">
         <v>-169000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-162000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-163000</v>
-      </c>
-      <c r="M96" s="3">
-        <v>-164000</v>
       </c>
       <c r="N96" s="3">
         <v>-164000</v>
       </c>
       <c r="O96" s="3">
-        <v>-159000</v>
+        <v>-164000</v>
       </c>
       <c r="P96" s="3">
         <v>-159000</v>
@@ -8630,34 +8864,34 @@
         <v>-159000</v>
       </c>
       <c r="S96" s="3">
-        <v>-150000</v>
+        <v>-159000</v>
       </c>
       <c r="T96" s="3">
         <v>-150000</v>
       </c>
       <c r="U96" s="3">
+        <v>-150000</v>
+      </c>
+      <c r="V96" s="3">
         <v>-151000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-150000</v>
-      </c>
-      <c r="W96" s="3">
-        <v>-134000</v>
       </c>
       <c r="X96" s="3">
         <v>-134000</v>
       </c>
       <c r="Y96" s="3">
+        <v>-134000</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-135000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-134000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-107000</v>
-      </c>
-      <c r="AB96" s="3">
-        <v>-108000</v>
       </c>
       <c r="AC96" s="3">
         <v>-108000</v>
@@ -8666,22 +8900,25 @@
         <v>-108000</v>
       </c>
       <c r="AE96" s="3">
+        <v>-108000</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-81000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-80000</v>
-      </c>
-      <c r="AG96" s="3">
-        <v>-79000</v>
       </c>
       <c r="AH96" s="3">
         <v>-79000</v>
       </c>
       <c r="AI96" s="3">
+        <v>-79000</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-54000</v>
       </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8781,8 +9018,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8882,8 +9122,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8983,307 +9226,319 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1464000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-168000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1077000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-26000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-13000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>202000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>381000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-482000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-195000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-361000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1283000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-484000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1189000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-197000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1172000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-173000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-874000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-255000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>168000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-507000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-761000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>20000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>201000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>1711000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-455000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-71000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>153000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-729000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-769000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>2908000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>348000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-957000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-510000</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-8000</v>
+        <v>-9000</v>
       </c>
       <c r="E101" s="3">
-        <v>-13000</v>
+        <v>-10000</v>
       </c>
       <c r="F101" s="3">
-        <v>15000</v>
+        <v>8000</v>
       </c>
       <c r="G101" s="3">
-        <v>-9000</v>
+        <v>12000</v>
       </c>
       <c r="H101" s="3">
+        <v>-17000</v>
+      </c>
+      <c r="I101" s="3">
+        <v>-24000</v>
+      </c>
+      <c r="J101" s="3">
+        <v>4000</v>
+      </c>
+      <c r="K101" s="3">
+        <v>12000</v>
+      </c>
+      <c r="L101" s="3">
+        <v>-17000</v>
+      </c>
+      <c r="M101" s="3">
+        <v>-24000</v>
+      </c>
+      <c r="N101" s="3">
+        <v>4000</v>
+      </c>
+      <c r="O101" s="3">
+        <v>2000</v>
+      </c>
+      <c r="P101" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>1000</v>
+      </c>
+      <c r="R101" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="S101" s="3">
+        <v>16000</v>
+      </c>
+      <c r="T101" s="3">
+        <v>7000</v>
+      </c>
+      <c r="U101" s="3">
+        <v>1000</v>
+      </c>
+      <c r="V101" s="3">
+        <v>-16000</v>
+      </c>
+      <c r="W101" s="3">
+        <v>7000</v>
+      </c>
+      <c r="X101" s="3">
         <v>-10000</v>
       </c>
-      <c r="I101" s="3">
-        <v>8000</v>
-      </c>
-      <c r="J101" s="3">
-        <v>12000</v>
-      </c>
-      <c r="K101" s="3">
-        <v>-17000</v>
-      </c>
-      <c r="L101" s="3">
-        <v>-24000</v>
-      </c>
-      <c r="M101" s="3">
+      <c r="Y101" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="Z101" s="3">
+        <v>5000</v>
+      </c>
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB101" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AC101" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="AD101" s="3">
+        <v>3000</v>
+      </c>
+      <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF101" s="3">
+        <v>3000</v>
+      </c>
+      <c r="AG101" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AH101" s="3">
         <v>4000</v>
       </c>
-      <c r="N101" s="3">
-        <v>2000</v>
-      </c>
-      <c r="O101" s="3">
-        <v>-7000</v>
-      </c>
-      <c r="P101" s="3">
+      <c r="AI101" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="AJ101" s="3">
         <v>1000</v>
       </c>
-      <c r="Q101" s="3">
-        <v>-6000</v>
-      </c>
-      <c r="R101" s="3">
-        <v>16000</v>
-      </c>
-      <c r="S101" s="3">
-        <v>7000</v>
-      </c>
-      <c r="T101" s="3">
-        <v>1000</v>
-      </c>
-      <c r="U101" s="3">
-        <v>-16000</v>
-      </c>
-      <c r="V101" s="3">
-        <v>7000</v>
-      </c>
-      <c r="W101" s="3">
-        <v>-10000</v>
-      </c>
-      <c r="X101" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="Y101" s="3">
-        <v>5000</v>
-      </c>
-      <c r="Z101" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA101" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="AB101" s="3">
-        <v>-5000</v>
-      </c>
-      <c r="AC101" s="3">
-        <v>3000</v>
-      </c>
-      <c r="AD101" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE101" s="3">
-        <v>3000</v>
-      </c>
-      <c r="AF101" s="3">
-        <v>2000</v>
-      </c>
-      <c r="AG101" s="3">
-        <v>4000</v>
-      </c>
-      <c r="AH101" s="3">
-        <v>-5000</v>
-      </c>
-      <c r="AI101" s="3">
-        <v>1000</v>
-      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-852000</v>
+      </c>
+      <c r="E102" s="3">
         <v>387000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>698000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>911000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-126000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>156000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-111000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-377000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-25000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-159000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1913000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>491000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>829000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>836000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1463000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>969000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>19000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>928000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>22000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>13000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>78000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>46000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-40000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>130000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>100000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-28000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-95000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-25000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>87000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-12000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-64000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-42000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>152000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TSN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TSN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="92">
   <si>
     <t>TSN</t>
   </si>
@@ -656,460 +656,472 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45654</v>
+      </c>
+      <c r="E7" s="2">
         <v>45563</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45472</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45381</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45290</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45108</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45017</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44835</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44744</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44653</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44562</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44471</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44380</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44289</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44198</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44107</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44009</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43918</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43827</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43736</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43645</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43554</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43463</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43372</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43099</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42917</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42826</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>13623000</v>
+      </c>
+      <c r="E8" s="3">
         <v>13565000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>13353000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>13072000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>13319000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>13348000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>13140000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>13133000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>13260000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>13737000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>13495000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>13117000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>12933000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>12811000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>12478000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>11300000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>10460000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>11460000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>10022000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>10888000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>10815000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>10884000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>10885000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>10443000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>10193000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>9999000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>10051000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>9773000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>10229000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>10145000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>9850000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>9083000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>9182000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>9156000</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>12526000</v>
+        <v>12431000</v>
       </c>
       <c r="E9" s="3">
-        <v>12370000</v>
+        <v>12571000</v>
       </c>
       <c r="F9" s="3">
+        <v>12325000</v>
+      </c>
+      <c r="G9" s="3">
         <v>12116000</v>
       </c>
-      <c r="G9" s="3">
-        <v>12293000</v>
-      </c>
       <c r="H9" s="3">
+        <v>12371000</v>
+      </c>
+      <c r="I9" s="3">
         <v>12664000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>12451000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>12518000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>12319000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>12412000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>11884000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>11382000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>10918000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>10270000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>10803000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>9952000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>9163000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>9653000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>8394000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>9966000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>9337000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>19490000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>9549000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>9251000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>8838000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>8660000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>8752000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>8753000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>8786000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>8794000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>8648000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>8036000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>7699000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>8067000</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>1039000</v>
+        <v>1192000</v>
       </c>
       <c r="E10" s="3">
-        <v>983000</v>
+        <v>994000</v>
       </c>
       <c r="F10" s="3">
+        <v>1028000</v>
+      </c>
+      <c r="G10" s="3">
         <v>956000</v>
       </c>
-      <c r="G10" s="3">
-        <v>1026000</v>
-      </c>
       <c r="H10" s="3">
+        <v>948000</v>
+      </c>
+      <c r="I10" s="3">
         <v>684000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>689000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>615000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>941000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1325000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1611000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1735000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2015000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2541000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1675000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1348000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1297000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1807000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1628000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>922000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1478000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>-8606000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1336000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1192000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1355000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1339000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1299000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1020000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1443000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1351000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1202000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1047000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1483000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1089000</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1146,16 +1158,17 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="3">
         <v>106000</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>8</v>
@@ -1163,11 +1176,11 @@
       <c r="G12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I12" s="3">
         <v>114000</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>8</v>
@@ -1250,8 +1263,11 @@
       <c r="AJ12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1354,40 +1370,43 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-62000</v>
+        <v>100000</v>
       </c>
       <c r="E14" s="3">
-        <v>105000</v>
+        <v>-107000</v>
       </c>
       <c r="F14" s="3">
+        <v>150000</v>
+      </c>
+      <c r="G14" s="3">
         <v>94000</v>
       </c>
-      <c r="G14" s="3">
-        <v>400000</v>
-      </c>
       <c r="H14" s="3">
+        <v>145000</v>
+      </c>
+      <c r="I14" s="3">
         <v>583000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>469000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>114000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-14000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>66000</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>8</v>
@@ -1395,50 +1414,50 @@
       <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="3">
         <v>65000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>55000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>95000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>120000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>223000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>342000</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
       <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>52000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>10000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>-40000</v>
-      </c>
-      <c r="Z14" s="3">
-        <v>8000</v>
       </c>
       <c r="AA14" s="3">
         <v>8000</v>
       </c>
       <c r="AB14" s="3">
-        <v>14000</v>
+        <v>8000</v>
       </c>
       <c r="AC14" s="3">
         <v>14000</v>
       </c>
       <c r="AD14" s="3">
-        <v>0</v>
+        <v>14000</v>
       </c>
       <c r="AE14" s="3">
         <v>0</v>
@@ -1458,8 +1477,11 @@
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1467,26 +1489,26 @@
         <v>325000</v>
       </c>
       <c r="E15" s="3">
+        <v>325000</v>
+      </c>
+      <c r="F15" s="3">
         <v>341000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>349000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>373000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>381000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>309000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>317000</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1562,8 +1584,11 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1597,216 +1622,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>13052000</v>
+        <v>12936000</v>
       </c>
       <c r="E17" s="3">
-        <v>12907000</v>
+        <v>13097000</v>
       </c>
       <c r="F17" s="3">
+        <v>12862000</v>
+      </c>
+      <c r="G17" s="3">
         <v>12666000</v>
       </c>
-      <c r="G17" s="3">
-        <v>12688000</v>
-      </c>
       <c r="H17" s="3">
+        <v>12933000</v>
+      </c>
+      <c r="I17" s="3">
         <v>13235000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>12999000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>13068000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>12793000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>12971000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>12462000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>11961000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>11478000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>10902000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>11416000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>10580000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>9755000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>10554000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>9247000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>10373000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>10057000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>10337000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>10049000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>9808000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>9386000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>9180000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>9254000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>9275000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>9307000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>9464000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>9153000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>8512000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>8200000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>8570000</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>513000</v>
+        <v>687000</v>
       </c>
       <c r="E18" s="3">
-        <v>446000</v>
+        <v>468000</v>
       </c>
       <c r="F18" s="3">
+        <v>491000</v>
+      </c>
+      <c r="G18" s="3">
         <v>406000</v>
       </c>
-      <c r="G18" s="3">
-        <v>631000</v>
-      </c>
       <c r="H18" s="3">
+        <v>386000</v>
+      </c>
+      <c r="I18" s="3">
         <v>113000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>141000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>65000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>467000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>766000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1033000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1156000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1455000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1909000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1062000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>720000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>705000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>906000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>775000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>515000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>758000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>547000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>836000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>635000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>807000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>819000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>797000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>498000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>922000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>681000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>697000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>571000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>982000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>586000</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1843,528 +1875,544 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-11000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>12000</v>
       </c>
-      <c r="G20" s="3">
-        <v>-25000</v>
-      </c>
       <c r="H20" s="3">
+        <v>-15000</v>
+      </c>
+      <c r="I20" s="3">
         <v>1000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>15000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>51000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-17000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>38000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>28000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>55000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>29000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>9000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>14000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>21000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-1000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>14000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>109000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>19000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-15000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>9000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>12000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>5000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>25000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>13000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>9000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>6000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-7000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-9000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>4000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-12000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>839000</v>
+        <v>998000</v>
       </c>
       <c r="E21" s="3">
-        <v>798000</v>
+        <v>794000</v>
       </c>
       <c r="F21" s="3">
+        <v>843000</v>
+      </c>
+      <c r="G21" s="3">
         <v>743000</v>
       </c>
-      <c r="G21" s="3">
-        <v>1029000</v>
-      </c>
       <c r="H21" s="3">
+        <v>774000</v>
+      </c>
+      <c r="I21" s="3">
         <v>493000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>435000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>383000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>821000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1059000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1368000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1479000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1810000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2246000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1373000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1040000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1024000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1221000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1084000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>917000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1065000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>821000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1131000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>920000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1062000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1090000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1048000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>737000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1157000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>892000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>875000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>754000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1147000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>768000</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>120000</v>
+      </c>
+      <c r="E22" s="3">
         <v>130000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>135000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>111000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>105000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>93000</v>
-      </c>
-      <c r="I22" s="3">
-        <v>89000</v>
       </c>
       <c r="J22" s="3">
         <v>89000</v>
       </c>
       <c r="K22" s="3">
+        <v>89000</v>
+      </c>
+      <c r="L22" s="3">
         <v>84000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>83000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>85000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>97000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>100000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>103000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>105000</v>
-      </c>
-      <c r="R22" s="3">
-        <v>110000</v>
       </c>
       <c r="S22" s="3">
         <v>110000</v>
       </c>
       <c r="T22" s="3">
+        <v>110000</v>
+      </c>
+      <c r="U22" s="3">
         <v>124000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>122000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>119000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>120000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>123000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>121000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>119000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>99000</v>
-      </c>
-      <c r="AB22" s="3">
-        <v>87000</v>
       </c>
       <c r="AC22" s="3">
         <v>87000</v>
       </c>
       <c r="AD22" s="3">
+        <v>87000</v>
+      </c>
+      <c r="AE22" s="3">
         <v>84000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>86000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>94000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>71000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>56000</v>
-      </c>
-      <c r="AI22" s="3">
-        <v>58000</v>
       </c>
       <c r="AJ22" s="3">
         <v>58000</v>
       </c>
+      <c r="AK22" s="3">
+        <v>58000</v>
+      </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>478000</v>
+      </c>
+      <c r="E23" s="3">
         <v>475000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>253000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>203000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>161000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-556000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-426000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-130000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>434000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>666000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>986000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1087000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1410000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1835000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>966000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>624000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>616000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>781000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>667000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>505000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>657000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>409000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>724000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>528000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>713000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>757000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>723000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>423000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>842000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>580000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>617000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>519000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>912000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>531000</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>112000</v>
+      </c>
+      <c r="E24" s="3">
         <v>111000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>57000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>55000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>47000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-113000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>9000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-39000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>114000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>129000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>233000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>254000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>284000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>477000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>213000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>147000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>144000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>165000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>140000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>126000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>148000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>79000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>43000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>98000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>161000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>220000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>182000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>116000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>204000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>185000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>169000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>178000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>318000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>139000</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2467,216 +2515,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>366000</v>
+      </c>
+      <c r="E26" s="3">
         <v>364000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>196000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>148000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>114000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-443000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-435000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-91000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>320000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>537000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>753000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>833000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1126000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1358000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>753000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>477000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>472000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>616000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>527000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>379000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>509000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>330000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>681000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>430000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>552000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>537000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>541000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>307000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>638000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>395000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>448000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>341000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>594000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>392000</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>359000</v>
+      </c>
+      <c r="E27" s="3">
         <v>357000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>191000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>145000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>107000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-450000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-417000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-97000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>316000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>538000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>750000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>829000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1121000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1355000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>749000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>476000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>467000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>613000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>527000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>376000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>505000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>327000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>676000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>426000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>551000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>537000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>540000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>306000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>637000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>394000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>447000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>340000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>593000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>391000</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2779,8 +2836,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2841,8 +2901,8 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>8</v>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>8</v>
@@ -2856,20 +2916,20 @@
       <c r="AA29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB29" s="3">
-        <v>0</v>
+      <c r="AB29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="3">
         <v>1000</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>9000</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>994000</v>
-      </c>
-      <c r="AF29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AG29" s="3" t="s">
         <v>8</v>
@@ -2883,8 +2943,11 @@
       <c r="AJ29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2987,8 +3050,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3091,216 +3157,225 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="E32" s="3">
         <v>1000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>11000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-12000</v>
       </c>
-      <c r="G32" s="3">
-        <v>25000</v>
-      </c>
       <c r="H32" s="3">
+        <v>15000</v>
+      </c>
+      <c r="I32" s="3">
         <v>-1000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-15000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-51000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>17000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-38000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-28000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-55000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-29000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-9000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-14000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-21000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>1000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-14000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-109000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-19000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>15000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-9000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-12000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-5000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-25000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-13000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-9000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-6000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>7000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>9000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-4000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>12000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-3000</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>359000</v>
+      </c>
+      <c r="E33" s="3">
         <v>357000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>191000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>145000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>107000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-450000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-417000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-97000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>316000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>538000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>750000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>829000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1121000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1355000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>749000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>476000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>467000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>613000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>527000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>376000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>505000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>327000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>676000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>426000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>551000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>537000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>541000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>315000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1631000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>394000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>447000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>340000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>593000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>391000</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3403,221 +3478,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>359000</v>
+      </c>
+      <c r="E35" s="3">
         <v>357000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>191000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>145000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>107000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-450000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-417000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-97000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>316000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>538000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>750000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>829000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1121000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1355000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>749000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>476000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>467000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>613000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>527000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>376000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>505000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>327000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>676000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>426000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>551000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>537000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>541000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>315000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1631000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>394000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>447000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>340000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>593000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>391000</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45654</v>
+      </c>
+      <c r="E38" s="2">
         <v>45563</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45472</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45381</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45290</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45108</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45017</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44835</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44744</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44653</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44562</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44471</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44380</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44289</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44198</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44107</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44009</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43918</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43827</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43736</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43645</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43554</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43463</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43372</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43099</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42917</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42826</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3654,8 +3738,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3692,138 +3777,142 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2292000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1717000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2569000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2182000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1484000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>573000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>699000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>543000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>654000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1031000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1056000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1151000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2956000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2507000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1613000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>877000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2406000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1420000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1365000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>437000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>497000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>484000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>406000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>360000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>400000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>270000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>170000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>198000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>293000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>318000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>231000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>243000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>307000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>349000</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E42" s="3">
         <v>10000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>13000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>16000</v>
-      </c>
-      <c r="G42" s="3">
-        <v>15000</v>
       </c>
       <c r="H42" s="3">
         <v>15000</v>
       </c>
       <c r="I42" s="3">
-        <v>7000</v>
+        <v>15000</v>
       </c>
       <c r="J42" s="3">
         <v>7000</v>
       </c>
       <c r="K42" s="3">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="L42" s="3">
         <v>0</v>
@@ -3900,450 +3989,465 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2323000</v>
+      </c>
+      <c r="E43" s="3">
         <v>2406000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2389000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2358000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2263000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2476000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2451000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2433000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2295000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2577000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2518000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2408000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2091000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2400000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2324000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2113000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1900000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1952000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2064000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2248000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2063000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>4346000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2452000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1837000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1892000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1723000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1684000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1594000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1600000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1675000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1710000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>1589000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>1512000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>1542000</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>5114000</v>
+      </c>
+      <c r="E44" s="3">
         <v>5195000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>5033000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>5056000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>5087000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>5328000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>5391000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>5504000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>5596000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>5514000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>5332000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>4990000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>4454000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>4382000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>4262000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>4128000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>3915000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>3859000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>3915000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>4025000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>4304000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>3929000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>4149000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>3899000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>3777000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>3513000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>3378000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>3328000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>3213000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>3239000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>3248000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>2970000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>2767000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>2732000</v>
       </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>352000</v>
+      </c>
+      <c r="E45" s="3">
         <v>423000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>568000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>354000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>367000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>330000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>335000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>405000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>408000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>508000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>397000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>448000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>635000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>533000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1009000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>896000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>323000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>367000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>355000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>389000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>329000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>404000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>426000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>280000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>232000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>182000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>845000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>870000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>887000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1026000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1099000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>215000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>156000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>265000</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>10082000</v>
+      </c>
+      <c r="E46" s="3">
         <v>9751000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>10572000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>9966000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>9216000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>8722000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>8883000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>8892000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>8953000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>9630000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>9303000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>8997000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>10136000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>9822000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>9208000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>8014000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>8544000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>7598000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>7699000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>7099000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>7193000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>6990000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>7433000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>6376000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>6301000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>5688000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>6077000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>5990000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>5993000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>6258000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>6288000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>5017000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>4742000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>4888000</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>109000</v>
+      </c>
+      <c r="E47" s="3">
         <v>103000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>96000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>92000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>93000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>89000</v>
-      </c>
-      <c r="I47" s="3">
-        <v>97000</v>
       </c>
       <c r="J47" s="3">
         <v>97000</v>
       </c>
       <c r="K47" s="3">
-        <v>0</v>
+        <v>97000</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -4420,216 +4524,225 @@
       <c r="AJ47" s="3">
         <v>0</v>
       </c>
+      <c r="AK47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>9353000</v>
+      </c>
+      <c r="E48" s="3">
         <v>10152000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>9368000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>9593000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>9672000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>10178000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>9612000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>9351000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>9120000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>9192000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>8393000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>8193000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>8012000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>7837000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>7725000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>7661000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>7664000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>8128000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>8055000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>8005000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>7911000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>7282000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>7271000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>7085000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>7018000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>6169000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>5925000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>5755000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>5673000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>5568000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>5545000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>5283000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>5206000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>5170000</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>15604000</v>
+      </c>
+      <c r="E49" s="3">
         <v>15694000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>15729000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>15863000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>15931000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>15976000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>16366000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>16707000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>16763000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>16765000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>16856000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>16945000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>17009000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>17068000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>17141000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>17204000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>17632000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>17673000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>17732000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>17745000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>17837000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>17881000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>18150000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>18241000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>18255000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>16498000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>15903000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>15635000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>15686000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>15567000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>15636000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>11705000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>11733000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>11753000</v>
       </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4732,8 +4845,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4836,112 +4952,118 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2162000</v>
+      </c>
+      <c r="E52" s="3">
         <v>1400000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1967000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1951000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1834000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1286000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1803000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1749000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1842000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1234000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1693000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1763000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1667000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1582000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1589000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1595000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1618000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1057000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1072000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1041000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>870000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>765000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>811000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>796000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>761000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>754000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>733000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>711000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>694000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>673000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>594000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>591000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>576000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>562000</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5044,112 +5166,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>37310000</v>
+      </c>
+      <c r="E54" s="3">
         <v>37100000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>37732000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>37465000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>36746000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>36251000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>36761000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>36796000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>36678000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>36821000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>36245000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>35898000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>36824000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>36309000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>35663000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>34474000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>35458000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>34456000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>34558000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>33890000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>33811000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>32918000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>33665000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>32498000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>32335000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>29109000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>28638000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>28091000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>28046000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>28066000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>28063000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>22596000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>22257000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>22373000</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5186,8 +5314,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5224,632 +5353,651 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2497000</v>
+      </c>
+      <c r="E57" s="3">
         <v>2402000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2291000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2244000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2623000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2594000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2421000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2387000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2530000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2483000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2306000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2269000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2115000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2225000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1950000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1900000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1997000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1876000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1743000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1742000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1916000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1926000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1958000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1710000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1962000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1694000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1546000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1485000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1748000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1698000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1608000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1466000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1591000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>1511000</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>95000</v>
+      </c>
+      <c r="E58" s="3">
         <v>247000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1320000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1315000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1308000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2048000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>457000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1065000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>490000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>459000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>67000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>79000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1090000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1067000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1566000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>580000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>566000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>548000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>750000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1142000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1947000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>2102000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>2125000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1564000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>3917000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1911000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1308000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1128000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>811000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>906000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1017000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>543000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>66000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>79000</v>
       </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1534000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1226000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1373000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1321000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1500000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1185000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1368000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1214000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2094000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2371000</v>
-      </c>
-      <c r="M59" s="3">
-        <v>2309000</v>
       </c>
       <c r="N59" s="3">
         <v>2309000</v>
       </c>
       <c r="O59" s="3">
+        <v>2309000</v>
+      </c>
+      <c r="P59" s="3">
         <v>2829000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3033000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2668000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2132000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2286000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1810000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1780000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1522000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1673000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1485000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1514000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1340000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1551000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1426000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1258000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1225000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1419000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1428000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1240000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1097000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1315000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>1172000</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4780000</v>
+      </c>
+      <c r="E60" s="3">
         <v>4787000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>5810000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>5633000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>6172000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>6499000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>4948000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>5346000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>5114000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>5313000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>4682000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>4657000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>6034000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>6325000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>6184000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>4612000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>4849000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>4234000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>4273000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>4406000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>5536000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>5513000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>5597000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>4614000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>7430000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>5031000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>4112000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>3838000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>3978000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>4032000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>3865000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>3106000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>2972000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>2762000</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>9711000</v>
+      </c>
+      <c r="E61" s="3">
         <v>10234000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>9701000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>9645000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>8370000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>7987000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>8863000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>7865000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>7859000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>7862000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>8261000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>8270000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>8274000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>8281000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>8786000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>9784000</v>
-      </c>
-      <c r="S61" s="3">
-        <v>10791000</v>
       </c>
       <c r="T61" s="3">
         <v>10791000</v>
       </c>
       <c r="U61" s="3">
+        <v>10791000</v>
+      </c>
+      <c r="V61" s="3">
         <v>11279000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>10978000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>9772000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>9830000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>10461000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>10810000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>8075000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>7962000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>8852000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>8872000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>8875000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>9297000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>9807000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>5905000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>5901000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>6200000</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1909000</v>
+      </c>
+      <c r="E62" s="3">
         <v>1100000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1701000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1672000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1614000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1009000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1599000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1589000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3918000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3835000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3813000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3815000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3974000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3849000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>4000000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>4008000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>4037000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>4045000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>4002000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3912000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>3937000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>3481000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>3466000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>3516000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>3571000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>3305000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>3237000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>3225000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>3219000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>4178000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>4254000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>3796000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>3817000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>3787000</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5952,8 +6100,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6056,8 +6207,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6160,112 +6314,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>18683000</v>
+      </c>
+      <c r="E66" s="3">
         <v>18586000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>19530000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>19242000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>18458000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>17996000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>17851000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>17238000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>17043000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>17119000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>16890000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>16884000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>18421000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>18586000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>19102000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>18543000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>19820000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>19202000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>19700000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>19441000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>19392000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>18968000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>19737000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>19075000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>19208000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>16306000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>16212000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>15955000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>16091000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>17525000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>17946000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>12825000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>12707000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>12765000</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6302,8 +6462,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6406,8 +6567,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6510,8 +6674,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6614,8 +6781,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6718,112 +6888,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>19054000</v>
+      </c>
+      <c r="E72" s="3">
         <v>18873000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>18687000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>18667000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>18693000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>18760000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>19378000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>19962000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>20225000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>20084000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>19708000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>19119000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>18453000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>17502000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>16305000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>15716000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>15399000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>15100000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>14769000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>14392000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>14178000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>13655000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>13553000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>13012000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>12719000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>12329000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>11913000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>11479000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>11272000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>9776000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>9464000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>9098000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>8837000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>8348000</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6926,8 +7102,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7030,8 +7209,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7134,112 +7316,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>18503000</v>
+      </c>
+      <c r="E76" s="3">
         <v>18390000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>18076000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>18089000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>18150000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>18133000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>18779000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>19399000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>19635000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>19702000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>19355000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>19014000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>18403000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>17723000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>16561000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>15931000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>15638000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>15254000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>14858000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>14449000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>14419000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>13950000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>13928000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>13423000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>13127000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>12803000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>12426000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>12136000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>11955000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>10541000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>10117000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>9771000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>9550000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>9608000</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7342,221 +7530,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45654</v>
+      </c>
+      <c r="E80" s="2">
         <v>45563</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45472</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45381</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45290</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45108</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45017</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44835</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44744</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44653</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44562</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44471</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44380</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44289</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44198</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44107</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44009</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43918</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43827</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43736</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43645</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43554</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43463</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43372</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43099</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42917</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42826</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>359000</v>
+      </c>
+      <c r="E81" s="3">
         <v>357000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>191000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>145000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>107000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-450000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-417000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-97000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>316000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>538000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>750000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>829000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1121000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1355000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>749000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>476000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>467000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>613000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>527000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>376000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>505000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>327000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>676000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>426000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>551000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>537000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>541000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>315000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1631000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>394000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>447000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>340000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>593000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>391000</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7593,112 +7790,116 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>373000</v>
+      </c>
+      <c r="E83" s="3">
         <v>152000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>309000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>317000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>303000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>246000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>233000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>230000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>303000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>310000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>297000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>295000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>300000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>308000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>302000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>306000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>298000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>316000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>295000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>293000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>288000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>289000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>286000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>273000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>250000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>246000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>238000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>230000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>229000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>218000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>187000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>179000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>177000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>179000</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7801,8 +8002,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7905,8 +8109,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8009,8 +8216,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8113,8 +8323,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8217,112 +8430,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1031000</v>
+      </c>
+      <c r="E89" s="3">
         <v>617000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>796000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-123000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1300000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>323000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>660000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>7000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>762000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>797000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>666000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-208000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1432000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1184000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1307000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-36000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1385000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1166000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1448000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>366000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>894000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>978000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>596000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>71000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>868000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1039000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>785000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>13000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1126000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1150000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>467000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-152000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1134000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>843000</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8359,112 +8578,116 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-271000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-248000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-263000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-267000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-354000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-375000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-467000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-508000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-589000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-564000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-476000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-439000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-408000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-350000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-302000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-268000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-289000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-292000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-283000</v>
-      </c>
-      <c r="V91" s="3">
-        <v>-312000</v>
       </c>
       <c r="W91" s="3">
         <v>-312000</v>
       </c>
       <c r="X91" s="3">
+        <v>-312000</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-288000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-315000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-338000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-318000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-313000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-328000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-263000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-296000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-287000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-315000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-267000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-200000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-180000</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8567,8 +8790,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8671,112 +8897,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-233000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-34000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-233000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-243000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-378000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-427000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-696000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-507000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-669000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-610000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-440000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-426000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-459000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>841000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-275000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-249000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-259000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-280000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-266000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-496000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-381000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-129000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-569000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-317000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-2449000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-483000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-737000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-264000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-422000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-297000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-3389000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-264000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-214000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-182000</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8813,13 +9045,14 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>171000</v>
+        <v>175000</v>
       </c>
       <c r="E96" s="3">
         <v>171000</v>
@@ -8831,7 +9064,7 @@
         <v>171000</v>
       </c>
       <c r="H96" s="3">
-        <v>167000</v>
+        <v>171000</v>
       </c>
       <c r="I96" s="3">
         <v>167000</v>
@@ -8840,22 +9073,22 @@
         <v>167000</v>
       </c>
       <c r="K96" s="3">
+        <v>167000</v>
+      </c>
+      <c r="L96" s="3">
         <v>-169000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-162000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-163000</v>
-      </c>
-      <c r="N96" s="3">
-        <v>-164000</v>
       </c>
       <c r="O96" s="3">
         <v>-164000</v>
       </c>
       <c r="P96" s="3">
-        <v>-159000</v>
+        <v>-164000</v>
       </c>
       <c r="Q96" s="3">
         <v>-159000</v>
@@ -8867,34 +9100,34 @@
         <v>-159000</v>
       </c>
       <c r="T96" s="3">
-        <v>-150000</v>
+        <v>-159000</v>
       </c>
       <c r="U96" s="3">
         <v>-150000</v>
       </c>
       <c r="V96" s="3">
+        <v>-150000</v>
+      </c>
+      <c r="W96" s="3">
         <v>-151000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-150000</v>
-      </c>
-      <c r="X96" s="3">
-        <v>-134000</v>
       </c>
       <c r="Y96" s="3">
         <v>-134000</v>
       </c>
       <c r="Z96" s="3">
+        <v>-134000</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-135000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-134000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-107000</v>
-      </c>
-      <c r="AC96" s="3">
-        <v>-108000</v>
       </c>
       <c r="AD96" s="3">
         <v>-108000</v>
@@ -8903,22 +9136,25 @@
         <v>-108000</v>
       </c>
       <c r="AF96" s="3">
+        <v>-108000</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-81000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-80000</v>
-      </c>
-      <c r="AH96" s="3">
-        <v>-79000</v>
       </c>
       <c r="AI96" s="3">
         <v>-79000</v>
       </c>
       <c r="AJ96" s="3">
+        <v>-79000</v>
+      </c>
+      <c r="AK96" s="3">
         <v>-54000</v>
       </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9021,8 +9257,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9125,8 +9364,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9229,316 +9471,328 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-195000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1464000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-168000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1077000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-26000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-13000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>202000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>381000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-482000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-195000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-361000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1283000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-484000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1189000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-197000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1172000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-173000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-874000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-255000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>168000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-507000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-761000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>20000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>201000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>1711000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-455000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-71000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>153000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-729000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-769000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>2908000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>348000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-957000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-510000</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-9000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-10000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>8000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>12000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-17000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-24000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>4000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>12000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-17000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-24000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>4000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>2000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-7000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>1000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-6000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>16000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>7000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>1000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-16000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>7000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-10000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>5000</v>
       </c>
-      <c r="AA101" s="3">
-        <v>0</v>
-      </c>
       <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-5000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>3000</v>
       </c>
-      <c r="AE101" s="3">
-        <v>0</v>
-      </c>
       <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG101" s="3">
         <v>3000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>2000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>4000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-5000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>575000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-852000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>387000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>698000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>911000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-126000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>156000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-111000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-377000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-25000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-159000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1913000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>491000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>829000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>836000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1463000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>969000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>19000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>928000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>22000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>13000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>78000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>46000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-40000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>130000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>100000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-28000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-95000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-25000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>87000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-12000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-64000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-42000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>152000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TSN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TSN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="92">
   <si>
     <t>TSN</t>
   </si>
@@ -656,472 +656,485 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45745</v>
+      </c>
+      <c r="E7" s="2">
         <v>45654</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45563</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45472</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45381</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45290</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45108</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45017</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44835</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44744</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44653</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44562</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44471</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44380</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44289</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44198</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44107</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44009</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43918</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43827</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43736</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43645</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43554</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43463</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43372</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43099</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42917</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42826</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>13074000</v>
+      </c>
+      <c r="E8" s="3">
         <v>13623000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>13565000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>13353000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>13072000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>13319000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>13348000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>13140000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>13133000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>13260000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>13737000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>13495000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>13117000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>12933000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>12811000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>12478000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>11300000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>10460000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>11460000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>10022000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>10888000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>10815000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>10884000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>10885000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>10443000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>10193000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>9999000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>10051000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>9773000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>10229000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>10145000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>9850000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>9083000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>9182000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>9156000</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>12065000</v>
+      </c>
+      <c r="E9" s="3">
         <v>12431000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>12571000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>12325000</v>
       </c>
-      <c r="G9" s="3">
-        <v>12116000</v>
-      </c>
       <c r="H9" s="3">
+        <v>12113000</v>
+      </c>
+      <c r="I9" s="3">
         <v>12371000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>12664000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>12451000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>12518000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>12319000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>12412000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>11884000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>11382000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>10918000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>10270000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>10803000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>9952000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>9163000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>9653000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>8394000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>9966000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>9337000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>19490000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>9549000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>9251000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>8838000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>8660000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>8752000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>8753000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>8786000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>8794000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>8648000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>8036000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>7699000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>8067000</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1009000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1192000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>994000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1028000</v>
       </c>
-      <c r="G10" s="3">
-        <v>956000</v>
-      </c>
       <c r="H10" s="3">
+        <v>959000</v>
+      </c>
+      <c r="I10" s="3">
         <v>948000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>684000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>689000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>615000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>941000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1325000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1611000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1735000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2015000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2541000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1675000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1348000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1297000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1807000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1628000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>922000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1478000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>-8606000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1336000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1192000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1355000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1339000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1299000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1020000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1443000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1351000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1202000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1047000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1483000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>1089000</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1159,19 +1172,20 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="3">
         <v>106000</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>8</v>
@@ -1179,11 +1193,11 @@
       <c r="H12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J12" s="3">
         <v>114000</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>8</v>
@@ -1266,8 +1280,11 @@
       <c r="AK12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1373,43 +1390,46 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>415000</v>
+      </c>
+      <c r="E14" s="3">
         <v>100000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-107000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>150000</v>
       </c>
-      <c r="G14" s="3">
-        <v>94000</v>
-      </c>
       <c r="H14" s="3">
+        <v>93000</v>
+      </c>
+      <c r="I14" s="3">
         <v>145000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>583000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>469000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>114000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-14000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>66000</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>8</v>
@@ -1417,50 +1437,50 @@
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R14" s="3">
         <v>65000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>55000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>95000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>120000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>223000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>342000</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
       <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
         <v>52000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>10000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>-40000</v>
-      </c>
-      <c r="AA14" s="3">
-        <v>8000</v>
       </c>
       <c r="AB14" s="3">
         <v>8000</v>
       </c>
       <c r="AC14" s="3">
-        <v>14000</v>
+        <v>8000</v>
       </c>
       <c r="AD14" s="3">
         <v>14000</v>
       </c>
       <c r="AE14" s="3">
-        <v>0</v>
+        <v>14000</v>
       </c>
       <c r="AF14" s="3">
         <v>0</v>
@@ -1480,38 +1500,41 @@
       <c r="AK14" s="3">
         <v>0</v>
       </c>
+      <c r="AL14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>325000</v>
+        <v>336000</v>
       </c>
       <c r="E15" s="3">
         <v>325000</v>
       </c>
       <c r="F15" s="3">
+        <v>325000</v>
+      </c>
+      <c r="G15" s="3">
         <v>341000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>349000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>373000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>381000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>309000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>317000</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1587,8 +1610,11 @@
       <c r="AK15" s="3">
         <v>0</v>
       </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1623,222 +1649,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>12559000</v>
+      </c>
+      <c r="E17" s="3">
         <v>12936000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>13097000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>12862000</v>
       </c>
-      <c r="G17" s="3">
-        <v>12666000</v>
-      </c>
       <c r="H17" s="3">
+        <v>12667000</v>
+      </c>
+      <c r="I17" s="3">
         <v>12933000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>13235000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>12999000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>13068000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>12793000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>12971000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>12462000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>11961000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>11478000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>10902000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>11416000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>10580000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>9755000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>10554000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>9247000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>10373000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>10057000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>10337000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>10049000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>9808000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>9386000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>9180000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>9254000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>9275000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>9307000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>9464000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>9153000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>8512000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>8200000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>8570000</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>515000</v>
+      </c>
+      <c r="E18" s="3">
         <v>687000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>468000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>491000</v>
       </c>
-      <c r="G18" s="3">
-        <v>406000</v>
-      </c>
       <c r="H18" s="3">
+        <v>405000</v>
+      </c>
+      <c r="I18" s="3">
         <v>386000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>113000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>141000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>65000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>467000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>766000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1033000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1156000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1455000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1909000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1062000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>720000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>705000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>906000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>775000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>515000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>758000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>547000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>836000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>635000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>807000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>819000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>797000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>498000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>922000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>681000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>697000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>571000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>982000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>586000</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1876,543 +1909,559 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-23000</v>
+      </c>
+      <c r="E20" s="3">
         <v>14000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-11000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>12000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-15000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>15000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>51000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-17000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>38000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>28000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>55000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>29000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>9000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>14000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>21000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-1000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>14000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>109000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>19000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-15000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>9000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>12000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>5000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>25000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>13000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>9000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>6000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-7000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-9000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>4000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-12000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>874000</v>
+      </c>
+      <c r="E21" s="3">
         <v>998000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>794000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>843000</v>
       </c>
-      <c r="G21" s="3">
-        <v>743000</v>
-      </c>
       <c r="H21" s="3">
+        <v>742000</v>
+      </c>
+      <c r="I21" s="3">
         <v>774000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>493000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>435000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>383000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>821000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1059000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1368000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1479000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1810000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2246000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1373000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1040000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1024000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1221000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1084000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>917000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1065000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>821000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1131000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>920000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1062000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1090000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1048000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>737000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1157000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>892000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>875000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>754000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1147000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>768000</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>110000</v>
+      </c>
+      <c r="E22" s="3">
         <v>120000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>130000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>135000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>111000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>105000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>93000</v>
-      </c>
-      <c r="J22" s="3">
-        <v>89000</v>
       </c>
       <c r="K22" s="3">
         <v>89000</v>
       </c>
       <c r="L22" s="3">
+        <v>89000</v>
+      </c>
+      <c r="M22" s="3">
         <v>84000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>83000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>85000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>97000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>100000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>103000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>105000</v>
-      </c>
-      <c r="S22" s="3">
-        <v>110000</v>
       </c>
       <c r="T22" s="3">
         <v>110000</v>
       </c>
       <c r="U22" s="3">
+        <v>110000</v>
+      </c>
+      <c r="V22" s="3">
         <v>124000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>122000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>119000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>120000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>123000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>121000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>119000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>99000</v>
-      </c>
-      <c r="AC22" s="3">
-        <v>87000</v>
       </c>
       <c r="AD22" s="3">
         <v>87000</v>
       </c>
       <c r="AE22" s="3">
+        <v>87000</v>
+      </c>
+      <c r="AF22" s="3">
         <v>84000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>86000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>94000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>71000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>56000</v>
-      </c>
-      <c r="AJ22" s="3">
-        <v>58000</v>
       </c>
       <c r="AK22" s="3">
         <v>58000</v>
       </c>
+      <c r="AL22" s="3">
+        <v>58000</v>
+      </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>30000</v>
+      </c>
+      <c r="E23" s="3">
         <v>478000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>475000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>253000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>203000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>161000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-556000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-426000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-130000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>434000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>666000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>986000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1087000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1410000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1835000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>966000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>624000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>616000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>781000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>667000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>505000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>657000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>409000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>724000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>528000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>713000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>757000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>723000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>423000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>842000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>580000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>617000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>519000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>912000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>531000</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E24" s="3">
         <v>112000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>111000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>57000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>55000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>47000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-113000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>9000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-39000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>114000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>129000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>233000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>254000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>284000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>477000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>213000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>147000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>144000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>165000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>140000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>126000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>148000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>79000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>43000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>98000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>161000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>220000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>182000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>116000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>204000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>185000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>169000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>178000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>318000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>139000</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2518,222 +2567,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E26" s="3">
         <v>366000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>364000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>196000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>148000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>114000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-443000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-435000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-91000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>320000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>537000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>753000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>833000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1126000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1358000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>753000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>477000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>472000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>616000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>527000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>379000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>509000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>330000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>681000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>430000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>552000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>537000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>541000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>307000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>638000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>395000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>448000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>341000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>594000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>392000</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E27" s="3">
         <v>359000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>357000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>191000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>145000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>107000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-450000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-417000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-97000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>316000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>538000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>750000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>829000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1121000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1355000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>749000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>476000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>467000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>613000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>527000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>376000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>505000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>327000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>676000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>426000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>551000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>537000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>540000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>306000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>637000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>394000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>447000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>340000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>593000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>391000</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2839,8 +2897,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2904,8 +2965,8 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>8</v>
+      <c r="X29" s="3">
+        <v>0</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>8</v>
@@ -2919,20 +2980,20 @@
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3">
-        <v>0</v>
+      <c r="AC29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="3">
         <v>1000</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>9000</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>994000</v>
-      </c>
-      <c r="AG29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AH29" s="3" t="s">
         <v>8</v>
@@ -2946,8 +3007,11 @@
       <c r="AK29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3053,8 +3117,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3160,222 +3227,231 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>23000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-14000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>11000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-12000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>15000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-15000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-51000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>17000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-38000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-28000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-55000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-29000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-9000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-14000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-21000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>1000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-14000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-109000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-19000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>15000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-9000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-12000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-5000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-25000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-13000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-9000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-6000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>7000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>9000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-4000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>12000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-3000</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E33" s="3">
         <v>359000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>357000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>191000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>145000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>107000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-450000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-417000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-97000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>316000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>538000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>750000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>829000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1121000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1355000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>749000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>476000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>467000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>613000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>527000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>376000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>505000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>327000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>676000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>426000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>551000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>537000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>541000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>315000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1631000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>394000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>447000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>340000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>593000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>391000</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3481,227 +3557,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E35" s="3">
         <v>359000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>357000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>191000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>145000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>107000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-450000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-417000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-97000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>316000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>538000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>750000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>829000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1121000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1355000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>749000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>476000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>467000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>613000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>527000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>376000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>505000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>327000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>676000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>426000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>551000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>537000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>541000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>315000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1631000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>394000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>447000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>340000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>593000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>391000</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45745</v>
+      </c>
+      <c r="E38" s="2">
         <v>45654</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45563</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45472</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45381</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45290</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45108</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45017</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44835</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44744</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44653</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44562</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44471</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44380</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44289</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44198</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44107</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44009</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43918</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43827</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43736</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43645</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43554</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43463</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43372</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43099</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42917</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42826</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3739,8 +3824,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3778,144 +3864,148 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>992000</v>
+      </c>
+      <c r="E41" s="3">
         <v>2292000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1717000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2569000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2182000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1484000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>573000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>699000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>543000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>654000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1031000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1056000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1151000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2956000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2507000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1613000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>877000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2406000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1420000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1365000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>437000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>497000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>484000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>406000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>360000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>400000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>270000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>170000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>198000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>293000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>318000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>231000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>243000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>307000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>349000</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E42" s="3">
         <v>1000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>10000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>13000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>16000</v>
-      </c>
-      <c r="H42" s="3">
-        <v>15000</v>
       </c>
       <c r="I42" s="3">
         <v>15000</v>
       </c>
       <c r="J42" s="3">
-        <v>7000</v>
+        <v>15000</v>
       </c>
       <c r="K42" s="3">
         <v>7000</v>
       </c>
       <c r="L42" s="3">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="M42" s="3">
         <v>0</v>
@@ -3992,465 +4082,480 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2385000</v>
+      </c>
+      <c r="E43" s="3">
         <v>2323000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2406000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2389000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2358000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2263000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2476000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2451000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2433000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2295000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2577000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2518000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2408000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2091000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2400000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2324000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2113000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1900000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1952000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2064000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2248000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2063000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>4346000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2452000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1837000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1892000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1723000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1684000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1594000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1600000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1675000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>1710000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>1589000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>1512000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>1542000</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>5395000</v>
+      </c>
+      <c r="E44" s="3">
         <v>5114000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>5195000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>5033000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>5056000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>5087000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>5328000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>5391000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>5504000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>5596000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>5514000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>5332000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>4990000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>4454000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>4382000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>4262000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>4128000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>3915000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>3859000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>3915000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>4025000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>4304000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>3929000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>4149000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>3899000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>3777000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>3513000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>3378000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>3328000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>3213000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>3239000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>3248000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>2970000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>2767000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>2732000</v>
       </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>386000</v>
+      </c>
+      <c r="E45" s="3">
         <v>352000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>423000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>568000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>354000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>367000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>330000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>335000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>405000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>408000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>508000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>397000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>448000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>635000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>533000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1009000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>896000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>323000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>367000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>355000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>389000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>329000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>404000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>426000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>280000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>232000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>182000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>845000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>870000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>887000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1026000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1099000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>215000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>156000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>265000</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>9168000</v>
+      </c>
+      <c r="E46" s="3">
         <v>10082000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>9751000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>10572000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>9966000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>9216000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>8722000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>8883000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>8892000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>8953000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>9630000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>9303000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>8997000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>10136000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>9822000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>9208000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>8014000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>8544000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>7598000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>7699000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>7099000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>7193000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>6990000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>7433000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>6376000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>6301000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>5688000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>6077000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>5990000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>5993000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>6258000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>6288000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>5017000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>4742000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>4888000</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>114000</v>
+      </c>
+      <c r="E47" s="3">
         <v>109000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>103000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>96000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>92000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>93000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>89000</v>
-      </c>
-      <c r="J47" s="3">
-        <v>97000</v>
       </c>
       <c r="K47" s="3">
         <v>97000</v>
       </c>
       <c r="L47" s="3">
-        <v>0</v>
+        <v>97000</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -4527,222 +4632,231 @@
       <c r="AK47" s="3">
         <v>0</v>
       </c>
+      <c r="AL47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>9278000</v>
+      </c>
+      <c r="E48" s="3">
         <v>9353000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>10152000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>9368000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>9593000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>9672000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>10178000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>9612000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>9351000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>9120000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>9192000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>8393000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>8193000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>8012000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>7837000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>7725000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>7661000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>7664000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>8128000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>8055000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>8005000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>7911000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>7282000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>7271000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>7085000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>7018000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>6169000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>5925000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>5755000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>5673000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>5568000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>5545000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>5283000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>5206000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>5170000</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>15545000</v>
+      </c>
+      <c r="E49" s="3">
         <v>15604000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>15694000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>15729000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>15863000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>15931000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>15976000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>16366000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>16707000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>16763000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>16765000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>16856000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>16945000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>17009000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>17068000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>17141000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>17204000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>17632000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>17673000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>17732000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>17745000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>17837000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>17881000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>18150000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>18241000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>18255000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>16498000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>15903000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>15635000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>15686000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>15567000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>15636000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>11705000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>11733000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>11753000</v>
       </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4848,8 +4962,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4955,115 +5072,121 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2175000</v>
+      </c>
+      <c r="E52" s="3">
         <v>2162000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1400000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1967000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1951000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1834000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1286000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1803000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1749000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1842000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1234000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1693000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1763000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1667000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1582000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1589000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1595000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1618000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1057000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1072000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1041000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>870000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>765000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>811000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>796000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>761000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>754000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>733000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>711000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>694000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>673000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>594000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>591000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>576000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>562000</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5169,115 +5292,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>36280000</v>
+      </c>
+      <c r="E54" s="3">
         <v>37310000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>37100000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>37732000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>37465000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>36746000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>36251000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>36761000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>36796000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>36678000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>36821000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>36245000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>35898000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>36824000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>36309000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>35663000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>34474000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>35458000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>34456000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>34558000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>33890000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>33811000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>32918000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>33665000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>32498000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>32335000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>29109000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>28638000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>28091000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>28046000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>28066000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>28063000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>22596000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>22257000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>22373000</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5315,8 +5444,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5354,650 +5484,669 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2350000</v>
+      </c>
+      <c r="E57" s="3">
         <v>2497000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2402000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2291000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2244000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2623000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2594000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2421000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2387000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2530000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2483000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2306000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2269000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2115000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2225000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1950000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1900000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1997000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1876000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1743000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1742000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1916000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1926000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1958000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1710000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1962000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1694000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1546000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1485000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1748000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1698000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1608000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1466000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>1591000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>1511000</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>896000</v>
+      </c>
+      <c r="E58" s="3">
         <v>95000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>247000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1320000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1315000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1308000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2048000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>457000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1065000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>490000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>459000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>67000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>79000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1090000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1067000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1566000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>580000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>566000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>548000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>750000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1142000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1947000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>2102000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>2125000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1564000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>3917000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1911000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1308000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1128000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>811000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>906000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1017000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>543000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>66000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>79000</v>
       </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1568000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1534000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1226000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1373000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1321000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1500000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1185000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1368000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1214000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2094000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2371000</v>
-      </c>
-      <c r="N59" s="3">
-        <v>2309000</v>
       </c>
       <c r="O59" s="3">
         <v>2309000</v>
       </c>
       <c r="P59" s="3">
+        <v>2309000</v>
+      </c>
+      <c r="Q59" s="3">
         <v>2829000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3033000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2668000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2132000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2286000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1810000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1780000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1522000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1673000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1485000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1514000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1340000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1551000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1426000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1258000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1225000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1419000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1428000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1240000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1097000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>1315000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>1172000</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>5494000</v>
+      </c>
+      <c r="E60" s="3">
         <v>4780000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>4787000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>5810000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>5633000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>6172000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>6499000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>4948000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>5346000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>5114000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>5313000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>4682000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>4657000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>6034000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>6325000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>6184000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>4612000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>4849000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>4234000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>4273000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>4406000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>5536000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>5513000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>5597000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>4614000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>7430000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>5031000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>4112000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>3838000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>3978000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>4032000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>3865000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>3106000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>2972000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>2762000</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>8172000</v>
+      </c>
+      <c r="E61" s="3">
         <v>9711000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>10234000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>9701000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>9645000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>8370000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>7987000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>8863000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>7865000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>7859000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>7862000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>8261000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>8270000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>8274000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>8281000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>8786000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>9784000</v>
-      </c>
-      <c r="T61" s="3">
-        <v>10791000</v>
       </c>
       <c r="U61" s="3">
         <v>10791000</v>
       </c>
       <c r="V61" s="3">
+        <v>10791000</v>
+      </c>
+      <c r="W61" s="3">
         <v>11279000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>10978000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>9772000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>9830000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>10461000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>10810000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>8075000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>7962000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>8852000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>8872000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>8875000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>9297000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>9807000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>5905000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>5901000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>6200000</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1843000</v>
+      </c>
+      <c r="E62" s="3">
         <v>1909000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1100000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1701000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1672000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1614000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1009000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1599000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1589000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3918000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3835000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3813000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3815000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3974000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3849000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>4000000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>4008000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>4037000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>4045000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>4002000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>3912000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>3937000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>3481000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>3466000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>3516000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>3571000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>3305000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>3237000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>3225000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>3219000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>4178000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>4254000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>3796000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>3817000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>3787000</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6103,8 +6252,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6210,8 +6362,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6317,115 +6472,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>17749000</v>
+      </c>
+      <c r="E66" s="3">
         <v>18683000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>18586000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>19530000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>19242000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>18458000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>17996000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>17851000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>17238000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>17043000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>17119000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>16890000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>16884000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>18421000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>18586000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>19102000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>18543000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>19820000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>19202000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>19700000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>19441000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>19392000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>18968000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>19737000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>19075000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>19208000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>16306000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>16212000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>15955000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>16091000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>17525000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>17946000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>12825000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>12707000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>12765000</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6463,8 +6624,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6570,8 +6732,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6677,8 +6842,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6784,8 +6952,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6891,115 +7062,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>18886000</v>
+      </c>
+      <c r="E72" s="3">
         <v>19054000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>18873000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>18687000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>18667000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>18693000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>18760000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>19378000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>19962000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>20225000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>20084000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>19708000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>19119000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>18453000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>17502000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>16305000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>15716000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>15399000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>15100000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>14769000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>14392000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>14178000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>13655000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>13553000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>13012000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>12719000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>12329000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>11913000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>11479000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>11272000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>9776000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>9464000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>9098000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>8837000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>8348000</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7105,8 +7282,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7212,8 +7392,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7319,115 +7502,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>18400000</v>
+      </c>
+      <c r="E76" s="3">
         <v>18503000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>18390000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>18076000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>18089000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>18150000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>18133000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>18779000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>19399000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>19635000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>19702000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>19355000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>19014000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>18403000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>17723000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>16561000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>15931000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>15638000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>15254000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>14858000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>14449000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>14419000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>13950000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>13928000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>13423000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>13127000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>12803000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>12426000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>12136000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>11955000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>10541000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>10117000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>9771000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>9550000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>9608000</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7533,227 +7722,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45745</v>
+      </c>
+      <c r="E80" s="2">
         <v>45654</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45563</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45472</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45381</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45290</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45108</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45017</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44835</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44744</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44653</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44562</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44471</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44380</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44289</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44198</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44107</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44009</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43918</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43827</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43736</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43645</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43554</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43463</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43372</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43099</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42917</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42826</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E81" s="3">
         <v>359000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>357000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>191000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>145000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>107000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-450000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-417000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-97000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>316000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>538000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>750000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>829000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1121000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1355000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>749000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>476000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>467000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>613000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>527000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>376000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>505000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>327000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>676000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>426000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>551000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>537000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>541000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>315000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1631000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>394000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>447000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>340000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>593000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>391000</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7791,115 +7989,119 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>349000</v>
+      </c>
+      <c r="E83" s="3">
         <v>373000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>152000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>309000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>317000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>303000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>246000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>233000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>230000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>303000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>310000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>297000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>295000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>300000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>308000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>302000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>306000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>298000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>316000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>295000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>293000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>288000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>289000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>286000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>273000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>250000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>246000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>238000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>230000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>229000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>218000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>187000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>179000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>177000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>179000</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8005,8 +8207,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8112,8 +8317,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8219,8 +8427,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8326,8 +8537,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8433,115 +8647,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-185000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1031000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>617000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>796000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-123000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1300000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>323000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>660000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>7000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>762000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>797000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>666000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-208000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1432000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1184000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1307000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-36000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1385000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1166000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1448000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>366000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>894000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>978000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>596000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>71000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>868000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1039000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>785000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>13000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1126000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1150000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>467000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-152000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>1134000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>843000</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8579,115 +8799,119 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-193000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-271000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-248000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-263000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-267000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-354000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-375000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-467000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-508000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-589000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-564000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-476000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-439000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-408000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-350000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-302000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-268000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-289000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-292000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-283000</v>
-      </c>
-      <c r="W91" s="3">
-        <v>-312000</v>
       </c>
       <c r="X91" s="3">
         <v>-312000</v>
       </c>
       <c r="Y91" s="3">
+        <v>-312000</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-288000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-315000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-338000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-318000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-313000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-328000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-263000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-296000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-287000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-315000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-267000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-200000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-180000</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8793,8 +9017,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8900,115 +9127,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-181000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-233000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-34000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-233000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-243000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-378000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-427000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-696000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-507000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-669000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-610000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-440000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-426000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-459000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>841000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-275000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-249000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-259000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-280000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-266000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-496000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-381000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-129000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-569000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-317000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-2449000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-483000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-737000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-264000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-422000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-297000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-3389000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-264000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-214000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-182000</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9046,16 +9279,17 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>174000</v>
+      </c>
+      <c r="E96" s="3">
         <v>175000</v>
-      </c>
-      <c r="E96" s="3">
-        <v>171000</v>
       </c>
       <c r="F96" s="3">
         <v>171000</v>
@@ -9067,7 +9301,7 @@
         <v>171000</v>
       </c>
       <c r="I96" s="3">
-        <v>167000</v>
+        <v>171000</v>
       </c>
       <c r="J96" s="3">
         <v>167000</v>
@@ -9076,22 +9310,22 @@
         <v>167000</v>
       </c>
       <c r="L96" s="3">
+        <v>167000</v>
+      </c>
+      <c r="M96" s="3">
         <v>-169000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-162000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-163000</v>
-      </c>
-      <c r="O96" s="3">
-        <v>-164000</v>
       </c>
       <c r="P96" s="3">
         <v>-164000</v>
       </c>
       <c r="Q96" s="3">
-        <v>-159000</v>
+        <v>-164000</v>
       </c>
       <c r="R96" s="3">
         <v>-159000</v>
@@ -9103,34 +9337,34 @@
         <v>-159000</v>
       </c>
       <c r="U96" s="3">
-        <v>-150000</v>
+        <v>-159000</v>
       </c>
       <c r="V96" s="3">
         <v>-150000</v>
       </c>
       <c r="W96" s="3">
+        <v>-150000</v>
+      </c>
+      <c r="X96" s="3">
         <v>-151000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-150000</v>
-      </c>
-      <c r="Y96" s="3">
-        <v>-134000</v>
       </c>
       <c r="Z96" s="3">
         <v>-134000</v>
       </c>
       <c r="AA96" s="3">
+        <v>-134000</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-135000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-134000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-107000</v>
-      </c>
-      <c r="AD96" s="3">
-        <v>-108000</v>
       </c>
       <c r="AE96" s="3">
         <v>-108000</v>
@@ -9139,22 +9373,25 @@
         <v>-108000</v>
       </c>
       <c r="AG96" s="3">
+        <v>-108000</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-81000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-80000</v>
-      </c>
-      <c r="AI96" s="3">
-        <v>-79000</v>
       </c>
       <c r="AJ96" s="3">
         <v>-79000</v>
       </c>
       <c r="AK96" s="3">
+        <v>-79000</v>
+      </c>
+      <c r="AL96" s="3">
         <v>-54000</v>
       </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9260,8 +9497,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9367,8 +9607,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9474,325 +9717,337 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-937000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-195000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1464000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-168000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1077000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-26000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-13000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>202000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>381000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-482000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-195000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-361000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1283000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-484000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1189000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-197000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1172000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-173000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-874000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-255000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>168000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-507000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-761000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>20000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>201000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>1711000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-455000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-71000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>153000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-729000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-769000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>2908000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>348000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-957000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-510000</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="E101" s="3">
         <v>15000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-9000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-10000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>8000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>12000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-17000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-24000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>4000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>12000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-17000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-24000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>4000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>2000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-7000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>1000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-6000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>16000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>7000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>1000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-16000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>7000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-10000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>5000</v>
       </c>
-      <c r="AB101" s="3">
-        <v>0</v>
-      </c>
       <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-5000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>3000</v>
       </c>
-      <c r="AF101" s="3">
-        <v>0</v>
-      </c>
       <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH101" s="3">
         <v>3000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>2000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>4000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-5000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1300000</v>
+      </c>
+      <c r="E102" s="3">
         <v>575000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-852000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>387000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>698000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>911000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-126000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>156000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-111000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-377000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-25000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-159000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1913000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>491000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>829000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>836000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-1463000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>969000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>19000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>928000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>22000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>13000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>78000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>46000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-40000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>130000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>100000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-28000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-95000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-25000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>87000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-12000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-64000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-42000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>152000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TSN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TSN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="92">
   <si>
     <t>TSN</t>
   </si>
@@ -656,485 +656,498 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45836</v>
+      </c>
+      <c r="E7" s="2">
         <v>45745</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45654</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45563</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45472</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45381</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45290</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45108</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45017</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44835</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44744</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44653</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44562</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44471</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44380</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44289</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44198</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44107</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44009</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43918</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43827</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43736</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43645</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43554</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43463</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43372</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43099</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42917</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42826</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>13884000</v>
+      </c>
+      <c r="E8" s="3">
         <v>13074000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>13623000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>13565000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>13353000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>13072000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>13319000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>13348000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>13140000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>13133000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>13260000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>13737000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>13495000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>13117000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>12933000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>12811000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>12478000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>11300000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>10460000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>11460000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>10022000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>10888000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>10815000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>10884000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>10885000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>10443000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>10193000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>9999000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>10051000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>9773000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>10229000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>10145000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>9850000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>9083000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>9182000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>9156000</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>12846000</v>
+      </c>
+      <c r="E9" s="3">
         <v>12065000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>12431000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>12571000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>12325000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>12113000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>12371000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>12664000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>12451000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>12518000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>12319000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>12412000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>11884000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>11382000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>10918000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>10270000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>10803000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>9952000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>9163000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>9653000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>8394000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>9966000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>9337000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>19490000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>9549000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>9251000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>8838000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>8660000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>8752000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>8753000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>8786000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>8794000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>8648000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>8036000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>7699000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>8067000</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1038000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1009000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1192000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>994000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1028000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>959000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>948000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>684000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>689000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>615000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>941000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1325000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1611000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1735000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2015000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2541000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1675000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1348000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1297000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1807000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1628000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>922000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1478000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>-8606000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1336000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1192000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1355000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1339000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1299000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1020000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1443000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1351000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1202000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1047000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>1483000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>1089000</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1173,8 +1186,9 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1184,11 +1198,11 @@
       <c r="E12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G12" s="3">
         <v>106000</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>8</v>
@@ -1196,11 +1210,11 @@
       <c r="I12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J12" s="3">
+      <c r="J12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K12" s="3">
         <v>114000</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>8</v>
@@ -1283,8 +1297,11 @@
       <c r="AL12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1393,46 +1410,49 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>245000</v>
+      </c>
+      <c r="E14" s="3">
         <v>415000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>100000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-107000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>150000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>93000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>145000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>583000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>469000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>114000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-14000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>66000</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>8</v>
@@ -1440,50 +1460,50 @@
       <c r="Q14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R14" s="3">
+      <c r="R14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S14" s="3">
         <v>65000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>55000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>95000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>120000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>223000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>342000</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
       <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>52000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>10000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>-40000</v>
-      </c>
-      <c r="AB14" s="3">
-        <v>8000</v>
       </c>
       <c r="AC14" s="3">
         <v>8000</v>
       </c>
       <c r="AD14" s="3">
-        <v>14000</v>
+        <v>8000</v>
       </c>
       <c r="AE14" s="3">
         <v>14000</v>
       </c>
       <c r="AF14" s="3">
-        <v>0</v>
+        <v>14000</v>
       </c>
       <c r="AG14" s="3">
         <v>0</v>
@@ -1503,41 +1523,44 @@
       <c r="AL14" s="3">
         <v>0</v>
       </c>
+      <c r="AM14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>329000</v>
+      </c>
+      <c r="E15" s="3">
         <v>336000</v>
-      </c>
-      <c r="E15" s="3">
-        <v>325000</v>
       </c>
       <c r="F15" s="3">
         <v>325000</v>
       </c>
       <c r="G15" s="3">
-        <v>341000</v>
+        <v>325000</v>
       </c>
       <c r="H15" s="3">
+        <v>360000</v>
+      </c>
+      <c r="I15" s="3">
         <v>349000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>373000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>381000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>309000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>317000</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
@@ -1613,8 +1636,11 @@
       <c r="AL15" s="3">
         <v>0</v>
       </c>
+      <c r="AM15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1650,228 +1676,235 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>13379000</v>
+      </c>
+      <c r="E17" s="3">
         <v>12559000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>12936000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>13097000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>12862000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>12667000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>12933000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>13235000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>12999000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>13068000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>12793000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>12971000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>12462000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>11961000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>11478000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>10902000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>11416000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>10580000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>9755000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>10554000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>9247000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>10373000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>10057000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>10337000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>10049000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>9808000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>9386000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>9180000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>9254000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>9275000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>9307000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>9464000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>9153000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>8512000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>8200000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>8570000</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>505000</v>
+      </c>
+      <c r="E18" s="3">
         <v>515000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>687000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>468000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>491000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>405000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>386000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>113000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>141000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>65000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>467000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>766000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1033000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1156000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1455000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1909000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1062000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>720000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>705000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>906000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>775000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>515000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>758000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>547000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>836000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>635000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>807000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>819000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>797000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>498000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>922000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>681000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>697000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>571000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>982000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>586000</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1910,558 +1943,574 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-31000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-23000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>14000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-11000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>12000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-15000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>15000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>51000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-17000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>38000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>28000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>55000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>29000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>9000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>14000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>21000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-1000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>14000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>109000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>19000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-15000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>9000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>12000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>5000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>25000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>13000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>9000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>6000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-7000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-9000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>4000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-12000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>865000</v>
+      </c>
+      <c r="E21" s="3">
         <v>874000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>998000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>794000</v>
       </c>
-      <c r="G21" s="3">
-        <v>843000</v>
-      </c>
       <c r="H21" s="3">
+        <v>862000</v>
+      </c>
+      <c r="I21" s="3">
         <v>742000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>774000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>493000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>435000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>383000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>821000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1059000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1368000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1479000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1810000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2246000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1373000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1040000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1024000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1221000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1084000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>917000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1065000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>821000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1131000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>920000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1062000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1090000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1048000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>737000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1157000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>892000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>875000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>754000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1147000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>768000</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>113000</v>
+      </c>
+      <c r="E22" s="3">
         <v>110000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>120000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>130000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>135000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>111000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>105000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>93000</v>
-      </c>
-      <c r="K22" s="3">
-        <v>89000</v>
       </c>
       <c r="L22" s="3">
         <v>89000</v>
       </c>
       <c r="M22" s="3">
+        <v>89000</v>
+      </c>
+      <c r="N22" s="3">
         <v>84000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>83000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>85000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>97000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>100000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>103000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>105000</v>
-      </c>
-      <c r="T22" s="3">
-        <v>110000</v>
       </c>
       <c r="U22" s="3">
         <v>110000</v>
       </c>
       <c r="V22" s="3">
+        <v>110000</v>
+      </c>
+      <c r="W22" s="3">
         <v>124000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>122000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>119000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>120000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>123000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>121000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>119000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>99000</v>
-      </c>
-      <c r="AD22" s="3">
-        <v>87000</v>
       </c>
       <c r="AE22" s="3">
         <v>87000</v>
       </c>
       <c r="AF22" s="3">
+        <v>87000</v>
+      </c>
+      <c r="AG22" s="3">
         <v>84000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>86000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>94000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>71000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>56000</v>
-      </c>
-      <c r="AK22" s="3">
-        <v>58000</v>
       </c>
       <c r="AL22" s="3">
         <v>58000</v>
       </c>
+      <c r="AM22" s="3">
+        <v>58000</v>
+      </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>193000</v>
+      </c>
+      <c r="E23" s="3">
         <v>30000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>478000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>475000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>253000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>203000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>161000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-556000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-426000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-130000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>434000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>666000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>986000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1087000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1410000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1835000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>966000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>624000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>616000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>781000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>667000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>505000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>657000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>409000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>724000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>528000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>713000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>757000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>723000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>423000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>842000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>580000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>617000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>519000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>912000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>531000</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>124000</v>
+      </c>
+      <c r="E24" s="3">
         <v>16000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>112000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>111000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>57000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>55000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>47000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-113000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>9000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-39000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>114000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>129000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>233000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>254000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>284000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>477000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>213000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>147000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>144000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>165000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>140000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>126000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>148000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>79000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>43000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>98000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>161000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>220000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>182000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>116000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>204000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>185000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>169000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>178000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>318000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>139000</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2570,228 +2619,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>69000</v>
+      </c>
+      <c r="E26" s="3">
         <v>14000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>366000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>364000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>196000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>148000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>114000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-443000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-435000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-91000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>320000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>537000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>753000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>833000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1126000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1358000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>753000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>477000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>472000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>616000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>527000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>379000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>509000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>330000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>681000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>430000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>552000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>537000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>541000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>307000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>638000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>395000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>448000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>341000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>594000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>392000</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>61000</v>
+      </c>
+      <c r="E27" s="3">
         <v>7000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>359000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>357000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>191000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>145000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>107000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-450000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-417000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-97000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>316000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>538000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>750000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>829000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1121000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1355000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>749000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>476000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>467000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>613000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>527000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>376000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>505000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>327000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>676000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>426000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>551000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>537000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>540000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>306000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>637000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>394000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>447000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>340000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>593000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>391000</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2900,8 +2958,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2968,8 +3029,8 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>8</v>
+      <c r="Y29" s="3">
+        <v>0</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>8</v>
@@ -2983,20 +3044,20 @@
       <c r="AC29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD29" s="3">
-        <v>0</v>
+      <c r="AD29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="3">
         <v>1000</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>9000</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>994000</v>
-      </c>
-      <c r="AH29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AI29" s="3" t="s">
         <v>8</v>
@@ -3010,8 +3071,11 @@
       <c r="AL29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3120,8 +3184,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3230,228 +3297,237 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>31000</v>
+      </c>
+      <c r="E32" s="3">
         <v>23000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-14000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>11000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-12000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>15000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-15000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-51000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>17000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-38000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-28000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-55000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-29000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-9000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-14000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-21000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>1000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-14000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-109000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-19000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>15000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-9000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-12000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-5000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-25000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-13000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-9000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-6000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>7000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>9000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-4000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>12000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-3000</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>61000</v>
+      </c>
+      <c r="E33" s="3">
         <v>7000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>359000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>357000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>191000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>145000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>107000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-450000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-417000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-97000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>316000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>538000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>750000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>829000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1121000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1355000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>749000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>476000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>467000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>613000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>527000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>376000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>505000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>327000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>676000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>426000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>551000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>537000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>541000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>315000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>1631000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>394000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>447000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>340000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>593000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>391000</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3560,233 +3636,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>61000</v>
+      </c>
+      <c r="E35" s="3">
         <v>7000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>359000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>357000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>191000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>145000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>107000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-450000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-417000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-97000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>316000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>538000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>750000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>829000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1121000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1355000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>749000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>476000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>467000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>613000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>527000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>376000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>505000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>327000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>676000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>426000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>551000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>537000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>541000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>315000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>1631000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>394000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>447000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>340000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>593000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>391000</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45836</v>
+      </c>
+      <c r="E38" s="2">
         <v>45745</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45654</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45563</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45472</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45381</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45290</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45108</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45017</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44835</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44744</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44653</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44562</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44471</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44380</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44289</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44198</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44107</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44009</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43918</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43827</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43736</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43645</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43554</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43463</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43372</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43099</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42917</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42826</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3825,8 +3910,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3865,150 +3951,154 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1547000</v>
+      </c>
+      <c r="E41" s="3">
         <v>992000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2292000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1717000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2569000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2182000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1484000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>573000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>699000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>543000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>654000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1031000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1056000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1151000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2956000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2507000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1613000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>877000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2406000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1420000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1365000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>437000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>497000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>484000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>406000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>360000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>400000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>270000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>170000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>198000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>293000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>318000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>231000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>243000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>307000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>349000</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E42" s="3">
         <v>10000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>10000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>13000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>16000</v>
-      </c>
-      <c r="I42" s="3">
-        <v>15000</v>
       </c>
       <c r="J42" s="3">
         <v>15000</v>
       </c>
       <c r="K42" s="3">
-        <v>7000</v>
+        <v>15000</v>
       </c>
       <c r="L42" s="3">
         <v>7000</v>
       </c>
       <c r="M42" s="3">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="N42" s="3">
         <v>0</v>
@@ -4085,480 +4175,495 @@
       <c r="AL42" s="3">
         <v>0</v>
       </c>
+      <c r="AM42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2454000</v>
+      </c>
+      <c r="E43" s="3">
         <v>2385000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2323000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2406000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2389000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2358000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2263000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2476000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2451000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2433000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2295000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2577000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2518000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2408000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2091000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2400000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2324000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2113000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1900000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1952000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2064000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2248000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2063000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>4346000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2452000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1837000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1892000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1723000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1684000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1594000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1600000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>1675000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>1710000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>1589000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>1512000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>1542000</v>
       </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>5436000</v>
+      </c>
+      <c r="E44" s="3">
         <v>5395000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>5114000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>5195000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>5033000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>5056000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>5087000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>5328000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>5391000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>5504000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>5596000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>5514000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>5332000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>4990000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>4454000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>4382000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>4262000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>4128000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>3915000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>3859000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>3915000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>4025000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>4304000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>3929000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>4149000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>3899000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>3777000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>3513000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>3378000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>3328000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>3213000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>3239000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>3248000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>2970000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>2767000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>2732000</v>
       </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>421000</v>
+      </c>
+      <c r="E45" s="3">
         <v>386000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>352000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>423000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>568000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>354000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>367000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>330000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>335000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>405000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>408000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>508000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>397000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>448000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>635000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>533000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1009000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>896000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>323000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>367000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>355000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>389000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>329000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>404000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>426000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>280000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>232000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>182000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>845000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>870000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>887000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1026000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>1099000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>215000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>156000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>265000</v>
       </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>9859000</v>
+      </c>
+      <c r="E46" s="3">
         <v>9168000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>10082000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>9751000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>10572000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>9966000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>9216000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>8722000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>8883000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>8892000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>8953000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>9630000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>9303000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>8997000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>10136000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>9822000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>9208000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>8014000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>8544000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>7598000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>7699000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>7099000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>7193000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>6990000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>7433000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>6376000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>6301000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>5688000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>6077000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>5990000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>5993000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>6258000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>6288000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>5017000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>4742000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>4888000</v>
       </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>115000</v>
+      </c>
+      <c r="E47" s="3">
         <v>114000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>109000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>103000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>96000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>92000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>93000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>89000</v>
-      </c>
-      <c r="K47" s="3">
-        <v>97000</v>
       </c>
       <c r="L47" s="3">
         <v>97000</v>
       </c>
       <c r="M47" s="3">
-        <v>0</v>
+        <v>97000</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -4635,228 +4740,237 @@
       <c r="AL47" s="3">
         <v>0</v>
       </c>
+      <c r="AM47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>9081000</v>
+      </c>
+      <c r="E48" s="3">
         <v>9278000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>9353000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>10152000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>9368000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>9593000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>9672000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>10178000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>9612000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>9351000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>9120000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>9192000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>8393000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>8193000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>8012000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>7837000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>7725000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>7661000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>7664000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>8128000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>8055000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>8005000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>7911000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>7282000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>7271000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>7085000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>7018000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>6169000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>5925000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>5755000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>5673000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>5568000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>5545000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>5283000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>5206000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>5170000</v>
       </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>15151000</v>
+      </c>
+      <c r="E49" s="3">
         <v>15545000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>15604000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>15694000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>15729000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>15863000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>15931000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>15976000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>16366000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>16707000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>16763000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>16765000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>16856000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>16945000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>17009000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>17068000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>17141000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>17204000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>17632000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>17673000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>17732000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>17745000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>17837000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>17881000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>18150000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>18241000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>18255000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>16498000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>15903000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>15635000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>15686000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>15567000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>15636000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>11705000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>11733000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>11753000</v>
       </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4965,8 +5079,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5075,118 +5192,124 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2258000</v>
+      </c>
+      <c r="E52" s="3">
         <v>2175000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2162000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1400000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1967000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1951000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1834000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1286000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1803000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1749000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1842000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1234000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1693000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1763000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1667000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1582000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1589000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1595000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1618000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1057000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1072000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1041000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>870000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>765000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>811000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>796000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>761000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>754000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>733000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>711000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>694000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>673000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>594000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>591000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>576000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>562000</v>
       </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5295,118 +5418,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>36464000</v>
+      </c>
+      <c r="E54" s="3">
         <v>36280000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>37310000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>37100000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>37732000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>37465000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>36746000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>36251000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>36761000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>36796000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>36678000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>36821000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>36245000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>35898000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>36824000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>36309000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>35663000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>34474000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>35458000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>34456000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>34558000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>33890000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>33811000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>32918000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>33665000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>32498000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>32335000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>29109000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>28638000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>28091000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>28046000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>28066000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>28063000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>22596000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>22257000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>22373000</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5445,8 +5574,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5485,668 +5615,687 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2373000</v>
+      </c>
+      <c r="E57" s="3">
         <v>2350000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2497000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2402000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2291000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2244000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2623000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2594000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2421000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2387000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2530000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2483000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2306000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2269000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2115000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2225000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1950000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1900000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1997000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1876000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1743000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1742000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1916000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1926000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1958000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1710000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1962000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1694000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1546000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1485000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1748000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1698000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1608000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>1466000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>1591000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>1511000</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>886000</v>
+      </c>
+      <c r="E58" s="3">
         <v>896000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>95000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>247000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1320000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1315000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1308000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2048000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>457000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1065000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>490000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>459000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>67000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>79000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1090000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1067000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1566000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>580000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>566000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>548000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>750000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1142000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1947000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>2102000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>2125000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1564000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>3917000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1911000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1308000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1128000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>811000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>906000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1017000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>543000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>66000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>79000</v>
       </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1619000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1568000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1534000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1226000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1373000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1321000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1500000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1185000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1368000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1214000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2094000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2371000</v>
-      </c>
-      <c r="O59" s="3">
-        <v>2309000</v>
       </c>
       <c r="P59" s="3">
         <v>2309000</v>
       </c>
       <c r="Q59" s="3">
+        <v>2309000</v>
+      </c>
+      <c r="R59" s="3">
         <v>2829000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3033000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2668000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2132000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2286000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1810000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1780000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1522000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1673000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1485000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1514000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1340000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1551000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1426000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1258000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1225000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1419000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1428000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1240000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>1097000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>1315000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>1172000</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>5690000</v>
+      </c>
+      <c r="E60" s="3">
         <v>5494000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>4780000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>4787000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>5810000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>5633000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>6172000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>6499000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4948000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>5346000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>5114000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>5313000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>4682000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>4657000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>6034000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>6325000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>6184000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>4612000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>4849000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>4234000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>4273000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>4406000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>5536000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>5513000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>5597000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>4614000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>7430000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>5031000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>4112000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>3838000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>3978000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>4032000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>3865000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>3106000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>2972000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>2762000</v>
       </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>8179000</v>
+      </c>
+      <c r="E61" s="3">
         <v>8172000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>9711000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>10234000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>9701000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>9645000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>8370000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>7987000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>8863000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>7865000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>7859000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>7862000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>8261000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>8270000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>8274000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>8281000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>8786000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>9784000</v>
-      </c>
-      <c r="U61" s="3">
-        <v>10791000</v>
       </c>
       <c r="V61" s="3">
         <v>10791000</v>
       </c>
       <c r="W61" s="3">
+        <v>10791000</v>
+      </c>
+      <c r="X61" s="3">
         <v>11279000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>10978000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>9772000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>9830000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>10461000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>10810000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>8075000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>7962000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>8852000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>8872000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>8875000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>9297000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>9807000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>5905000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>5901000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>6200000</v>
       </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1910000</v>
+      </c>
+      <c r="E62" s="3">
         <v>1843000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1909000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1100000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1701000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1672000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1614000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1009000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1599000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1589000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3918000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3835000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3813000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3815000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3974000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3849000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>4000000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>4008000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>4037000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>4045000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>4002000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>3912000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>3937000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>3481000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>3466000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>3516000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>3571000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>3305000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>3237000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>3225000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>3219000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>4178000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>4254000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>3796000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>3817000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>3787000</v>
       </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6255,8 +6404,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6365,8 +6517,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6475,118 +6630,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>17996000</v>
+      </c>
+      <c r="E66" s="3">
         <v>17749000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>18683000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>18586000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>19530000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>19242000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>18458000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>17996000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>17851000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>17238000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>17043000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>17119000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>16890000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>16884000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>18421000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>18586000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>19102000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>18543000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>19820000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>19202000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>19700000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>19441000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>19392000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>18968000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>19737000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>19075000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>19208000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>16306000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>16212000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>15955000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>16091000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>17525000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>17946000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>12825000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>12707000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>12765000</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6625,8 +6786,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6735,8 +6897,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6845,8 +7010,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6955,8 +7123,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7065,118 +7236,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>18772000</v>
+      </c>
+      <c r="E72" s="3">
         <v>18886000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>19054000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>18873000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>18687000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>18667000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>18693000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>18760000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>19378000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>19962000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>20225000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>20084000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>19708000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>19119000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>18453000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>17502000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>16305000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>15716000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>15399000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>15100000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>14769000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>14392000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>14178000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>13655000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>13553000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>13012000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>12719000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>12329000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>11913000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>11479000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>11272000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>9776000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>9464000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>9098000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>8837000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>8348000</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7285,8 +7462,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7395,8 +7575,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7505,118 +7688,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>18338000</v>
+      </c>
+      <c r="E76" s="3">
         <v>18400000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>18503000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>18390000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>18076000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>18089000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>18150000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>18133000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>18779000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>19399000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>19635000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>19702000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>19355000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>19014000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>18403000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>17723000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>16561000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>15931000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>15638000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>15254000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>14858000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>14449000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>14419000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>13950000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>13928000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>13423000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>13127000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>12803000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>12426000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>12136000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>11955000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>10541000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>10117000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>9771000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>9550000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>9608000</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7725,233 +7914,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45836</v>
+      </c>
+      <c r="E80" s="2">
         <v>45745</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45654</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45563</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45472</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45381</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45290</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45108</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45017</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44835</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44744</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44653</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44562</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44471</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44380</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44289</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44198</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44107</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44009</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43918</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43827</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43736</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43645</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43554</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43463</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43372</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43099</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42917</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42826</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>61000</v>
+      </c>
+      <c r="E81" s="3">
         <v>7000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>359000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>357000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>191000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>145000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>107000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-450000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-417000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-97000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>316000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>538000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>750000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>829000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1121000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1355000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>749000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>476000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>467000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>613000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>527000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>376000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>505000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>327000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>676000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>426000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>551000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>537000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>541000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>315000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>1631000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>394000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>447000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>340000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>593000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>391000</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7990,118 +8188,122 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>360000</v>
+      </c>
+      <c r="E83" s="3">
         <v>349000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>373000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>152000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>309000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>317000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>303000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>246000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>233000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>230000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>303000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>310000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>297000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>295000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>300000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>308000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>302000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>306000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>298000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>316000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>295000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>293000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>288000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>289000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>286000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>273000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>250000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>246000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>238000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>230000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>229000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>218000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>187000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>179000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>177000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>179000</v>
       </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8210,8 +8412,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8320,8 +8525,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8430,8 +8638,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8540,8 +8751,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8650,118 +8864,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>774000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-185000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1031000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>617000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>796000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-123000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1300000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>323000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>660000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>7000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>762000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>797000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>666000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-208000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1432000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1184000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1307000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-36000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1385000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1166000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1448000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>366000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>894000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>978000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>596000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>71000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>868000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1039000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>785000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>13000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1126000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1150000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>467000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-152000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>1134000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>843000</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8800,118 +9020,122 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-227000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-193000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-271000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-248000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-263000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-267000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-354000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-375000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-467000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-508000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-589000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-564000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-476000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-439000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-408000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-350000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-302000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-268000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-289000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-292000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-283000</v>
-      </c>
-      <c r="X91" s="3">
-        <v>-312000</v>
       </c>
       <c r="Y91" s="3">
         <v>-312000</v>
       </c>
       <c r="Z91" s="3">
+        <v>-312000</v>
+      </c>
+      <c r="AA91" s="3">
         <v>-288000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-315000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-338000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-318000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-313000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-328000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-263000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-296000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-287000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-315000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-267000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-200000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-180000</v>
       </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9020,8 +9244,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9130,118 +9357,124 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-181000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-233000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-34000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-233000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-243000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-378000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-427000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-696000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-507000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-669000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-610000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-440000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-426000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-459000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>841000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-275000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-249000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-259000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-280000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-266000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-496000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-381000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-129000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-569000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-317000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-2449000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-483000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-737000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-264000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-422000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-297000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-3389000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-264000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-214000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-182000</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9280,19 +9513,20 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>175000</v>
+      </c>
+      <c r="E96" s="3">
         <v>174000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>175000</v>
-      </c>
-      <c r="F96" s="3">
-        <v>171000</v>
       </c>
       <c r="G96" s="3">
         <v>171000</v>
@@ -9304,7 +9538,7 @@
         <v>171000</v>
       </c>
       <c r="J96" s="3">
-        <v>167000</v>
+        <v>171000</v>
       </c>
       <c r="K96" s="3">
         <v>167000</v>
@@ -9313,22 +9547,22 @@
         <v>167000</v>
       </c>
       <c r="M96" s="3">
+        <v>167000</v>
+      </c>
+      <c r="N96" s="3">
         <v>-169000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-162000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-163000</v>
-      </c>
-      <c r="P96" s="3">
-        <v>-164000</v>
       </c>
       <c r="Q96" s="3">
         <v>-164000</v>
       </c>
       <c r="R96" s="3">
-        <v>-159000</v>
+        <v>-164000</v>
       </c>
       <c r="S96" s="3">
         <v>-159000</v>
@@ -9340,34 +9574,34 @@
         <v>-159000</v>
       </c>
       <c r="V96" s="3">
-        <v>-150000</v>
+        <v>-159000</v>
       </c>
       <c r="W96" s="3">
         <v>-150000</v>
       </c>
       <c r="X96" s="3">
+        <v>-150000</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-151000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-150000</v>
-      </c>
-      <c r="Z96" s="3">
-        <v>-134000</v>
       </c>
       <c r="AA96" s="3">
         <v>-134000</v>
       </c>
       <c r="AB96" s="3">
+        <v>-134000</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-135000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-134000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-107000</v>
-      </c>
-      <c r="AE96" s="3">
-        <v>-108000</v>
       </c>
       <c r="AF96" s="3">
         <v>-108000</v>
@@ -9376,22 +9610,25 @@
         <v>-108000</v>
       </c>
       <c r="AH96" s="3">
+        <v>-108000</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-81000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-80000</v>
-      </c>
-      <c r="AJ96" s="3">
-        <v>-79000</v>
       </c>
       <c r="AK96" s="3">
         <v>-79000</v>
       </c>
       <c r="AL96" s="3">
+        <v>-79000</v>
+      </c>
+      <c r="AM96" s="3">
         <v>-54000</v>
       </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9500,8 +9737,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9610,8 +9850,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9720,334 +9963,346 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-245000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-937000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-195000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1464000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-168000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1077000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-26000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-13000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>202000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>381000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-482000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-195000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-361000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1283000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-484000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1189000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-197000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1172000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-173000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-874000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-255000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>168000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-507000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-761000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>20000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>201000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>1711000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-455000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-71000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>153000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-729000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-769000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>2908000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>348000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-957000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-510000</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-13000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>15000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-9000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-10000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>8000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>12000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-17000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-24000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>4000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>12000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-17000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-24000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>4000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>2000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-7000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>1000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-6000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>16000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>7000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>1000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-16000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>7000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-10000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>5000</v>
       </c>
-      <c r="AC101" s="3">
-        <v>0</v>
-      </c>
       <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-5000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>3000</v>
       </c>
-      <c r="AG101" s="3">
-        <v>0</v>
-      </c>
       <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI101" s="3">
         <v>3000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>2000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>4000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-5000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>555000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1300000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>575000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-852000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>387000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>698000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>911000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-126000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>156000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-111000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-377000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-25000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-159000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1913000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>491000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>829000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>836000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-1463000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>969000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>19000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>928000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>22000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>13000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>78000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>46000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-40000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>130000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>100000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-28000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-95000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-25000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>87000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-12000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-64000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-42000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>152000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TSN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TSN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="92">
   <si>
     <t>TSN</t>
   </si>
@@ -656,511 +656,523 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46018</v>
+      </c>
+      <c r="E7" s="2">
         <v>45927</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45836</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45745</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45654</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45563</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45472</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45381</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45290</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45108</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45017</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44835</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44744</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44653</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44562</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44471</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44380</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44289</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44198</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44107</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44009</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43918</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43827</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43736</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43645</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43554</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43463</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43372</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43099</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42917</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42826</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42735</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>14313000</v>
+      </c>
+      <c r="E8" s="3">
         <v>13860000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>13884000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>13074000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>13623000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>13565000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>13353000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>13072000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>13319000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>13348000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>13140000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>13133000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>13260000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>13737000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>13495000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>13117000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>12933000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>12811000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>12478000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>11300000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>10460000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>11460000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>10022000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>10888000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>10815000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>10884000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>10885000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>10443000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>10193000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>9999000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>10051000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>9773000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>10229000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>10145000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>9850000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>9083000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>9182000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>9156000</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>13400000</v>
+      </c>
+      <c r="E9" s="3">
         <v>13336000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>12846000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>12065000</v>
       </c>
-      <c r="G9" s="3">
-        <v>12431000</v>
-      </c>
       <c r="H9" s="3">
+        <v>12457000</v>
+      </c>
+      <c r="I9" s="3">
         <v>12571000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>12325000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>12113000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>12371000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>12664000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>12451000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>12518000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>12319000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>12412000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>11884000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>11382000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>10918000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>10270000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>10803000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>9952000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>9163000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>9653000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>8394000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>9966000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>9337000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>19490000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>9549000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>9251000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>8838000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>8660000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>8752000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>8753000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>8786000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>8794000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>8648000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>8036000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>7699000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>8067000</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>913000</v>
+      </c>
+      <c r="E10" s="3">
         <v>524000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1038000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1009000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
+        <v>1166000</v>
+      </c>
+      <c r="I10" s="3">
+        <v>994000</v>
+      </c>
+      <c r="J10" s="3">
+        <v>1028000</v>
+      </c>
+      <c r="K10" s="3">
+        <v>959000</v>
+      </c>
+      <c r="L10" s="3">
+        <v>948000</v>
+      </c>
+      <c r="M10" s="3">
+        <v>684000</v>
+      </c>
+      <c r="N10" s="3">
+        <v>689000</v>
+      </c>
+      <c r="O10" s="3">
+        <v>615000</v>
+      </c>
+      <c r="P10" s="3">
+        <v>941000</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>1325000</v>
+      </c>
+      <c r="R10" s="3">
+        <v>1611000</v>
+      </c>
+      <c r="S10" s="3">
+        <v>1735000</v>
+      </c>
+      <c r="T10" s="3">
+        <v>2015000</v>
+      </c>
+      <c r="U10" s="3">
+        <v>2541000</v>
+      </c>
+      <c r="V10" s="3">
+        <v>1675000</v>
+      </c>
+      <c r="W10" s="3">
+        <v>1348000</v>
+      </c>
+      <c r="X10" s="3">
+        <v>1297000</v>
+      </c>
+      <c r="Y10" s="3">
+        <v>1807000</v>
+      </c>
+      <c r="Z10" s="3">
+        <v>1628000</v>
+      </c>
+      <c r="AA10" s="3">
+        <v>922000</v>
+      </c>
+      <c r="AB10" s="3">
+        <v>1478000</v>
+      </c>
+      <c r="AC10" s="3">
+        <v>-8606000</v>
+      </c>
+      <c r="AD10" s="3">
+        <v>1336000</v>
+      </c>
+      <c r="AE10" s="3">
         <v>1192000</v>
       </c>
-      <c r="H10" s="3">
-        <v>994000</v>
-      </c>
-      <c r="I10" s="3">
-        <v>1028000</v>
-      </c>
-      <c r="J10" s="3">
-        <v>959000</v>
-      </c>
-      <c r="K10" s="3">
-        <v>948000</v>
-      </c>
-      <c r="L10" s="3">
-        <v>684000</v>
-      </c>
-      <c r="M10" s="3">
-        <v>689000</v>
-      </c>
-      <c r="N10" s="3">
-        <v>615000</v>
-      </c>
-      <c r="O10" s="3">
-        <v>941000</v>
-      </c>
-      <c r="P10" s="3">
-        <v>1325000</v>
-      </c>
-      <c r="Q10" s="3">
-        <v>1611000</v>
-      </c>
-      <c r="R10" s="3">
-        <v>1735000</v>
-      </c>
-      <c r="S10" s="3">
-        <v>2015000</v>
-      </c>
-      <c r="T10" s="3">
-        <v>2541000</v>
-      </c>
-      <c r="U10" s="3">
-        <v>1675000</v>
-      </c>
-      <c r="V10" s="3">
-        <v>1348000</v>
-      </c>
-      <c r="W10" s="3">
-        <v>1297000</v>
-      </c>
-      <c r="X10" s="3">
-        <v>1807000</v>
-      </c>
-      <c r="Y10" s="3">
-        <v>1628000</v>
-      </c>
-      <c r="Z10" s="3">
-        <v>922000</v>
-      </c>
-      <c r="AA10" s="3">
-        <v>1478000</v>
-      </c>
-      <c r="AB10" s="3">
-        <v>-8606000</v>
-      </c>
-      <c r="AC10" s="3">
-        <v>1336000</v>
-      </c>
-      <c r="AD10" s="3">
-        <v>1192000</v>
-      </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1355000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1339000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1299000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1020000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1443000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1351000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>1202000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>1047000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>1483000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>1089000</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1201,16 +1213,17 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="3">
         <v>126000</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>8</v>
@@ -1218,11 +1231,11 @@
       <c r="G12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I12" s="3">
         <v>106000</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>8</v>
@@ -1230,11 +1243,11 @@
       <c r="K12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L12" s="3">
+      <c r="L12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M12" s="3">
         <v>114000</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N12" s="3" t="s">
         <v>8</v>
@@ -1317,8 +1330,11 @@
       <c r="AN12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1433,52 +1449,55 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>192000</v>
+      </c>
+      <c r="E14" s="3">
         <v>-258000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>245000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>415000</v>
       </c>
-      <c r="G14" s="3">
-        <v>100000</v>
-      </c>
       <c r="H14" s="3">
+        <v>72000</v>
+      </c>
+      <c r="I14" s="3">
         <v>-107000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>150000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>93000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>145000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>583000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>469000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>114000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-14000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>66000</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>8</v>
@@ -1486,50 +1505,50 @@
       <c r="S14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T14" s="3">
+      <c r="T14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U14" s="3">
         <v>65000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>55000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>95000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>120000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>223000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>342000</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
       <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
         <v>52000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>10000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>-40000</v>
-      </c>
-      <c r="AD14" s="3">
-        <v>8000</v>
       </c>
       <c r="AE14" s="3">
         <v>8000</v>
       </c>
       <c r="AF14" s="3">
-        <v>14000</v>
+        <v>8000</v>
       </c>
       <c r="AG14" s="3">
         <v>14000</v>
       </c>
       <c r="AH14" s="3">
-        <v>0</v>
+        <v>14000</v>
       </c>
       <c r="AI14" s="3">
         <v>0</v>
@@ -1549,47 +1568,50 @@
       <c r="AN14" s="3">
         <v>0</v>
       </c>
+      <c r="AO14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>319000</v>
+      </c>
+      <c r="E15" s="3">
         <v>321000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>329000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>336000</v>
       </c>
-      <c r="G15" s="3">
-        <v>325000</v>
-      </c>
       <c r="H15" s="3">
+        <v>319000</v>
+      </c>
+      <c r="I15" s="3">
         <v>306000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>360000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>349000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>373000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>381000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>309000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>317000</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
       <c r="P15" s="3">
         <v>0</v>
       </c>
@@ -1665,8 +1687,11 @@
       <c r="AN15" s="3">
         <v>0</v>
       </c>
+      <c r="AO15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1704,240 +1729,247 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>13896000</v>
+      </c>
+      <c r="E17" s="3">
         <v>13929000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>13379000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>12559000</v>
       </c>
-      <c r="G17" s="3">
-        <v>12936000</v>
-      </c>
       <c r="H17" s="3">
+        <v>12964000</v>
+      </c>
+      <c r="I17" s="3">
         <v>13125000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>12862000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>12667000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>12933000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>13235000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>12999000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>13068000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>12793000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>12971000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>12462000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>11961000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>11478000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>10902000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>11416000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>10580000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>9755000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>10554000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>9247000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>10373000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>10057000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>10337000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>10049000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>9808000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>9386000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>9180000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>9254000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>9275000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>9307000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>9464000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>9153000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>8512000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>8200000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>8570000</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>417000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-69000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>505000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>515000</v>
       </c>
-      <c r="G18" s="3">
-        <v>687000</v>
-      </c>
       <c r="H18" s="3">
+        <v>659000</v>
+      </c>
+      <c r="I18" s="3">
         <v>440000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>491000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>405000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>386000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>113000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>141000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>65000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>467000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>766000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1033000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1156000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1455000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1909000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1062000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>720000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>705000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>906000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>775000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>515000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>758000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>547000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>836000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>635000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>807000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>819000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>797000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>498000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>922000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>681000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>697000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>571000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>982000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>586000</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1978,588 +2010,604 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E20" s="3">
         <v>31000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-31000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-23000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>14000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-29000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-11000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>12000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-15000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>15000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>51000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-17000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>38000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>28000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>55000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>29000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>9000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>14000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>21000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>14000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>109000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>19000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-15000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>9000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>12000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>5000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>25000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>13000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>9000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>6000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-7000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-9000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>4000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-12000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>729000</v>
+      </c>
+      <c r="E21" s="3">
         <v>221000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>865000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>874000</v>
       </c>
-      <c r="G21" s="3">
-        <v>998000</v>
-      </c>
       <c r="H21" s="3">
+        <v>964000</v>
+      </c>
+      <c r="I21" s="3">
         <v>775000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>862000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>742000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>774000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>493000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>435000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>383000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>821000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1059000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1368000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1479000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1810000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>2246000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1373000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1040000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1024000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1221000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1084000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>917000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1065000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>821000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1131000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>920000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1062000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1090000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1048000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>737000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1157000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>892000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>875000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>754000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>1147000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>768000</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>104000</v>
+      </c>
+      <c r="E22" s="3">
         <v>106000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>113000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>110000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>120000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>130000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>135000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>111000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>105000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>93000</v>
-      </c>
-      <c r="M22" s="3">
-        <v>89000</v>
       </c>
       <c r="N22" s="3">
         <v>89000</v>
       </c>
       <c r="O22" s="3">
+        <v>89000</v>
+      </c>
+      <c r="P22" s="3">
         <v>84000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>83000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>85000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>97000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>100000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>103000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>105000</v>
-      </c>
-      <c r="V22" s="3">
-        <v>110000</v>
       </c>
       <c r="W22" s="3">
         <v>110000</v>
       </c>
       <c r="X22" s="3">
+        <v>110000</v>
+      </c>
+      <c r="Y22" s="3">
         <v>124000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>122000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>119000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>120000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>123000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>121000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>119000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>99000</v>
-      </c>
-      <c r="AF22" s="3">
-        <v>87000</v>
       </c>
       <c r="AG22" s="3">
         <v>87000</v>
       </c>
       <c r="AH22" s="3">
+        <v>87000</v>
+      </c>
+      <c r="AI22" s="3">
         <v>84000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>86000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>94000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>71000</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>56000</v>
-      </c>
-      <c r="AM22" s="3">
-        <v>58000</v>
       </c>
       <c r="AN22" s="3">
         <v>58000</v>
       </c>
+      <c r="AO22" s="3">
+        <v>58000</v>
+      </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>127000</v>
+      </c>
+      <c r="E23" s="3">
         <v>68000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>193000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>30000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>478000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>475000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>253000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>203000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>161000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-556000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-426000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-130000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>434000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>666000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>986000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1087000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1410000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1835000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>966000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>624000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>616000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>781000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>667000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>505000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>657000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>409000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>724000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>528000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>713000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>757000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>723000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>423000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>842000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>580000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>617000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>519000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>912000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>531000</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>37000</v>
+      </c>
+      <c r="E24" s="3">
         <v>10000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>124000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>16000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>112000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>111000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>57000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>55000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>47000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-113000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>9000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-39000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>114000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>129000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>233000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>254000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>284000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>477000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>213000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>147000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>144000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>165000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>140000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>126000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>148000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>79000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>43000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>98000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>161000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>220000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>182000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>116000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>204000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>185000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>169000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>178000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>318000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>139000</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2674,240 +2722,249 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>90000</v>
+      </c>
+      <c r="E26" s="3">
         <v>58000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>69000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>14000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>366000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>364000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>196000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>148000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>114000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-443000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-435000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-91000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>320000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>537000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>753000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>833000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1126000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1358000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>753000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>477000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>472000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>616000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>527000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>379000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>509000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>330000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>681000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>430000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>552000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>537000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>541000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>307000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>638000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>395000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>448000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>341000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>594000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>392000</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>85000</v>
+      </c>
+      <c r="E27" s="3">
         <v>47000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>61000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>7000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>359000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>357000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>191000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>145000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>107000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-450000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-417000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-97000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>316000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>538000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>750000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>829000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1121000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1355000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>749000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>476000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>467000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>613000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>527000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>376000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>505000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>327000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>676000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>426000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>551000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>537000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>540000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>306000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>637000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>394000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>447000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>340000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>593000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>391000</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3022,8 +3079,11 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3096,8 +3156,8 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
@@ -3111,20 +3171,20 @@
       <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF29" s="3">
-        <v>0</v>
+      <c r="AF29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="3">
         <v>1000</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>9000</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>994000</v>
-      </c>
-      <c r="AJ29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AK29" s="3" t="s">
         <v>8</v>
@@ -3138,8 +3198,11 @@
       <c r="AN29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3254,8 +3317,11 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3370,240 +3436,249 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-31000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>31000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>23000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-14000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>29000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>11000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-12000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>15000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-15000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-51000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>17000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-38000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-28000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-55000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-29000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-9000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-14000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-21000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>1000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-14000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-109000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-19000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>15000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-9000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-12000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-5000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-25000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-13000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-9000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-6000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>7000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>9000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-4000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>12000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-3000</v>
       </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>85000</v>
+      </c>
+      <c r="E33" s="3">
         <v>47000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>61000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>7000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>359000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>357000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>191000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>145000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>107000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-450000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-417000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-97000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>316000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>538000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>750000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>829000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1121000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1355000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>749000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>476000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>467000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>613000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>527000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>376000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>505000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>327000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>676000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>426000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>551000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>537000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>541000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>315000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>1631000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>394000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>447000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>340000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>593000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>391000</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3718,245 +3793,254 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>85000</v>
+      </c>
+      <c r="E35" s="3">
         <v>47000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>61000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>7000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>359000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>357000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>191000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>145000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>107000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-450000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-417000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-97000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>316000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>538000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>750000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>829000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1121000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1355000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>749000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>476000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>467000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>613000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>527000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>376000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>505000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>327000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>676000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>426000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>551000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>537000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>541000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>315000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>1631000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>394000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>447000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>340000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>593000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>391000</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46018</v>
+      </c>
+      <c r="E38" s="2">
         <v>45927</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45836</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45745</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45654</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45563</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45472</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45381</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45290</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45108</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45017</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44835</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44744</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44653</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44562</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44471</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44380</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44289</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44198</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44107</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44009</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43918</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43827</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43736</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43645</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43554</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43463</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43372</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43099</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42917</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42826</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42735</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3997,8 +4081,9 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4039,124 +4124,128 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1278000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1229000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1547000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>992000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2292000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1717000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2569000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2182000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1484000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>573000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>699000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>543000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>654000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1031000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1056000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1151000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2956000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2507000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1613000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>877000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2406000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1420000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1365000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>437000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>497000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>484000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>406000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>360000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>400000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>270000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>170000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>198000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>293000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>318000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>231000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>243000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>307000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>349000</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4164,37 +4253,37 @@
         <v>0</v>
       </c>
       <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>1000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>10000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>10000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>13000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>16000</v>
-      </c>
-      <c r="K42" s="3">
-        <v>15000</v>
       </c>
       <c r="L42" s="3">
         <v>15000</v>
       </c>
       <c r="M42" s="3">
-        <v>7000</v>
+        <v>15000</v>
       </c>
       <c r="N42" s="3">
         <v>7000</v>
       </c>
       <c r="O42" s="3">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="P42" s="3">
         <v>0</v>
@@ -4271,510 +4360,525 @@
       <c r="AN42" s="3">
         <v>0</v>
       </c>
+      <c r="AO42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2429000</v>
+      </c>
+      <c r="E43" s="3">
         <v>2524000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2454000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2385000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2323000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2406000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2389000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2358000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2263000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2476000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2451000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2433000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2295000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2577000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2518000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2408000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2091000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2400000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2324000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2113000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1900000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1952000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2064000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2248000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2063000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>4346000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2452000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1837000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1892000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1723000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1684000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>1594000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>1600000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>1675000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>1710000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>1589000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>1512000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>1542000</v>
       </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>5406000</v>
+      </c>
+      <c r="E44" s="3">
         <v>5681000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>5436000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>5395000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>5114000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>5195000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>5033000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>5056000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>5087000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>5328000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>5391000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>5504000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>5596000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>5514000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>5332000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>4990000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>4454000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>4382000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>4262000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>4128000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>3915000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>3859000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>3915000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>4025000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>4304000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>3929000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>4149000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>3899000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>3777000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>3513000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>3378000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>3328000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>3213000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>3239000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>3248000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>2970000</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>2767000</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>2732000</v>
       </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>399000</v>
+      </c>
+      <c r="E45" s="3">
         <v>482000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>421000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>386000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>352000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>423000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>568000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>354000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>367000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>330000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>335000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>405000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>408000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>508000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>397000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>448000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>635000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>533000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1009000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>896000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>323000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>367000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>355000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>389000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>329000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>404000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>426000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>280000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>232000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>182000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>845000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>870000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>887000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>1026000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>1099000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>215000</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>156000</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>265000</v>
       </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>9512000</v>
+      </c>
+      <c r="E46" s="3">
         <v>9916000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>9859000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>9168000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>10082000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>9751000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>10572000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>9966000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>9216000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>8722000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>8883000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>8892000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>8953000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>9630000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>9303000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>8997000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>10136000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>9822000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>9208000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>8014000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>8544000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>7598000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>7699000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>7099000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>7193000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>6990000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>7433000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>6376000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>6301000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>5688000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>6077000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>5990000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>5993000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>6258000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>6288000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>5017000</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>4742000</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>4888000</v>
       </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>118000</v>
+      </c>
+      <c r="E47" s="3">
         <v>117000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>115000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>114000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>109000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>103000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>96000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>92000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>93000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>89000</v>
-      </c>
-      <c r="M47" s="3">
-        <v>97000</v>
       </c>
       <c r="N47" s="3">
         <v>97000</v>
       </c>
       <c r="O47" s="3">
-        <v>0</v>
+        <v>97000</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -4851,240 +4955,249 @@
       <c r="AN47" s="3">
         <v>0</v>
       </c>
+      <c r="AO47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>9064000</v>
+      </c>
+      <c r="E48" s="3">
         <v>10091000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>9081000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>9278000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>9353000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>10152000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>9368000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>9593000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>9672000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>10178000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>9612000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>9351000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>9120000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>9192000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>8393000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>8193000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>8012000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>7837000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>7725000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>7661000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>7664000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>8128000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>8055000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>8005000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>7911000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>7282000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>7271000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>7085000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>7018000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>6169000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>5925000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>5755000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>5673000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>5568000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>5545000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>5283000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>5206000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>5170000</v>
       </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>15051000</v>
+      </c>
+      <c r="E49" s="3">
         <v>15093000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>15151000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>15545000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>15604000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>15694000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>15729000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>15863000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>15931000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>15976000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>16366000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>16707000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>16763000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>16765000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>16856000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>16945000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>17009000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>17068000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>17141000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>17204000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>17632000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>17673000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>17732000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>17745000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>17837000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>17881000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>18150000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>18241000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>18255000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>16498000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>15903000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>15635000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>15686000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>15567000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>15636000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>11705000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>11733000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>11753000</v>
       </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5199,8 +5312,11 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5315,124 +5431,130 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2274000</v>
+      </c>
+      <c r="E52" s="3">
         <v>1441000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2258000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2175000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2162000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1400000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1967000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1951000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1834000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1286000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1803000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1749000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1842000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1234000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1693000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1763000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1667000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1582000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1589000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1595000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1618000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1057000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1072000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1041000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>870000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>765000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>811000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>796000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>761000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>754000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>733000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>711000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>694000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>673000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>594000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>591000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>576000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>562000</v>
       </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5547,124 +5669,130 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>36019000</v>
+      </c>
+      <c r="E54" s="3">
         <v>36658000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>36464000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>36280000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>37310000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>37100000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>37732000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>37465000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>36746000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>36251000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>36761000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>36796000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>36678000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>36821000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>36245000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>35898000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>36824000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>36309000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>35663000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>34474000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>35458000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>34456000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>34558000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>33890000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>33811000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>32918000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>33665000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>32498000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>32335000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>29109000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>28638000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>28091000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>28046000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>28066000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>28063000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>22596000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>22257000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>22373000</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5705,8 +5833,9 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5747,704 +5876,723 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2723000</v>
+      </c>
+      <c r="E57" s="3">
         <v>2601000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2373000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2350000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2497000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2402000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2291000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2244000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2623000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2594000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2421000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2387000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2530000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2483000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2306000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2269000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2115000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2225000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1950000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1900000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1997000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1876000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1743000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1742000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1916000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1926000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1958000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1710000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1962000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1694000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1546000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1485000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1748000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>1698000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>1608000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>1466000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>1591000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>1511000</v>
       </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>909000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1110000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>886000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>896000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>95000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>247000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1320000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1315000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1308000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2048000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>457000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1065000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>490000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>459000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>67000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>79000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1090000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1067000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1566000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>580000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>566000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>548000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>750000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1142000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1947000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>2102000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>2125000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1564000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>3917000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1911000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1308000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1128000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>811000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>906000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>1017000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>543000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>66000</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>79000</v>
       </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1910000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1769000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1619000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1568000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1534000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1226000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1373000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1321000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1500000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1185000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1368000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1214000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2094000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2371000</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>2309000</v>
       </c>
       <c r="R59" s="3">
         <v>2309000</v>
       </c>
       <c r="S59" s="3">
+        <v>2309000</v>
+      </c>
+      <c r="T59" s="3">
         <v>2829000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>3033000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2668000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2132000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2286000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1810000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1780000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1522000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1673000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1485000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1514000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1340000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1551000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1426000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1258000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1225000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1419000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>1428000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>1240000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>1097000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>1315000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>1172000</v>
       </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6203000</v>
+      </c>
+      <c r="E60" s="3">
         <v>6389000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>5690000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>5494000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>4780000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>4787000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>5810000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>5633000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>6172000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>6499000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>4948000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>5346000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>5114000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>5313000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>4682000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>4657000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>6034000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>6325000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>6184000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>4612000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>4849000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>4234000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>4273000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>4406000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>5536000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>5513000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>5597000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>4614000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>7430000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>5031000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>4112000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>3838000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>3978000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>4032000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>3865000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>3106000</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>2972000</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>2762000</v>
       </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>7453000</v>
+      </c>
+      <c r="E61" s="3">
         <v>8585000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>8179000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>8172000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>9711000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>10234000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>9701000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>9645000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>8370000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>7987000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>8863000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>7865000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>7859000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>7862000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>8261000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>8270000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>8274000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>8281000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>8786000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>9784000</v>
-      </c>
-      <c r="W61" s="3">
-        <v>10791000</v>
       </c>
       <c r="X61" s="3">
         <v>10791000</v>
       </c>
       <c r="Y61" s="3">
+        <v>10791000</v>
+      </c>
+      <c r="Z61" s="3">
         <v>11279000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>10978000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>9772000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>9830000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>10461000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>10810000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>8075000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>7962000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>8852000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>8872000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>8875000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>9297000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>9807000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>5905000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>5901000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>6200000</v>
       </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1995000</v>
+      </c>
+      <c r="E62" s="3">
         <v>1097000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1910000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1843000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1909000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1100000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1701000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1672000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1614000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1009000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1599000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1589000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3918000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3835000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3813000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3815000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3974000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3849000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>4000000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>4008000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>4037000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>4045000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>4002000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>3912000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>3937000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>3481000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>3466000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>3516000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>3571000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>3305000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>3237000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>3225000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>3219000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>4178000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>4254000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>3796000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>3817000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>3787000</v>
       </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6559,8 +6707,11 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6675,8 +6826,11 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6791,124 +6945,130 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>17856000</v>
+      </c>
+      <c r="E66" s="3">
         <v>18431000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>17996000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>17749000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>18683000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>18586000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>19530000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>19242000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>18458000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>17996000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>17851000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>17238000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>17043000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>17119000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>16890000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>16884000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>18421000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>18586000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>19102000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>18543000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>19820000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>19202000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>19700000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>19441000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>19392000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>18968000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>19737000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>19075000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>19208000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>16306000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>16212000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>15955000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>16091000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>17525000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>17946000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>12825000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>12707000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>12765000</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6949,8 +7109,9 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7065,8 +7226,11 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7181,8 +7345,11 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7297,8 +7464,11 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7413,124 +7583,130 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>18553000</v>
+      </c>
+      <c r="E72" s="3">
         <v>18647000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>18772000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>18886000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>19054000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>18873000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>18687000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>18667000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>18693000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>18760000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>19378000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>19962000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>20225000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>20084000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>19708000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>19119000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>18453000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>17502000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>16305000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>15716000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>15399000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>15100000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>14769000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>14392000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>14178000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>13655000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>13553000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>13012000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>12719000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>12329000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>11913000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>11479000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>11272000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>9776000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>9464000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>9098000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>8837000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>8348000</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7645,8 +7821,11 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7761,8 +7940,11 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7877,124 +8059,130 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>18023000</v>
+      </c>
+      <c r="E76" s="3">
         <v>18085000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>18338000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>18400000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>18503000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>18390000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>18076000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>18089000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>18150000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>18133000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>18779000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>19399000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>19635000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>19702000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>19355000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>19014000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>18403000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>17723000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>16561000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>15931000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>15638000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>15254000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>14858000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>14449000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>14419000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>13950000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>13928000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>13423000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>13127000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>12803000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>12426000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>12136000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>11955000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>10541000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>10117000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>9771000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>9550000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>9608000</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8109,245 +8297,254 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46018</v>
+      </c>
+      <c r="E80" s="2">
         <v>45927</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45836</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45745</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45654</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45563</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45472</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45381</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45290</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45108</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45017</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44835</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44744</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44653</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44562</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44471</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44380</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44289</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44198</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44107</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44009</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43918</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43827</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43736</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43645</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43554</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43463</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43372</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43099</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42917</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42826</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42735</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>85000</v>
+      </c>
+      <c r="E81" s="3">
         <v>47000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>61000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>7000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>359000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>357000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>191000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>145000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>107000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-450000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-417000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-97000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>316000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>538000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>750000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>829000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1121000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1355000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>749000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>476000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>467000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>613000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>527000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>376000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>505000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>327000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>676000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>426000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>551000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>537000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>541000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>315000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>1631000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>394000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>447000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>340000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>593000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>391000</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8388,124 +8585,128 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>261000</v>
+      </c>
+      <c r="E83" s="3">
         <v>77000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>360000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>349000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>373000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>152000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>309000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>317000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>303000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>246000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>233000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>230000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>303000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>310000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>297000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>295000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>300000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>308000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>302000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>306000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>298000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>316000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>295000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>293000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>288000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>289000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>286000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>273000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>250000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>246000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>238000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>230000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>229000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>218000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>187000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>179000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>177000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>179000</v>
       </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8620,8 +8821,11 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8736,8 +8940,11 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8852,8 +9059,11 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8968,8 +9178,11 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9084,124 +9297,130 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>942000</v>
+      </c>
+      <c r="E89" s="3">
         <v>535000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>774000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-185000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1031000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>617000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>796000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-123000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1300000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>323000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>660000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>7000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>762000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>797000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>666000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-208000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1432000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1184000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1307000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-36000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1385000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1166000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1448000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>366000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>894000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>978000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>596000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>71000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>868000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1039000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>785000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>13000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1126000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>1150000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>467000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>-152000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>1134000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>843000</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9242,124 +9461,128 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-252000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-287000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-227000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-193000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-271000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-248000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-263000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-267000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-354000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-375000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-467000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-508000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-589000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-564000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-476000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-439000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-408000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-350000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-302000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-268000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-289000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-292000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-283000</v>
-      </c>
-      <c r="Z91" s="3">
-        <v>-312000</v>
       </c>
       <c r="AA91" s="3">
         <v>-312000</v>
       </c>
       <c r="AB91" s="3">
+        <v>-312000</v>
+      </c>
+      <c r="AC91" s="3">
         <v>-288000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-315000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-338000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-318000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-313000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-328000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-263000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-296000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-287000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-315000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-267000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-200000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-180000</v>
       </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9474,8 +9697,11 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9590,124 +9816,130 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-183000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-260000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>9000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-181000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-233000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-34000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-233000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-243000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-378000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-427000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-696000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-507000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-669000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-610000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-440000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-426000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-459000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>841000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-275000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-249000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-259000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-280000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-266000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-496000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-381000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-129000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-569000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-317000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-2449000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-483000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-737000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-264000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-422000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-297000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-3389000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-264000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-214000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-182000</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9748,25 +9980,26 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>177000</v>
+      </c>
+      <c r="E96" s="3">
         <v>173000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>175000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>174000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>175000</v>
-      </c>
-      <c r="H96" s="3">
-        <v>171000</v>
       </c>
       <c r="I96" s="3">
         <v>171000</v>
@@ -9778,7 +10011,7 @@
         <v>171000</v>
       </c>
       <c r="L96" s="3">
-        <v>167000</v>
+        <v>171000</v>
       </c>
       <c r="M96" s="3">
         <v>167000</v>
@@ -9787,22 +10020,22 @@
         <v>167000</v>
       </c>
       <c r="O96" s="3">
+        <v>167000</v>
+      </c>
+      <c r="P96" s="3">
         <v>-169000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-162000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-163000</v>
-      </c>
-      <c r="R96" s="3">
-        <v>-164000</v>
       </c>
       <c r="S96" s="3">
         <v>-164000</v>
       </c>
       <c r="T96" s="3">
-        <v>-159000</v>
+        <v>-164000</v>
       </c>
       <c r="U96" s="3">
         <v>-159000</v>
@@ -9814,34 +10047,34 @@
         <v>-159000</v>
       </c>
       <c r="X96" s="3">
-        <v>-150000</v>
+        <v>-159000</v>
       </c>
       <c r="Y96" s="3">
         <v>-150000</v>
       </c>
       <c r="Z96" s="3">
+        <v>-150000</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-151000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-150000</v>
-      </c>
-      <c r="AB96" s="3">
-        <v>-134000</v>
       </c>
       <c r="AC96" s="3">
         <v>-134000</v>
       </c>
       <c r="AD96" s="3">
+        <v>-134000</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-135000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-134000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-107000</v>
-      </c>
-      <c r="AG96" s="3">
-        <v>-108000</v>
       </c>
       <c r="AH96" s="3">
         <v>-108000</v>
@@ -9850,22 +10083,25 @@
         <v>-108000</v>
       </c>
       <c r="AJ96" s="3">
+        <v>-108000</v>
+      </c>
+      <c r="AK96" s="3">
         <v>-81000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-80000</v>
-      </c>
-      <c r="AL96" s="3">
-        <v>-79000</v>
       </c>
       <c r="AM96" s="3">
         <v>-79000</v>
       </c>
       <c r="AN96" s="3">
+        <v>-79000</v>
+      </c>
+      <c r="AO96" s="3">
         <v>-54000</v>
       </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9980,8 +10216,11 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10096,8 +10335,11 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10212,352 +10454,364 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-718000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-600000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-245000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-937000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-195000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1464000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-168000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1077000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-26000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-13000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>202000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>381000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-482000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-195000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-361000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1283000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-484000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1189000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-197000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1172000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-173000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-874000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-255000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>168000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-507000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-761000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>20000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>201000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>1711000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-455000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-71000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>153000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-729000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-769000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>2908000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>348000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-957000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-510000</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-28000</v>
+      </c>
+      <c r="E101" s="3">
         <v>29000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-8000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-13000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>15000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-9000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-10000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>8000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>12000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-17000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-24000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>4000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>12000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-17000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-24000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>4000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>2000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-7000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>1000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-6000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>16000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>7000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>1000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-16000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>7000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-10000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>5000</v>
       </c>
-      <c r="AE101" s="3">
-        <v>0</v>
-      </c>
       <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-5000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>3000</v>
       </c>
-      <c r="AI101" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK101" s="3">
         <v>3000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>2000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>4000</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>-5000</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>49000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-318000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>555000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1300000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>575000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-852000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>387000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>698000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>911000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-126000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>156000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-111000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-377000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-25000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-159000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1913000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>491000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>829000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>836000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-1463000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>969000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>19000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>928000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>22000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>13000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>78000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>46000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-40000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>130000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>100000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-28000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-95000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-25000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>87000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-12000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-64000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-42000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>152000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TSN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TSN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="92">
   <si>
     <t>TSN</t>
   </si>
@@ -656,523 +656,536 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46109</v>
+      </c>
+      <c r="E7" s="2">
         <v>46018</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45927</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45836</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45745</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45654</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45563</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45472</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45381</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45290</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45108</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45017</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44835</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44744</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44653</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44562</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44471</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44380</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44289</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44198</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44107</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44009</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43918</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43827</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43736</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43645</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43554</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43463</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43372</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43099</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43008</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42917</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42826</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42735</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>13653000</v>
+      </c>
+      <c r="E8" s="3">
         <v>14313000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>13860000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>13884000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>13074000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>13623000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>13565000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>13353000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>13072000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>13319000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>13348000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>13140000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>13133000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>13260000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>13737000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>13495000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>13117000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>12933000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>12811000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>12478000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>11300000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>10460000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>11460000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>10022000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>10888000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>10815000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>10884000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>10885000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>10443000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>10193000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>9999000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>10051000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>9773000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>10229000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>10145000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>9850000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>9083000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>9182000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>9156000</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>12632000</v>
+      </c>
+      <c r="E9" s="3">
         <v>13400000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>13336000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>12846000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>12065000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>12457000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>12571000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>12325000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>12113000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>12371000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>12664000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>12451000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>12518000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>12319000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>12412000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>11884000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>11382000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>10918000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>10270000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>10803000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>9952000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>9163000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>9653000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>8394000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>9966000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>9337000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>19490000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>9549000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>9251000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>8838000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>8660000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>8752000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>8753000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>8786000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>8794000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>8648000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>8036000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>7699000</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>8067000</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1021000</v>
+      </c>
+      <c r="E10" s="3">
         <v>913000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>524000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1038000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1009000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1166000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>994000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1028000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>959000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>948000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>684000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>689000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>615000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>941000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1325000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1611000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1735000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2015000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2541000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1675000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1348000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1297000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1807000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1628000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>922000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1478000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>-8606000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1336000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1192000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1355000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1339000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1299000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1020000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1443000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>1351000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>1202000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>1047000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>1483000</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>1089000</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1214,19 +1227,20 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="3">
         <v>126000</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>8</v>
@@ -1234,11 +1248,11 @@
       <c r="H12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J12" s="3">
         <v>106000</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>8</v>
@@ -1246,11 +1260,11 @@
       <c r="L12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M12" s="3">
+      <c r="M12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N12" s="3">
         <v>114000</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O12" s="3" t="s">
         <v>8</v>
@@ -1333,8 +1347,11 @@
       <c r="AO12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1452,55 +1469,58 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>62000</v>
+      </c>
+      <c r="E14" s="3">
         <v>192000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-258000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>245000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>415000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>72000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-107000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>150000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>93000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>145000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>583000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>469000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>114000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-14000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>66000</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>8</v>
@@ -1508,50 +1528,50 @@
       <c r="T14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U14" s="3">
+      <c r="U14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V14" s="3">
         <v>65000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>55000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>95000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>120000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>223000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>342000</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
       <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
         <v>52000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>10000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>-40000</v>
-      </c>
-      <c r="AE14" s="3">
-        <v>8000</v>
       </c>
       <c r="AF14" s="3">
         <v>8000</v>
       </c>
       <c r="AG14" s="3">
-        <v>14000</v>
+        <v>8000</v>
       </c>
       <c r="AH14" s="3">
         <v>14000</v>
       </c>
       <c r="AI14" s="3">
-        <v>0</v>
+        <v>14000</v>
       </c>
       <c r="AJ14" s="3">
         <v>0</v>
@@ -1571,50 +1591,53 @@
       <c r="AO14" s="3">
         <v>0</v>
       </c>
+      <c r="AP14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>317000</v>
+      </c>
+      <c r="E15" s="3">
         <v>319000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>321000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>329000</v>
       </c>
-      <c r="G15" s="3">
-        <v>336000</v>
-      </c>
       <c r="H15" s="3">
+        <v>330000</v>
+      </c>
+      <c r="I15" s="3">
         <v>319000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>306000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>360000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>349000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>373000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>381000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>309000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>317000</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
@@ -1690,8 +1713,11 @@
       <c r="AO15" s="3">
         <v>0</v>
       </c>
+      <c r="AP15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1730,246 +1756,253 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>13156000</v>
+      </c>
+      <c r="E17" s="3">
         <v>13896000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>13929000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>13379000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>12559000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>12964000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>13125000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>12862000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>12667000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>12933000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>13235000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>12999000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>13068000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>12793000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>12971000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>12462000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>11961000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>11478000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>10902000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>11416000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>10580000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>9755000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>10554000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>9247000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>10373000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>10057000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>10337000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>10049000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>9808000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>9386000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>9180000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>9254000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>9275000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>9307000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>9464000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>9153000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>8512000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>8200000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>8570000</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>497000</v>
+      </c>
+      <c r="E18" s="3">
         <v>417000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-69000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>505000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>515000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>659000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>440000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>491000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>405000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>386000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>113000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>141000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>65000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>467000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>766000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1033000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1156000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1455000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1909000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1062000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>720000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>705000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>906000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>775000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>515000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>758000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>547000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>836000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>635000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>807000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>819000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>797000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>498000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>922000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>681000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>697000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>571000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>982000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>586000</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2011,603 +2044,619 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="E20" s="3">
         <v>7000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>31000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-31000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-23000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>14000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-29000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-11000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>12000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-15000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>15000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>51000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-17000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>38000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>28000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>55000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>29000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>9000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>14000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>21000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>14000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>109000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>19000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-15000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>9000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>12000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>5000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>25000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>13000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>9000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>6000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-7000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-9000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>4000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-12000</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>827000</v>
+      </c>
+      <c r="E21" s="3">
         <v>729000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>221000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>865000</v>
       </c>
-      <c r="G21" s="3">
-        <v>874000</v>
-      </c>
       <c r="H21" s="3">
+        <v>868000</v>
+      </c>
+      <c r="I21" s="3">
         <v>964000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>775000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>862000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>742000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>774000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>493000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>435000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>383000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>821000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1059000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1368000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1479000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1810000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>2246000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1373000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1040000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1024000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1221000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1084000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>917000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1065000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>821000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1131000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>920000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1062000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1090000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1048000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>737000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1157000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>892000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>875000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>754000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>1147000</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>768000</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>97000</v>
+      </c>
+      <c r="E22" s="3">
         <v>104000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>106000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>113000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>110000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>120000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>130000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>135000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>111000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>105000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>93000</v>
-      </c>
-      <c r="N22" s="3">
-        <v>89000</v>
       </c>
       <c r="O22" s="3">
         <v>89000</v>
       </c>
       <c r="P22" s="3">
+        <v>89000</v>
+      </c>
+      <c r="Q22" s="3">
         <v>84000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>83000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>85000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>97000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>100000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>103000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>105000</v>
-      </c>
-      <c r="W22" s="3">
-        <v>110000</v>
       </c>
       <c r="X22" s="3">
         <v>110000</v>
       </c>
       <c r="Y22" s="3">
+        <v>110000</v>
+      </c>
+      <c r="Z22" s="3">
         <v>124000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>122000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>119000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>120000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>123000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>121000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>119000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>99000</v>
-      </c>
-      <c r="AG22" s="3">
-        <v>87000</v>
       </c>
       <c r="AH22" s="3">
         <v>87000</v>
       </c>
       <c r="AI22" s="3">
+        <v>87000</v>
+      </c>
+      <c r="AJ22" s="3">
         <v>84000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>86000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>94000</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>71000</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>56000</v>
-      </c>
-      <c r="AN22" s="3">
-        <v>58000</v>
       </c>
       <c r="AO22" s="3">
         <v>58000</v>
       </c>
+      <c r="AP22" s="3">
+        <v>58000</v>
+      </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>359000</v>
+      </c>
+      <c r="E23" s="3">
         <v>127000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>68000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>193000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>30000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>478000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>475000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>253000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>203000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>161000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-556000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-426000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-130000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>434000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>666000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>986000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1087000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1410000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1835000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>966000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>624000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>616000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>781000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>667000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>505000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>657000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>409000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>724000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>528000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>713000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>757000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>723000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>423000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>842000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>580000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>617000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>519000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>912000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>531000</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>95000</v>
+      </c>
+      <c r="E24" s="3">
         <v>37000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>10000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>124000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>16000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>112000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>111000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>57000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>55000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>47000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-113000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>9000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-39000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>114000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>129000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>233000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>254000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>284000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>477000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>213000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>147000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>144000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>165000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>140000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>126000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>148000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>79000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>43000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>98000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>161000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>220000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>182000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>116000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>204000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>185000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>169000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>178000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>318000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>139000</v>
       </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2725,246 +2774,255 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>264000</v>
+      </c>
+      <c r="E26" s="3">
         <v>90000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>58000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>69000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>14000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>366000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>364000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>196000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>148000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>114000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-443000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-435000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-91000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>320000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>537000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>753000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>833000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1126000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1358000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>753000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>477000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>472000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>616000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>527000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>379000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>509000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>330000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>681000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>430000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>552000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>537000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>541000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>307000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>638000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>395000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>448000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>341000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>594000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>392000</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>260000</v>
+      </c>
+      <c r="E27" s="3">
         <v>85000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>47000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>61000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>7000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>359000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>357000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>191000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>145000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>107000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-450000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-417000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-97000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>316000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>538000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>750000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>829000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1121000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1355000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>749000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>476000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>467000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>613000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>527000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>376000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>505000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>327000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>676000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>426000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>551000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>537000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>540000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>306000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>637000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>394000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>447000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>340000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>593000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>391000</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3082,8 +3140,11 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3159,8 +3220,8 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
+      <c r="AB29" s="3">
+        <v>0</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
@@ -3174,20 +3235,20 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG29" s="3">
-        <v>0</v>
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI29" s="3">
         <v>1000</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>9000</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>994000</v>
-      </c>
-      <c r="AK29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AL29" s="3" t="s">
         <v>8</v>
@@ -3201,8 +3262,11 @@
       <c r="AO29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3320,8 +3384,11 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3439,246 +3506,255 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-7000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-31000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>31000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>23000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-14000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>29000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>11000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-12000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>15000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-15000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-51000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>17000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-38000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-28000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-55000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-29000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-9000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-14000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-21000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>1000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-14000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-109000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-19000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>15000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-9000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-12000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-5000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-25000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-13000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-9000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-6000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>7000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>9000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-4000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>12000</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-3000</v>
       </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>260000</v>
+      </c>
+      <c r="E33" s="3">
         <v>85000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>47000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>61000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>7000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>359000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>357000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>191000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>145000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>107000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-450000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-417000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-97000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>316000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>538000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>750000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>829000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1121000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1355000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>749000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>476000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>467000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>613000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>527000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>376000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>505000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>327000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>676000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>426000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>551000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>537000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>541000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>315000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>1631000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>394000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>447000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>340000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>593000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>391000</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3796,251 +3872,260 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>260000</v>
+      </c>
+      <c r="E35" s="3">
         <v>85000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>47000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>61000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>7000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>359000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>357000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>191000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>145000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>107000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-450000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-417000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-97000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>316000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>538000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>750000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>829000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1121000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1355000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>749000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>476000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>467000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>613000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>527000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>376000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>505000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>327000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>676000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>426000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>551000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>537000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>541000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>315000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>1631000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>394000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>447000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>340000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>593000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>391000</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46109</v>
+      </c>
+      <c r="E38" s="2">
         <v>46018</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45927</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45836</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45745</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45654</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45563</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45472</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45381</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45290</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45108</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45017</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44835</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44744</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44653</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44562</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44471</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44380</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44289</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44198</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44107</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44009</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43918</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43827</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43736</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43645</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43554</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43463</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43372</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43099</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43008</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42917</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42826</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42735</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4082,8 +4167,9 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4125,127 +4211,131 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>500000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1278000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1229000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1547000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>992000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2292000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1717000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2569000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2182000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1484000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>573000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>699000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>543000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>654000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1031000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1056000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1151000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2956000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2507000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1613000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>877000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2406000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1420000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1365000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>437000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>497000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>484000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>406000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>360000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>400000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>270000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>170000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>198000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>293000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>318000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>231000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>243000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>307000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>349000</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4256,37 +4346,37 @@
         <v>0</v>
       </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
         <v>1000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J42" s="3">
         <v>10000</v>
       </c>
-      <c r="H42" s="3">
-        <v>1000</v>
-      </c>
-      <c r="I42" s="3">
-        <v>10000</v>
-      </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>13000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>16000</v>
-      </c>
-      <c r="L42" s="3">
-        <v>15000</v>
       </c>
       <c r="M42" s="3">
         <v>15000</v>
       </c>
       <c r="N42" s="3">
-        <v>7000</v>
+        <v>15000</v>
       </c>
       <c r="O42" s="3">
         <v>7000</v>
       </c>
       <c r="P42" s="3">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="Q42" s="3">
         <v>0</v>
@@ -4363,484 +4453,499 @@
       <c r="AO42" s="3">
         <v>0</v>
       </c>
+      <c r="AP42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2399000</v>
+      </c>
+      <c r="E43" s="3">
         <v>2429000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2524000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2454000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2385000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2323000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2406000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2389000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2358000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2263000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2476000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2451000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2433000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2295000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2577000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2518000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2408000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2091000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2400000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2324000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2113000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1900000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1952000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2064000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2248000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2063000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>4346000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2452000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1837000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1892000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1723000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>1684000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>1594000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>1600000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>1675000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>1710000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>1589000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>1512000</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>1542000</v>
       </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>5478000</v>
+      </c>
+      <c r="E44" s="3">
         <v>5406000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>5681000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>5436000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>5395000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>5114000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>5195000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>5033000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>5056000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>5087000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>5328000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>5391000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>5504000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>5596000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>5514000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>5332000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>4990000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>4454000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>4382000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>4262000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>4128000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>3915000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>3859000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>3915000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>4025000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>4304000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>3929000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>4149000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>3899000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>3777000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>3513000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>3378000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>3328000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>3213000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>3239000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>3248000</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>2970000</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>2767000</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>2732000</v>
       </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>497000</v>
+      </c>
+      <c r="E45" s="3">
         <v>399000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>482000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>421000</v>
       </c>
-      <c r="G45" s="3">
-        <v>386000</v>
-      </c>
       <c r="H45" s="3">
+        <v>396000</v>
+      </c>
+      <c r="I45" s="3">
         <v>352000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>423000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>568000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>354000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>367000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>330000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>335000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>405000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>408000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>508000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>397000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>448000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>635000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>533000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1009000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>896000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>323000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>367000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>355000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>389000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>329000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>404000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>426000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>280000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>232000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>182000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>845000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>870000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>887000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>1026000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>1099000</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>215000</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>156000</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>265000</v>
       </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>8874000</v>
+      </c>
+      <c r="E46" s="3">
         <v>9512000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>9916000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>9859000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>9168000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>10082000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>9751000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>10572000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>9966000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>9216000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>8722000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>8883000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>8892000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>8953000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>9630000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>9303000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>8997000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>10136000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>9822000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>9208000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>8014000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>8544000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>7598000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>7699000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>7099000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>7193000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>6990000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>7433000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>6376000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>6301000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>5688000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>6077000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>5990000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>5993000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>6258000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>6288000</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>5017000</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>4742000</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>4888000</v>
       </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4848,40 +4953,40 @@
         <v>118000</v>
       </c>
       <c r="E47" s="3">
+        <v>118000</v>
+      </c>
+      <c r="F47" s="3">
         <v>117000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>115000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>114000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>109000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>103000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>96000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>92000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>93000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>89000</v>
-      </c>
-      <c r="N47" s="3">
-        <v>97000</v>
       </c>
       <c r="O47" s="3">
         <v>97000</v>
       </c>
       <c r="P47" s="3">
-        <v>0</v>
+        <v>97000</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -4958,246 +5063,255 @@
       <c r="AO47" s="3">
         <v>0</v>
       </c>
+      <c r="AP47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>8917000</v>
+      </c>
+      <c r="E48" s="3">
         <v>9064000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>10091000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>9081000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>9278000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>9353000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>10152000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>9368000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>9593000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>9672000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>10178000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>9612000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>9351000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>9120000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>9192000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>8393000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>8193000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>8012000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>7837000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>7725000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>7661000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>7664000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>8128000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>8055000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>8005000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>7911000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>7282000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>7271000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>7085000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>7018000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>6169000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>5925000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>5755000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>5673000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>5568000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>5545000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>5283000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>5206000</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>5170000</v>
       </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>14998000</v>
+      </c>
+      <c r="E49" s="3">
         <v>15051000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>15093000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>15151000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>15545000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>15604000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>15694000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>15729000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>15863000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>15931000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>15976000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>16366000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>16707000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>16763000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>16765000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>16856000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>16945000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>17009000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>17068000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>17141000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>17204000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>17632000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>17673000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>17732000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>17745000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>17837000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>17881000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>18150000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>18241000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>18255000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>16498000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>15903000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>15635000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>15686000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>15567000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>15636000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>11705000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>11733000</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>11753000</v>
       </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5315,8 +5429,11 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5434,127 +5551,133 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2258000</v>
+      </c>
+      <c r="E52" s="3">
         <v>2274000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1441000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2258000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2175000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2162000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1400000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1967000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1951000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1834000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1286000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1803000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1749000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1842000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1234000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1693000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1763000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1667000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1582000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1589000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1595000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1618000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1057000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1072000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1041000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>870000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>765000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>811000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>796000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>761000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>754000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>733000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>711000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>694000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>673000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>594000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>591000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>576000</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>562000</v>
       </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5672,127 +5795,133 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>35165000</v>
+      </c>
+      <c r="E54" s="3">
         <v>36019000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>36658000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>36464000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>36280000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>37310000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>37100000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>37732000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>37465000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>36746000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>36251000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>36761000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>36796000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>36678000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>36821000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>36245000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>35898000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>36824000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>36309000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>35663000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>34474000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>35458000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>34456000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>34558000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>33890000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>33811000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>32918000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>33665000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>32498000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>32335000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>29109000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>28638000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>28091000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>28046000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>28066000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>28063000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>22596000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>22257000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>22373000</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5834,8 +5963,9 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5877,722 +6007,741 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2467000</v>
+      </c>
+      <c r="E57" s="3">
         <v>2723000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2601000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2373000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2350000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2497000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2402000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2291000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2244000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2623000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2594000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2421000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2387000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2530000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2483000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2306000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2269000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2115000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2225000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1950000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1900000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1997000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1876000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1743000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1742000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1916000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1926000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1958000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1710000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1962000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1694000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1546000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1485000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>1748000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>1698000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>1608000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>1466000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>1591000</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>1511000</v>
       </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>141000</v>
+      </c>
+      <c r="E58" s="3">
         <v>909000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1110000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>886000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>896000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>95000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>247000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1320000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1315000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1308000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2048000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>457000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1065000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>490000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>459000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>67000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>79000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1090000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1067000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1566000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>580000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>566000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>548000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>750000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1142000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1947000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>2102000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>2125000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1564000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>3917000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1911000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1308000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1128000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>811000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>906000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>1017000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>543000</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>66000</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>79000</v>
       </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1563000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1910000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1769000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1619000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1568000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1534000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1226000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1373000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1321000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1500000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1185000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1368000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1214000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2094000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2371000</v>
-      </c>
-      <c r="R59" s="3">
-        <v>2309000</v>
       </c>
       <c r="S59" s="3">
         <v>2309000</v>
       </c>
       <c r="T59" s="3">
+        <v>2309000</v>
+      </c>
+      <c r="U59" s="3">
         <v>2829000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3033000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2668000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2132000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2286000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1810000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1780000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1522000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1673000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1485000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1514000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1340000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1551000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1426000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1258000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1225000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>1419000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>1428000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>1240000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>1097000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>1315000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>1172000</v>
       </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4848000</v>
+      </c>
+      <c r="E60" s="3">
         <v>6203000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>6389000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>5690000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>5494000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>4780000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>4787000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>5810000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>5633000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>6172000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>6499000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>4948000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>5346000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>5114000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>5313000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>4682000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>4657000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>6034000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>6325000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>6184000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>4612000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>4849000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>4234000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>4273000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>4406000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>5536000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>5513000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>5597000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>4614000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>7430000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>5031000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>4112000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>3838000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>3978000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>4032000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>3865000</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>3106000</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>2972000</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>2762000</v>
       </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>7942000</v>
+      </c>
+      <c r="E61" s="3">
         <v>7453000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>8585000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>8179000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>8172000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>9711000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>10234000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>9701000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>9645000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>8370000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>7987000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>8863000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>7865000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>7859000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>7862000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>8261000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>8270000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>8274000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>8281000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>8786000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>9784000</v>
-      </c>
-      <c r="X61" s="3">
-        <v>10791000</v>
       </c>
       <c r="Y61" s="3">
         <v>10791000</v>
       </c>
       <c r="Z61" s="3">
+        <v>10791000</v>
+      </c>
+      <c r="AA61" s="3">
         <v>11279000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>10978000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>9772000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>9830000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>10461000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>10810000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>8075000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>7962000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>8852000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>8872000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>8875000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>9297000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>9807000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>5905000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>5901000</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>6200000</v>
       </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1958000</v>
+      </c>
+      <c r="E62" s="3">
         <v>1995000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1097000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1910000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1843000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1909000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1100000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1701000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1672000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1614000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1009000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1599000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1589000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3918000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3835000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3813000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3815000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3974000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3849000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>4000000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>4008000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>4037000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>4045000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>4002000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>3912000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>3937000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>3481000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>3466000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>3516000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>3571000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>3305000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>3237000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>3225000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>3219000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>4178000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>4254000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>3796000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>3817000</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>3787000</v>
       </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6710,8 +6859,11 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6829,8 +6981,11 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6948,127 +7103,133 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>16964000</v>
+      </c>
+      <c r="E66" s="3">
         <v>17856000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>18431000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>17996000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>17749000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>18683000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>18586000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>19530000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>19242000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>18458000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>17996000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>17851000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>17238000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>17043000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>17119000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>16890000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>16884000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>18421000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>18586000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>19102000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>18543000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>19820000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>19202000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>19700000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>19441000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>19392000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>18968000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>19737000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>19075000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>19208000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>16306000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>16212000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>15955000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>16091000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>17525000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>17946000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>12825000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>12707000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>12765000</v>
       </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7110,8 +7271,9 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7229,8 +7391,11 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7348,8 +7513,11 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7467,8 +7635,11 @@
       <c r="AO70" s="3">
         <v>0</v>
       </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7586,127 +7757,133 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>18637000</v>
+      </c>
+      <c r="E72" s="3">
         <v>18553000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>18647000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>18772000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>18886000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>19054000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>18873000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>18687000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>18667000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>18693000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>18760000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>19378000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>19962000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>20225000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>20084000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>19708000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>19119000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>18453000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>17502000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>16305000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>15716000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>15399000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>15100000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>14769000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>14392000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>14178000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>13655000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>13553000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>13012000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>12719000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>12329000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>11913000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>11479000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>11272000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>9776000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>9464000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>9098000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>8837000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>8348000</v>
       </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7824,8 +8001,11 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7943,8 +8123,11 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8062,127 +8245,133 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>18098000</v>
+      </c>
+      <c r="E76" s="3">
         <v>18023000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>18085000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>18338000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>18400000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>18503000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>18390000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>18076000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>18089000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>18150000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>18133000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>18779000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>19399000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>19635000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>19702000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>19355000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>19014000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>18403000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>17723000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>16561000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>15931000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>15638000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>15254000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>14858000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>14449000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>14419000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>13950000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>13928000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>13423000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>13127000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>12803000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>12426000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>12136000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>11955000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>10541000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>10117000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>9771000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>9550000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>9608000</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8300,251 +8489,260 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46109</v>
+      </c>
+      <c r="E80" s="2">
         <v>46018</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45927</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45836</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45745</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45654</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45563</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45472</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45381</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45290</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45108</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45017</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44835</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44744</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44653</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44562</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44471</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44380</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44289</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44198</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44107</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44009</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43918</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43827</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43736</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43645</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43554</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43463</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43372</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43099</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43008</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42917</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42826</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42735</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>260000</v>
+      </c>
+      <c r="E81" s="3">
         <v>85000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>47000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>61000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>7000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>359000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>357000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>191000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>145000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>107000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-450000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-417000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-97000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>316000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>538000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>750000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>829000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1121000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1355000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>749000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>476000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>467000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>613000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>527000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>376000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>505000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>327000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>676000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>426000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>551000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>537000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>541000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>315000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>1631000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>394000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>447000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>340000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>593000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>391000</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8586,127 +8784,131 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>271000</v>
+      </c>
+      <c r="E83" s="3">
         <v>261000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>77000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>360000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>349000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>373000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>152000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>309000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>317000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>303000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>246000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>233000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>230000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>303000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>310000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>297000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>295000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>300000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>308000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>302000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>306000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>298000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>316000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>295000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>293000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>288000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>289000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>286000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>273000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>250000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>246000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>238000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>230000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>229000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>218000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>187000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>179000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>177000</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>179000</v>
       </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8824,8 +9026,11 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8943,8 +9148,11 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9062,8 +9270,11 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9181,8 +9392,11 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9300,127 +9514,133 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-113000</v>
+      </c>
+      <c r="E89" s="3">
         <v>942000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>535000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>774000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-185000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1031000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>617000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>796000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-123000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1300000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>323000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>660000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>7000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>762000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>797000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>666000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-208000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1432000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1184000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1307000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-36000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1385000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1166000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1448000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>366000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>894000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>978000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>596000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>71000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>868000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1039000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>785000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>13000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>1126000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>1150000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>467000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>-152000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>1134000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>843000</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9462,127 +9682,131 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-145000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-252000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-287000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-227000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-193000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-271000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-248000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-263000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-267000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-354000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-375000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-467000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-508000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-589000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-564000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-476000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-439000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-408000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-350000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-302000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-268000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-289000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-292000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-283000</v>
-      </c>
-      <c r="AA91" s="3">
-        <v>-312000</v>
       </c>
       <c r="AB91" s="3">
         <v>-312000</v>
       </c>
       <c r="AC91" s="3">
+        <v>-312000</v>
+      </c>
+      <c r="AD91" s="3">
         <v>-288000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-315000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-338000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-318000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-313000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-328000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-263000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-296000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-287000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-315000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-267000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-200000</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-180000</v>
       </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9700,8 +9924,11 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9819,127 +10046,133 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-116000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-183000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-260000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>9000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-181000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-233000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-34000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-233000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-243000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-378000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-427000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-696000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-507000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-669000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-610000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-440000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-426000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-459000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>841000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-275000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-249000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-259000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-280000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-266000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-496000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-381000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-129000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-569000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-317000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-2449000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-483000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-737000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-264000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-422000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-297000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-3389000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-264000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-214000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-182000</v>
       </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9981,28 +10214,29 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>176000</v>
+      </c>
+      <c r="E96" s="3">
         <v>177000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>173000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>175000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>174000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>175000</v>
-      </c>
-      <c r="I96" s="3">
-        <v>171000</v>
       </c>
       <c r="J96" s="3">
         <v>171000</v>
@@ -10014,7 +10248,7 @@
         <v>171000</v>
       </c>
       <c r="M96" s="3">
-        <v>167000</v>
+        <v>171000</v>
       </c>
       <c r="N96" s="3">
         <v>167000</v>
@@ -10023,22 +10257,22 @@
         <v>167000</v>
       </c>
       <c r="P96" s="3">
+        <v>167000</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-169000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-162000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-163000</v>
-      </c>
-      <c r="S96" s="3">
-        <v>-164000</v>
       </c>
       <c r="T96" s="3">
         <v>-164000</v>
       </c>
       <c r="U96" s="3">
-        <v>-159000</v>
+        <v>-164000</v>
       </c>
       <c r="V96" s="3">
         <v>-159000</v>
@@ -10050,34 +10284,34 @@
         <v>-159000</v>
       </c>
       <c r="Y96" s="3">
-        <v>-150000</v>
+        <v>-159000</v>
       </c>
       <c r="Z96" s="3">
         <v>-150000</v>
       </c>
       <c r="AA96" s="3">
+        <v>-150000</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-151000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-150000</v>
-      </c>
-      <c r="AC96" s="3">
-        <v>-134000</v>
       </c>
       <c r="AD96" s="3">
         <v>-134000</v>
       </c>
       <c r="AE96" s="3">
+        <v>-134000</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-135000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-134000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-107000</v>
-      </c>
-      <c r="AH96" s="3">
-        <v>-108000</v>
       </c>
       <c r="AI96" s="3">
         <v>-108000</v>
@@ -10086,22 +10320,25 @@
         <v>-108000</v>
       </c>
       <c r="AK96" s="3">
+        <v>-108000</v>
+      </c>
+      <c r="AL96" s="3">
         <v>-81000</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-80000</v>
-      </c>
-      <c r="AM96" s="3">
-        <v>-79000</v>
       </c>
       <c r="AN96" s="3">
         <v>-79000</v>
       </c>
       <c r="AO96" s="3">
+        <v>-79000</v>
+      </c>
+      <c r="AP96" s="3">
         <v>-54000</v>
       </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10219,8 +10456,11 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10338,8 +10578,11 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10457,361 +10700,373 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-549000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-718000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-600000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-245000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-937000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-195000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1464000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-168000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1077000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-26000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-13000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>202000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>381000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-482000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-195000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-361000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1283000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-484000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1189000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-197000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-1172000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-173000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-874000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-255000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>168000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-507000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-761000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>20000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>201000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>1711000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-455000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-71000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>153000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-729000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-769000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>2908000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>348000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-957000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-510000</v>
       </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-28000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>29000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-8000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-13000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>15000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-9000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-10000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>8000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>12000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-17000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-24000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>4000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>12000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-17000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-24000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>4000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>2000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-7000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>1000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-6000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>16000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>7000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>1000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-16000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>7000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-10000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>5000</v>
       </c>
-      <c r="AF101" s="3">
-        <v>0</v>
-      </c>
       <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-5000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>3000</v>
       </c>
-      <c r="AJ101" s="3">
-        <v>0</v>
-      </c>
       <c r="AK101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL101" s="3">
         <v>3000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>2000</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>4000</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>-5000</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-778000</v>
+      </c>
+      <c r="E102" s="3">
         <v>49000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-318000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>555000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1300000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>575000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-852000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>387000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>698000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>911000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-126000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>156000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-111000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-377000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-25000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-159000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-1913000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>491000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>829000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>836000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-1463000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>969000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>19000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>928000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>22000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>13000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>78000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>46000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-40000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>130000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>100000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-28000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-95000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-25000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>87000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-12000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-64000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-42000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>152000</v>
       </c>
     </row>
